--- a/Data/2014_F013B4_CO_ISOS/2014_F013B4_CO_ISOS_SoilAnalysis.xlsx
+++ b/Data/2014_F013B4_CO_ISOS/2014_F013B4_CO_ISOS_SoilAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2014_F013B4_CO_ISOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B7C0AF-921C-4E6F-8854-0A2968FABC72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5501E6ED-F02F-4BB7-B48A-5982009108EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16320" yWindow="-28050" windowWidth="17910" windowHeight="25080" activeTab="3" xr2:uid="{8C00C1F2-89F9-4A44-A266-AB1BCF5C18BB}"/>
+    <workbookView xWindow="-1665" yWindow="-25290" windowWidth="27270" windowHeight="17295" xr2:uid="{8C00C1F2-89F9-4A44-A266-AB1BCF5C18BB}"/>
   </bookViews>
   <sheets>
     <sheet name="SoilDJH" sheetId="4" r:id="rId1"/>
@@ -446,9 +446,6 @@
     <t>Plot</t>
   </si>
   <si>
-    <t>2013d260EM38</t>
-  </si>
-  <si>
     <t>2015d118EM38</t>
   </si>
   <si>
@@ -1314,6 +1311,9 @@
   </si>
   <si>
     <t>2016-p0604</t>
+  </si>
+  <si>
+    <t>2013d260EM38V</t>
   </si>
 </sst>
 </file>
@@ -1696,13 +1696,13 @@
         <v>122</v>
       </c>
       <c r="B1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E1" t="s">
         <v>134</v>
@@ -1713,7 +1713,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C2">
         <v>409014.13040000002</v>
@@ -1730,7 +1730,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C3">
         <v>409013.595399999</v>
@@ -1747,7 +1747,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C4">
         <v>409013.23430000001</v>
@@ -1764,7 +1764,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C5">
         <v>409012.73710000003</v>
@@ -1781,7 +1781,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C6">
         <v>409012.32490000001</v>
@@ -1798,7 +1798,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C7">
         <v>409011.88799999899</v>
@@ -1815,7 +1815,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C8">
         <v>408983.429999999</v>
@@ -1832,7 +1832,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C9">
         <v>408983.89409999899</v>
@@ -1849,7 +1849,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C10">
         <v>408984.30259999901</v>
@@ -1866,7 +1866,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C11">
         <v>408984.79070000001</v>
@@ -1883,7 +1883,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C12">
         <v>408985.21360000002</v>
@@ -1900,7 +1900,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C13">
         <v>408985.649299999</v>
@@ -1917,7 +1917,7 @@
         <v>131</v>
       </c>
       <c r="B14" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C14">
         <v>408992.87400000001</v>
@@ -1934,7 +1934,7 @@
         <v>132</v>
       </c>
       <c r="B15" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C15">
         <v>408992.37520000001</v>
@@ -1951,7 +1951,7 @@
         <v>133</v>
       </c>
       <c r="B16" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C16">
         <v>408991.93300000002</v>
@@ -1968,7 +1968,7 @@
         <v>134</v>
       </c>
       <c r="B17" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C17">
         <v>408991.4412</v>
@@ -1985,7 +1985,7 @@
         <v>135</v>
       </c>
       <c r="B18" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C18">
         <v>408990.94170000002</v>
@@ -2002,7 +2002,7 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C19">
         <v>408957.18540000002</v>
@@ -2019,7 +2019,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C20">
         <v>408956.76750000002</v>
@@ -2036,7 +2036,7 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C21">
         <v>408956.30570000003</v>
@@ -2053,7 +2053,7 @@
         <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C22">
         <v>408955.91499999899</v>
@@ -2070,7 +2070,7 @@
         <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C23">
         <v>408955.44280000002</v>
@@ -2087,7 +2087,7 @@
         <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C24">
         <v>408955.01179999899</v>
@@ -2104,7 +2104,7 @@
         <v>136</v>
       </c>
       <c r="B25" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C25">
         <v>408962.41840000002</v>
@@ -2121,7 +2121,7 @@
         <v>137</v>
       </c>
       <c r="B26" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C26">
         <v>408961.93680000002</v>
@@ -2138,7 +2138,7 @@
         <v>138</v>
       </c>
       <c r="B27" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C27">
         <v>408961.4645</v>
@@ -2155,7 +2155,7 @@
         <v>139</v>
       </c>
       <c r="B28" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C28">
         <v>408960.96830000001</v>
@@ -2172,7 +2172,7 @@
         <v>140</v>
       </c>
       <c r="B29" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C29">
         <v>408960.493599999</v>
@@ -2189,7 +2189,7 @@
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C30">
         <v>408926.557299999</v>
@@ -2206,7 +2206,7 @@
         <v>20</v>
       </c>
       <c r="B31" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C31">
         <v>408926.97979999898</v>
@@ -2223,7 +2223,7 @@
         <v>21</v>
       </c>
       <c r="B32" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C32">
         <v>408927.42930000002</v>
@@ -2240,7 +2240,7 @@
         <v>22</v>
       </c>
       <c r="B33" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C33">
         <v>408927.88109999901</v>
@@ -2257,7 +2257,7 @@
         <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C34">
         <v>408928.31640000001</v>
@@ -2274,7 +2274,7 @@
         <v>24</v>
       </c>
       <c r="B35" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C35">
         <v>408928.783999999</v>
@@ -2291,7 +2291,7 @@
         <v>141</v>
       </c>
       <c r="B36" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C36">
         <v>408936.025599999</v>
@@ -2308,7 +2308,7 @@
         <v>142</v>
       </c>
       <c r="B37" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C37">
         <v>408935.529199999</v>
@@ -2325,7 +2325,7 @@
         <v>143</v>
       </c>
       <c r="B38" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C38">
         <v>408935.03840000002</v>
@@ -2342,7 +2342,7 @@
         <v>144</v>
       </c>
       <c r="B39" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C39">
         <v>408934.55099999899</v>
@@ -2359,7 +2359,7 @@
         <v>145</v>
       </c>
       <c r="B40" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C40">
         <v>408934.06530000002</v>
@@ -2376,7 +2376,7 @@
         <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C41">
         <v>408901.33329999901</v>
@@ -2393,7 +2393,7 @@
         <v>26</v>
       </c>
       <c r="B42" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C42">
         <v>408900.9032</v>
@@ -2410,7 +2410,7 @@
         <v>27</v>
       </c>
       <c r="B43" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C43">
         <v>408900.44150000002</v>
@@ -2427,7 +2427,7 @@
         <v>28</v>
       </c>
       <c r="B44" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C44">
         <v>408899.99949999899</v>
@@ -2444,7 +2444,7 @@
         <v>29</v>
       </c>
       <c r="B45" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C45">
         <v>408899.580599999</v>
@@ -2461,7 +2461,7 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C46">
         <v>408899.109999999</v>
@@ -2478,7 +2478,7 @@
         <v>146</v>
       </c>
       <c r="B47" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C47">
         <v>408906.29479999898</v>
@@ -2495,7 +2495,7 @@
         <v>147</v>
       </c>
       <c r="B48" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C48">
         <v>408905.79359999899</v>
@@ -2512,7 +2512,7 @@
         <v>148</v>
       </c>
       <c r="B49" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C49">
         <v>408905.32140000002</v>
@@ -2529,7 +2529,7 @@
         <v>149</v>
       </c>
       <c r="B50" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C50">
         <v>408904.8211</v>
@@ -2546,7 +2546,7 @@
         <v>150</v>
       </c>
       <c r="B51" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C51">
         <v>408904.35749999899</v>
@@ -2563,7 +2563,7 @@
         <v>31</v>
       </c>
       <c r="B52" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C52">
         <v>408870.67979999899</v>
@@ -2580,7 +2580,7 @@
         <v>32</v>
       </c>
       <c r="B53" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C53">
         <v>408871.13660000003</v>
@@ -2597,7 +2597,7 @@
         <v>33</v>
       </c>
       <c r="B54" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C54">
         <v>408871.57900000003</v>
@@ -2614,7 +2614,7 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C55">
         <v>408872.00809999899</v>
@@ -2631,7 +2631,7 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C56">
         <v>408872.451899999</v>
@@ -2648,7 +2648,7 @@
         <v>36</v>
       </c>
       <c r="B57" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C57">
         <v>408872.89059999899</v>
@@ -2665,7 +2665,7 @@
         <v>151</v>
       </c>
       <c r="B58" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C58">
         <v>408879.86940000003</v>
@@ -2682,7 +2682,7 @@
         <v>152</v>
       </c>
       <c r="B59" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C59">
         <v>408879.400499999</v>
@@ -2699,7 +2699,7 @@
         <v>153</v>
       </c>
       <c r="B60" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C60">
         <v>408878.89939999901</v>
@@ -2716,7 +2716,7 @@
         <v>154</v>
       </c>
       <c r="B61" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C61">
         <v>408878.41070000001</v>
@@ -2733,7 +2733,7 @@
         <v>155</v>
       </c>
       <c r="B62" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C62">
         <v>408877.92340000003</v>
@@ -2750,7 +2750,7 @@
         <v>37</v>
       </c>
       <c r="B63" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C63">
         <v>408845.46089999902</v>
@@ -2767,7 +2767,7 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C64">
         <v>408845.02049999899</v>
@@ -2784,7 +2784,7 @@
         <v>39</v>
       </c>
       <c r="B65" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C65">
         <v>408844.56319999899</v>
@@ -2801,7 +2801,7 @@
         <v>40</v>
       </c>
       <c r="B66" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C66">
         <v>408844.13500000001</v>
@@ -2818,7 +2818,7 @@
         <v>41</v>
       </c>
       <c r="B67" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C67">
         <v>408843.68329999998</v>
@@ -2835,7 +2835,7 @@
         <v>42</v>
       </c>
       <c r="B68" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C68">
         <v>408843.26179999899</v>
@@ -2852,7 +2852,7 @@
         <v>156</v>
       </c>
       <c r="B69" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C69">
         <v>408850.18070000003</v>
@@ -2869,7 +2869,7 @@
         <v>157</v>
       </c>
       <c r="B70" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C70">
         <v>408849.70020000002</v>
@@ -2886,7 +2886,7 @@
         <v>158</v>
       </c>
       <c r="B71" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C71">
         <v>408849.219199999</v>
@@ -2903,7 +2903,7 @@
         <v>159</v>
       </c>
       <c r="B72" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C72">
         <v>408848.73200000002</v>
@@ -2920,7 +2920,7 @@
         <v>160</v>
       </c>
       <c r="B73" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C73">
         <v>408848.231299999</v>
@@ -2937,7 +2937,7 @@
         <v>43</v>
       </c>
       <c r="B74" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C74">
         <v>408814.80080000003</v>
@@ -2954,7 +2954,7 @@
         <v>44</v>
       </c>
       <c r="B75" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C75">
         <v>408815.248499999</v>
@@ -2971,7 +2971,7 @@
         <v>45</v>
       </c>
       <c r="B76" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C76">
         <v>408815.666399999</v>
@@ -2988,7 +2988,7 @@
         <v>46</v>
       </c>
       <c r="B77" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C77">
         <v>408816.12689999898</v>
@@ -3005,7 +3005,7 @@
         <v>47</v>
       </c>
       <c r="B78" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C78">
         <v>408816.55469999899</v>
@@ -3022,7 +3022,7 @@
         <v>48</v>
       </c>
       <c r="B79" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C79">
         <v>408817.00829999999</v>
@@ -3039,7 +3039,7 @@
         <v>161</v>
       </c>
       <c r="B80" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C80">
         <v>408823.76260000002</v>
@@ -3056,7 +3056,7 @@
         <v>162</v>
       </c>
       <c r="B81" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C81">
         <v>408823.264399999</v>
@@ -3073,7 +3073,7 @@
         <v>163</v>
       </c>
       <c r="B82" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C82">
         <v>408822.77899999899</v>
@@ -3090,7 +3090,7 @@
         <v>164</v>
       </c>
       <c r="B83" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C83">
         <v>408822.312299999</v>
@@ -3107,7 +3107,7 @@
         <v>165</v>
       </c>
       <c r="B84" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C84">
         <v>408821.829399999</v>
@@ -3124,7 +3124,7 @@
         <v>49</v>
       </c>
       <c r="B85" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C85">
         <v>408788.581799999</v>
@@ -3141,7 +3141,7 @@
         <v>50</v>
       </c>
       <c r="B86" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C86">
         <v>408788.11670000001</v>
@@ -3158,7 +3158,7 @@
         <v>51</v>
       </c>
       <c r="B87" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C87">
         <v>408787.67560000002</v>
@@ -3175,7 +3175,7 @@
         <v>52</v>
       </c>
       <c r="B88" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C88">
         <v>408787.222799999</v>
@@ -3192,7 +3192,7 @@
         <v>53</v>
       </c>
       <c r="B89" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C89">
         <v>408786.80749999901</v>
@@ -3209,7 +3209,7 @@
         <v>54</v>
       </c>
       <c r="B90" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C90">
         <v>408786.36930000002</v>
@@ -3226,7 +3226,7 @@
         <v>166</v>
       </c>
       <c r="B91" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C91">
         <v>408793.35800000001</v>
@@ -3243,7 +3243,7 @@
         <v>167</v>
       </c>
       <c r="B92" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C92">
         <v>408792.866099999</v>
@@ -3260,7 +3260,7 @@
         <v>168</v>
       </c>
       <c r="B93" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C93">
         <v>408792.38530000002</v>
@@ -3277,7 +3277,7 @@
         <v>169</v>
       </c>
       <c r="B94" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C94">
         <v>408791.8947</v>
@@ -3294,7 +3294,7 @@
         <v>170</v>
       </c>
       <c r="B95" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C95">
         <v>408791.43050000002</v>
@@ -3311,7 +3311,7 @@
         <v>55</v>
       </c>
       <c r="B96" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C96">
         <v>408757.90980000002</v>
@@ -3328,7 +3328,7 @@
         <v>56</v>
       </c>
       <c r="B97" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C97">
         <v>408758.367499999</v>
@@ -3345,7 +3345,7 @@
         <v>57</v>
       </c>
       <c r="B98" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C98">
         <v>408758.807399999</v>
@@ -3362,7 +3362,7 @@
         <v>58</v>
       </c>
       <c r="B99" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C99">
         <v>408759.24219999899</v>
@@ -3379,7 +3379,7 @@
         <v>59</v>
       </c>
       <c r="B100" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C100">
         <v>408759.692099999</v>
@@ -3396,7 +3396,7 @@
         <v>60</v>
       </c>
       <c r="B101" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C101">
         <v>408760.11839999899</v>
@@ -3413,7 +3413,7 @@
         <v>171</v>
       </c>
       <c r="B102" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C102">
         <v>408766.92910000001</v>
@@ -3430,7 +3430,7 @@
         <v>172</v>
       </c>
       <c r="B103" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C103">
         <v>408766.46409999899</v>
@@ -3447,7 +3447,7 @@
         <v>173</v>
       </c>
       <c r="B104" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C104">
         <v>408765.99229999899</v>
@@ -3464,7 +3464,7 @@
         <v>174</v>
       </c>
       <c r="B105" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C105">
         <v>408765.47999999899</v>
@@ -3481,7 +3481,7 @@
         <v>175</v>
       </c>
       <c r="B106" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C106">
         <v>408765.01639999897</v>
@@ -3498,7 +3498,7 @@
         <v>61</v>
       </c>
       <c r="B107" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C107">
         <v>408674.80969999899</v>
@@ -3515,7 +3515,7 @@
         <v>62</v>
       </c>
       <c r="B108" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C108">
         <v>408674.3175</v>
@@ -3532,7 +3532,7 @@
         <v>63</v>
       </c>
       <c r="B109" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C109">
         <v>408673.885899999</v>
@@ -3549,7 +3549,7 @@
         <v>64</v>
       </c>
       <c r="B110" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C110">
         <v>408673.42570000002</v>
@@ -3566,7 +3566,7 @@
         <v>65</v>
       </c>
       <c r="B111" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C111">
         <v>408673.00859999901</v>
@@ -3583,7 +3583,7 @@
         <v>66</v>
       </c>
       <c r="B112" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C112">
         <v>408672.59139999899</v>
@@ -3600,7 +3600,7 @@
         <v>176</v>
       </c>
       <c r="B113" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C113">
         <v>408680.68900000001</v>
@@ -3617,7 +3617,7 @@
         <v>177</v>
       </c>
       <c r="B114" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C114">
         <v>408680.20289999899</v>
@@ -3634,7 +3634,7 @@
         <v>178</v>
       </c>
       <c r="B115" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C115">
         <v>408679.7047</v>
@@ -3651,7 +3651,7 @@
         <v>179</v>
       </c>
       <c r="B116" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C116">
         <v>408679.21340000001</v>
@@ -3668,7 +3668,7 @@
         <v>180</v>
       </c>
       <c r="B117" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C117">
         <v>408678.73639999999</v>
@@ -3698,13 +3698,13 @@
         <v>122</v>
       </c>
       <c r="B1" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D1" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E1" t="s">
         <v>134</v>
@@ -3715,7 +3715,7 @@
         <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C2">
         <v>409014.52750000003</v>
@@ -3732,7 +3732,7 @@
         <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C3">
         <v>409016.286599999</v>
@@ -3749,7 +3749,7 @@
         <v>151</v>
       </c>
       <c r="B4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C4">
         <v>409015.53</v>
@@ -3766,7 +3766,7 @@
         <v>152</v>
       </c>
       <c r="B5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C5">
         <v>409014.96</v>
@@ -3783,7 +3783,7 @@
         <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C6">
         <v>409000.4903</v>
@@ -3800,7 +3800,7 @@
         <v>71</v>
       </c>
       <c r="B7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C7">
         <v>408997.63040000002</v>
@@ -3817,7 +3817,7 @@
         <v>72</v>
       </c>
       <c r="B8" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C8">
         <v>408987.19380000001</v>
@@ -3834,7 +3834,7 @@
         <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C9">
         <v>408982.38959999901</v>
@@ -3851,7 +3851,7 @@
         <v>146</v>
       </c>
       <c r="B10" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C10">
         <v>408985.71999999898</v>
@@ -3868,7 +3868,7 @@
         <v>147</v>
       </c>
       <c r="B11" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C11">
         <v>408984.80999999901</v>
@@ -3885,7 +3885,7 @@
         <v>148</v>
       </c>
       <c r="B12" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C12">
         <v>408983.89</v>
@@ -3902,7 +3902,7 @@
         <v>149</v>
       </c>
       <c r="B13" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C13">
         <v>409002.11999999901</v>
@@ -3919,7 +3919,7 @@
         <v>150</v>
       </c>
       <c r="B14" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C14">
         <v>409003.26</v>
@@ -3936,7 +3936,7 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C15">
         <v>408957.29330000002</v>
@@ -3953,7 +3953,7 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C16">
         <v>408956.69130000001</v>
@@ -3970,7 +3970,7 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C17">
         <v>408956.084399999</v>
@@ -3987,7 +3987,7 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C18">
         <v>408955.49589999899</v>
@@ -4004,7 +4004,7 @@
         <v>74</v>
       </c>
       <c r="B19" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C19">
         <v>408973.7121</v>
@@ -4021,7 +4021,7 @@
         <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C20">
         <v>408968.074599999</v>
@@ -4038,7 +4038,7 @@
         <v>84</v>
       </c>
       <c r="B21" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C21">
         <v>408961.65999999898</v>
@@ -4055,7 +4055,7 @@
         <v>144</v>
       </c>
       <c r="B22" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C22">
         <v>408961.76</v>
@@ -4072,7 +4072,7 @@
         <v>145</v>
       </c>
       <c r="B23" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C23">
         <v>408963.02</v>
@@ -4089,7 +4089,7 @@
         <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C24">
         <v>408943.05879999901</v>
@@ -4106,7 +4106,7 @@
         <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C25">
         <v>408942.48519999901</v>
@@ -4123,7 +4123,7 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C26">
         <v>408941.846599999</v>
@@ -4140,7 +4140,7 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C27">
         <v>408941.274299999</v>
@@ -4157,7 +4157,7 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C28">
         <v>408928.85560000001</v>
@@ -4174,7 +4174,7 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C29">
         <v>408928.25300000003</v>
@@ -4191,7 +4191,7 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C30">
         <v>408927.64370000002</v>
@@ -4208,7 +4208,7 @@
         <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C31">
         <v>408927.035299999</v>
@@ -4225,7 +4225,7 @@
         <v>85</v>
       </c>
       <c r="B32" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C32">
         <v>408933.28</v>
@@ -4242,7 +4242,7 @@
         <v>140</v>
       </c>
       <c r="B33" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C33">
         <v>408933.33</v>
@@ -4259,7 +4259,7 @@
         <v>141</v>
       </c>
       <c r="B34" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C34">
         <v>408934.59</v>
@@ -4276,7 +4276,7 @@
         <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C35">
         <v>408914.35340000002</v>
@@ -4293,7 +4293,7 @@
         <v>14</v>
       </c>
       <c r="B36" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C36">
         <v>408913.7599</v>
@@ -4310,7 +4310,7 @@
         <v>15</v>
       </c>
       <c r="B37" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C37">
         <v>408913.14380000002</v>
@@ -4327,7 +4327,7 @@
         <v>16</v>
       </c>
       <c r="B38" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C38">
         <v>408912.52870000002</v>
@@ -4344,7 +4344,7 @@
         <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C39">
         <v>408904.549999999</v>
@@ -4361,7 +4361,7 @@
         <v>138</v>
       </c>
       <c r="B40" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C40">
         <v>408906.5</v>
@@ -4378,7 +4378,7 @@
         <v>139</v>
       </c>
       <c r="B41" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C41">
         <v>408905.239999999</v>
@@ -4395,7 +4395,7 @@
         <v>153</v>
       </c>
       <c r="B42" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C42">
         <v>408900.20380000002</v>
@@ -4412,7 +4412,7 @@
         <v>154</v>
       </c>
       <c r="B43" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C43">
         <v>408899.61949999898</v>
@@ -4429,7 +4429,7 @@
         <v>155</v>
       </c>
       <c r="B44" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C44">
         <v>408899.00260000001</v>
@@ -4446,7 +4446,7 @@
         <v>156</v>
       </c>
       <c r="B45" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C45">
         <v>408898.37829999899</v>
@@ -4463,7 +4463,7 @@
         <v>87</v>
       </c>
       <c r="B46" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C46">
         <v>408877.08</v>
@@ -4480,7 +4480,7 @@
         <v>134</v>
       </c>
       <c r="B47" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C47">
         <v>408879.09999999899</v>
@@ -4497,7 +4497,7 @@
         <v>135</v>
       </c>
       <c r="B48" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C48">
         <v>408877.859999999</v>
@@ -4514,7 +4514,7 @@
         <v>157</v>
       </c>
       <c r="B49" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C49">
         <v>408885.99040000001</v>
@@ -4531,7 +4531,7 @@
         <v>158</v>
       </c>
       <c r="B50" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C50">
         <v>408885.37439999898</v>
@@ -4548,7 +4548,7 @@
         <v>159</v>
       </c>
       <c r="B51" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C51">
         <v>408884.80279999902</v>
@@ -4565,7 +4565,7 @@
         <v>160</v>
       </c>
       <c r="B52" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C52">
         <v>408884.17149999901</v>
@@ -4582,7 +4582,7 @@
         <v>17</v>
       </c>
       <c r="B53" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C53">
         <v>408859.25290000002</v>
@@ -4599,7 +4599,7 @@
         <v>18</v>
       </c>
       <c r="B54" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C54">
         <v>408858.64659999899</v>
@@ -4616,7 +4616,7 @@
         <v>19</v>
       </c>
       <c r="B55" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C55">
         <v>408858.0344</v>
@@ -4633,7 +4633,7 @@
         <v>20</v>
       </c>
       <c r="B56" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C56">
         <v>408857.44079999899</v>
@@ -4650,7 +4650,7 @@
         <v>21</v>
       </c>
       <c r="B57" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C57">
         <v>408845.03460000001</v>
@@ -4667,7 +4667,7 @@
         <v>22</v>
       </c>
       <c r="B58" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C58">
         <v>408844.4375</v>
@@ -4684,7 +4684,7 @@
         <v>23</v>
       </c>
       <c r="B59" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C59">
         <v>408843.829399999</v>
@@ -4701,7 +4701,7 @@
         <v>24</v>
       </c>
       <c r="B60" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C60">
         <v>408843.20490000001</v>
@@ -4718,7 +4718,7 @@
         <v>88</v>
       </c>
       <c r="B61" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C61">
         <v>408849.53</v>
@@ -4735,7 +4735,7 @@
         <v>132</v>
       </c>
       <c r="B62" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C62">
         <v>408849.489999999</v>
@@ -4752,7 +4752,7 @@
         <v>133</v>
       </c>
       <c r="B63" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C63">
         <v>408850.72999999899</v>
@@ -4769,7 +4769,7 @@
         <v>25</v>
       </c>
       <c r="B64" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C64">
         <v>408830.81489999901</v>
@@ -4786,7 +4786,7 @@
         <v>26</v>
       </c>
       <c r="B65" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C65">
         <v>408830.206899999</v>
@@ -4803,7 +4803,7 @@
         <v>27</v>
       </c>
       <c r="B66" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C66">
         <v>408829.59519999899</v>
@@ -4820,7 +4820,7 @@
         <v>28</v>
       </c>
       <c r="B67" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C67">
         <v>408828.99920000002</v>
@@ -4837,7 +4837,7 @@
         <v>29</v>
       </c>
       <c r="B68" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C68">
         <v>408816.59179999901</v>
@@ -4854,7 +4854,7 @@
         <v>30</v>
       </c>
       <c r="B69" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C69">
         <v>408815.986199999</v>
@@ -4871,7 +4871,7 @@
         <v>31</v>
       </c>
       <c r="B70" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C70">
         <v>408815.39</v>
@@ -4888,7 +4888,7 @@
         <v>32</v>
       </c>
       <c r="B71" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C71">
         <v>408814.777</v>
@@ -4905,7 +4905,7 @@
         <v>89</v>
       </c>
       <c r="B72" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C72">
         <v>408821.01</v>
@@ -4922,7 +4922,7 @@
         <v>128</v>
       </c>
       <c r="B73" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C73">
         <v>408821.109999999</v>
@@ -4939,7 +4939,7 @@
         <v>129</v>
       </c>
       <c r="B74" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C74">
         <v>408822.35</v>
@@ -4956,7 +4956,7 @@
         <v>33</v>
       </c>
       <c r="B75" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C75">
         <v>408802.449499999</v>
@@ -4973,7 +4973,7 @@
         <v>34</v>
       </c>
       <c r="B76" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C76">
         <v>408801.83819999901</v>
@@ -4990,7 +4990,7 @@
         <v>35</v>
       </c>
       <c r="B77" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C77">
         <v>408801.21379999898</v>
@@ -5007,7 +5007,7 @@
         <v>36</v>
       </c>
       <c r="B78" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C78">
         <v>408800.62819999899</v>
@@ -5024,7 +5024,7 @@
         <v>37</v>
       </c>
       <c r="B79" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C79">
         <v>408788.22350000002</v>
@@ -5041,7 +5041,7 @@
         <v>38</v>
       </c>
       <c r="B80" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C80">
         <v>408787.60700000002</v>
@@ -5058,7 +5058,7 @@
         <v>39</v>
       </c>
       <c r="B81" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C81">
         <v>408787.00040000002</v>
@@ -5075,7 +5075,7 @@
         <v>40</v>
       </c>
       <c r="B82" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C82">
         <v>408786.40159999899</v>
@@ -5092,7 +5092,7 @@
         <v>90</v>
       </c>
       <c r="B83" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C83">
         <v>408792.64</v>
@@ -5109,7 +5109,7 @@
         <v>126</v>
       </c>
       <c r="B84" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C84">
         <v>408794.59</v>
@@ -5126,7 +5126,7 @@
         <v>127</v>
       </c>
       <c r="B85" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C85">
         <v>408793.34999999899</v>
@@ -5143,7 +5143,7 @@
         <v>41</v>
       </c>
       <c r="B86" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C86">
         <v>408773.99790000002</v>
@@ -5160,7 +5160,7 @@
         <v>42</v>
       </c>
       <c r="B87" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C87">
         <v>408773.39649999898</v>
@@ -5177,7 +5177,7 @@
         <v>43</v>
       </c>
       <c r="B88" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C88">
         <v>408772.784099999</v>
@@ -5194,7 +5194,7 @@
         <v>44</v>
       </c>
       <c r="B89" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C89">
         <v>408772.17050000001</v>
@@ -5211,7 +5211,7 @@
         <v>45</v>
       </c>
       <c r="B90" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C90">
         <v>408759.7758</v>
@@ -5228,7 +5228,7 @@
         <v>46</v>
       </c>
       <c r="B91" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C91">
         <v>408759.1692</v>
@@ -5245,7 +5245,7 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C92">
         <v>408758.57179999899</v>
@@ -5262,7 +5262,7 @@
         <v>48</v>
       </c>
       <c r="B93" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C93">
         <v>408757.959299999</v>
@@ -5279,7 +5279,7 @@
         <v>91</v>
       </c>
       <c r="B94" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C94">
         <v>408764.2</v>
@@ -5296,7 +5296,7 @@
         <v>122</v>
       </c>
       <c r="B95" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C95">
         <v>408766.09</v>
@@ -5313,7 +5313,7 @@
         <v>123</v>
       </c>
       <c r="B96" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C96">
         <v>408764.84999999899</v>
@@ -5330,7 +5330,7 @@
         <v>67</v>
       </c>
       <c r="B97" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C97">
         <v>408685.49530000001</v>
@@ -5347,7 +5347,7 @@
         <v>68</v>
       </c>
       <c r="B98" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C98">
         <v>408676.1875</v>
@@ -5364,7 +5364,7 @@
         <v>70</v>
       </c>
       <c r="B99" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C99">
         <v>408673.02689999901</v>
@@ -5381,7 +5381,7 @@
         <v>94</v>
       </c>
       <c r="B100" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C100">
         <v>408678.94</v>
@@ -5398,7 +5398,7 @@
         <v>113</v>
       </c>
       <c r="B101" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C101">
         <v>408680.549999999</v>
@@ -5415,7 +5415,7 @@
         <v>114</v>
       </c>
       <c r="B102" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C102">
         <v>408679.679999999</v>
@@ -5432,7 +5432,7 @@
         <v>115</v>
       </c>
       <c r="B103" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C103">
         <v>408678.72999999899</v>
@@ -5462,211 +5462,211 @@
         <v>121</v>
       </c>
       <c r="C1" t="s">
+        <v>424</v>
+      </c>
+      <c r="D1" t="s">
         <v>135</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>136</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>137</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>138</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>139</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>140</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>141</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>142</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>143</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>144</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>145</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>146</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>147</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>148</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>149</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>150</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>151</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>152</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>153</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>154</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>155</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>156</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>157</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>158</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>159</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>160</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>161</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>162</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>163</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>164</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>165</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>166</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>167</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>168</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>169</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>170</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>171</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>172</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>173</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>174</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>175</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>176</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>177</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>178</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>179</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>180</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>181</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>182</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>183</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>184</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>185</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>186</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>187</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>188</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>189</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>190</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>191</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>192</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>193</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>194</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>195</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>196</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>197</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>198</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>199</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>200</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>201</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>202</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">
@@ -29887,211 +29887,211 @@
         <v>134</v>
       </c>
       <c r="C1" t="s">
+        <v>424</v>
+      </c>
+      <c r="D1" t="s">
         <v>135</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>136</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>137</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>138</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>139</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>140</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>141</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>142</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>143</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>144</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>145</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>146</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>147</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>148</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>149</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>150</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>151</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>152</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>153</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>154</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>155</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>156</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>157</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>158</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>159</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>160</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>161</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>162</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>163</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>164</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>165</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>166</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>167</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>168</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>169</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>170</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>171</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>172</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>173</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>174</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>175</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>176</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>177</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>178</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>179</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>180</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>181</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>182</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>183</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>184</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>185</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>186</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>187</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>188</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>189</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BG1" t="s">
         <v>190</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>191</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>192</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>193</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>194</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>195</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>196</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>197</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>198</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>199</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>200</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>201</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
         <v>202</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">
@@ -32438,15 +32438,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001E2F74E811AAA4409A164A292B7ABC74" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a274884ad72c80bb9b486423286f1f97">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="728ae82c-3d1b-45f0-8d67-959bce25b5b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0920719d7b65f5660acd9896835e0dd0" ns3:_="">
     <xsd:import namespace="728ae82c-3d1b-45f0-8d67-959bce25b5b0"/>
@@ -32596,6 +32587,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9EAE9DF-01E1-49E5-8603-E69C76183A40}">
   <ds:schemaRefs>
@@ -32613,14 +32613,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FABF7966-B5A2-43B3-86A8-0DA6CE927C7F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45043DEE-C555-410D-B3FE-BB9490E0CF46}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -32636,4 +32628,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FABF7966-B5A2-43B3-86A8-0DA6CE927C7F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Data/2014_F013B4_CO_ISOS/2014_F013B4_CO_ISOS_SoilAnalysis.xlsx
+++ b/Data/2014_F013B4_CO_ISOS/2014_F013B4_CO_ISOS_SoilAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2014_F013B4_CO_ISOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5501E6ED-F02F-4BB7-B48A-5982009108EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9758605B-4105-44E7-9C86-7E0C88ACA3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1665" yWindow="-25290" windowWidth="27270" windowHeight="17295" xr2:uid="{8C00C1F2-89F9-4A44-A266-AB1BCF5C18BB}"/>
+    <workbookView xWindow="-1425" yWindow="-24390" windowWidth="17775" windowHeight="24285" xr2:uid="{8C00C1F2-89F9-4A44-A266-AB1BCF5C18BB}"/>
   </bookViews>
   <sheets>
     <sheet name="SoilDJH" sheetId="4" r:id="rId1"/>
@@ -6848,58 +6848,58 @@
         <v>24.005870000000002</v>
       </c>
       <c r="X13">
-        <v>9.7547999999999996E-2</v>
+        <v>0.15607699999999999</v>
       </c>
       <c r="Y13">
-        <v>0.109148</v>
+        <v>0.174652</v>
       </c>
       <c r="Z13">
-        <v>0.12523000000000001</v>
+        <v>0.20036799999999999</v>
       </c>
       <c r="AA13">
-        <v>0.112215</v>
+        <v>0.17954400000000001</v>
       </c>
       <c r="AB13">
-        <v>9.2175999999999994E-2</v>
+        <v>0.147481</v>
       </c>
       <c r="AC13">
-        <v>7.9911999999999997E-2</v>
+        <v>0.12785299999999999</v>
       </c>
       <c r="AD13">
-        <v>0.10778600000000001</v>
+        <v>0.172458</v>
       </c>
       <c r="AE13">
-        <v>0.120409</v>
+        <v>0.19265399999999999</v>
       </c>
       <c r="AF13">
-        <v>0.134048</v>
+        <v>0.214477</v>
       </c>
       <c r="AG13">
-        <v>0.126004</v>
+        <v>0.20160700000000001</v>
       </c>
       <c r="AH13">
-        <v>0.10698199999999999</v>
+        <v>0.17089499999999999</v>
       </c>
       <c r="AI13">
-        <v>9.1370000000000007E-2</v>
+        <v>0.14722399999999999</v>
       </c>
       <c r="AJ13">
-        <v>0.17502999999999999</v>
+        <v>0.28004699999999999</v>
       </c>
       <c r="AK13">
-        <v>0.187169</v>
+        <v>0.29947000000000001</v>
       </c>
       <c r="AL13">
-        <v>0.206764</v>
+        <v>0.32244699999999998</v>
       </c>
       <c r="AM13">
-        <v>0.201157</v>
+        <v>0.31440899999999999</v>
       </c>
       <c r="AN13">
-        <v>0.17346300000000001</v>
+        <v>0.27857500000000002</v>
       </c>
       <c r="AO13">
-        <v>0.16167200000000001</v>
+        <v>0.26617800000000003</v>
       </c>
       <c r="AP13">
         <v>57.787498999999997</v>
@@ -7060,58 +7060,58 @@
         <v>23.682977999999999</v>
       </c>
       <c r="X14">
-        <v>9.9849999999999994E-2</v>
+        <v>0.15976099999999999</v>
       </c>
       <c r="Y14">
-        <v>0.11158</v>
+        <v>0.17677999999999999</v>
       </c>
       <c r="Z14">
-        <v>0.12442599999999999</v>
+        <v>0.19908200000000001</v>
       </c>
       <c r="AA14">
-        <v>0.114344</v>
+        <v>0.182951</v>
       </c>
       <c r="AB14">
-        <v>9.4672000000000006E-2</v>
+        <v>0.151475</v>
       </c>
       <c r="AC14">
-        <v>8.1865999999999994E-2</v>
+        <v>0.13098000000000001</v>
       </c>
       <c r="AD14">
-        <v>0.10943</v>
+        <v>0.17508899999999999</v>
       </c>
       <c r="AE14">
-        <v>0.12063599999999999</v>
+        <v>0.19301699999999999</v>
       </c>
       <c r="AF14">
-        <v>0.13256899999999999</v>
+        <v>0.21211099999999999</v>
       </c>
       <c r="AG14">
-        <v>0.124959</v>
+        <v>0.199935</v>
       </c>
       <c r="AH14">
-        <v>0.105657</v>
+        <v>0.16903399999999999</v>
       </c>
       <c r="AI14">
-        <v>9.1082999999999997E-2</v>
+        <v>0.14666999999999999</v>
       </c>
       <c r="AJ14">
-        <v>0.17566300000000001</v>
+        <v>0.28106100000000001</v>
       </c>
       <c r="AK14">
-        <v>0.18792800000000001</v>
+        <v>0.30068499999999998</v>
       </c>
       <c r="AL14">
-        <v>0.205067</v>
+        <v>0.32048599999999999</v>
       </c>
       <c r="AM14">
-        <v>0.19897000000000001</v>
+        <v>0.31213600000000002</v>
       </c>
       <c r="AN14">
-        <v>0.172897</v>
+        <v>0.27720499999999998</v>
       </c>
       <c r="AO14">
-        <v>0.15973699999999999</v>
+        <v>0.26388600000000001</v>
       </c>
       <c r="AP14">
         <v>57.929814</v>
@@ -7272,58 +7272,58 @@
         <v>23.515084999999999</v>
       </c>
       <c r="X15">
-        <v>0.101836</v>
+        <v>0.162937</v>
       </c>
       <c r="Y15">
-        <v>0.11333799999999999</v>
+        <v>0.17789099999999999</v>
       </c>
       <c r="Z15">
-        <v>0.11715200000000001</v>
+        <v>0.187443</v>
       </c>
       <c r="AA15">
-        <v>0.113996</v>
+        <v>0.182394</v>
       </c>
       <c r="AB15">
-        <v>9.9099000000000007E-2</v>
+        <v>0.15855900000000001</v>
       </c>
       <c r="AC15">
-        <v>8.6423E-2</v>
+        <v>0.13827400000000001</v>
       </c>
       <c r="AD15">
-        <v>0.111026</v>
+        <v>0.17764099999999999</v>
       </c>
       <c r="AE15">
-        <v>0.120088</v>
+        <v>0.19214100000000001</v>
       </c>
       <c r="AF15">
-        <v>0.12645999999999999</v>
+        <v>0.20233499999999999</v>
       </c>
       <c r="AG15">
-        <v>0.122887</v>
+        <v>0.19661899999999999</v>
       </c>
       <c r="AH15">
-        <v>0.103676</v>
+        <v>0.16616300000000001</v>
       </c>
       <c r="AI15">
-        <v>9.1374999999999998E-2</v>
+        <v>0.146952</v>
       </c>
       <c r="AJ15">
-        <v>0.17965900000000001</v>
+        <v>0.28745399999999999</v>
       </c>
       <c r="AK15">
-        <v>0.187143</v>
+        <v>0.29942800000000003</v>
       </c>
       <c r="AL15">
-        <v>0.197076</v>
+        <v>0.31145800000000001</v>
       </c>
       <c r="AM15">
-        <v>0.19422</v>
+        <v>0.30690699999999999</v>
       </c>
       <c r="AN15">
-        <v>0.17039699999999999</v>
+        <v>0.27390500000000001</v>
       </c>
       <c r="AO15">
-        <v>0.157914</v>
+        <v>0.26186700000000002</v>
       </c>
       <c r="AP15">
         <v>57.735405</v>
@@ -7427,7 +7427,7 @@
         <v>44.333333000000003</v>
       </c>
       <c r="F16">
-        <v>56.733507000000003</v>
+        <v>56.733505999999998</v>
       </c>
       <c r="G16">
         <v>57.340744000000001</v>
@@ -7481,58 +7481,58 @@
         <v>23.295596</v>
       </c>
       <c r="X16">
-        <v>0.103864</v>
+        <v>0.166182</v>
       </c>
       <c r="Y16">
-        <v>0.111114</v>
+        <v>0.175346</v>
       </c>
       <c r="Z16">
-        <v>0.11100400000000001</v>
+        <v>0.17760600000000001</v>
       </c>
       <c r="AA16">
-        <v>0.117938</v>
+        <v>0.18870100000000001</v>
       </c>
       <c r="AB16">
-        <v>0.10098799999999999</v>
+        <v>0.161581</v>
       </c>
       <c r="AC16">
-        <v>9.0923000000000004E-2</v>
+        <v>0.145479</v>
       </c>
       <c r="AD16">
-        <v>0.112571</v>
+        <v>0.180113</v>
       </c>
       <c r="AE16">
-        <v>0.115728</v>
+        <v>0.185166</v>
       </c>
       <c r="AF16">
-        <v>0.11766</v>
+        <v>0.18825600000000001</v>
       </c>
       <c r="AG16">
-        <v>0.12032900000000001</v>
+        <v>0.192526</v>
       </c>
       <c r="AH16">
-        <v>0.100802</v>
+        <v>0.16198599999999999</v>
       </c>
       <c r="AI16">
-        <v>9.1273000000000007E-2</v>
+        <v>0.146816</v>
       </c>
       <c r="AJ16">
-        <v>0.18557000000000001</v>
+        <v>0.29691099999999998</v>
       </c>
       <c r="AK16">
-        <v>0.18429400000000001</v>
+        <v>0.29487000000000002</v>
       </c>
       <c r="AL16">
-        <v>0.187773</v>
+        <v>0.301431</v>
       </c>
       <c r="AM16">
-        <v>0.193638</v>
+        <v>0.30580299999999999</v>
       </c>
       <c r="AN16">
-        <v>0.167769</v>
+        <v>0.26991999999999999</v>
       </c>
       <c r="AO16">
-        <v>0.15767200000000001</v>
+        <v>0.26171499999999998</v>
       </c>
       <c r="AP16">
         <v>56.991723999999998</v>
@@ -7690,58 +7690,58 @@
         <v>22.77281</v>
       </c>
       <c r="X17">
-        <v>0.10574</v>
+        <v>0.169185</v>
       </c>
       <c r="Y17">
-        <v>0.111148</v>
+        <v>0.17261099999999999</v>
       </c>
       <c r="Z17">
-        <v>0.112543</v>
+        <v>0.18006900000000001</v>
       </c>
       <c r="AA17">
-        <v>0.10901</v>
+        <v>0.17441499999999999</v>
       </c>
       <c r="AB17">
-        <v>9.7862000000000005E-2</v>
+        <v>0.15658</v>
       </c>
       <c r="AC17">
-        <v>8.7280999999999997E-2</v>
+        <v>0.13964799999999999</v>
       </c>
       <c r="AD17">
-        <v>0.114732</v>
+        <v>0.18357100000000001</v>
       </c>
       <c r="AE17">
-        <v>0.11276700000000001</v>
+        <v>0.180427</v>
       </c>
       <c r="AF17">
-        <v>0.11641700000000001</v>
+        <v>0.18626799999999999</v>
       </c>
       <c r="AG17">
-        <v>0.116302</v>
+        <v>0.186083</v>
       </c>
       <c r="AH17">
-        <v>9.7948999999999994E-2</v>
+        <v>0.15782199999999999</v>
       </c>
       <c r="AI17">
-        <v>9.1624999999999998E-2</v>
+        <v>0.14748800000000001</v>
       </c>
       <c r="AJ17">
-        <v>0.18426899999999999</v>
+        <v>0.29483100000000001</v>
       </c>
       <c r="AK17">
-        <v>0.18353</v>
+        <v>0.29364800000000002</v>
       </c>
       <c r="AL17">
-        <v>0.19259100000000001</v>
+        <v>0.30556100000000003</v>
       </c>
       <c r="AM17">
-        <v>0.19069</v>
+        <v>0.30158699999999999</v>
       </c>
       <c r="AN17">
-        <v>0.16728999999999999</v>
+        <v>0.26743400000000001</v>
       </c>
       <c r="AO17">
-        <v>0.15871099999999999</v>
+        <v>0.26345299999999999</v>
       </c>
       <c r="AP17">
         <v>56.682724999999998</v>
@@ -7899,58 +7899,58 @@
         <v>22.269383999999999</v>
       </c>
       <c r="X18">
-        <v>0.104472</v>
+        <v>0.167156</v>
       </c>
       <c r="Y18">
-        <v>9.9465999999999999E-2</v>
+        <v>0.162767</v>
       </c>
       <c r="Z18">
-        <v>0.110849</v>
+        <v>0.17735899999999999</v>
       </c>
       <c r="AA18">
-        <v>0.106652</v>
+        <v>0.17064399999999999</v>
       </c>
       <c r="AB18">
-        <v>9.6847000000000003E-2</v>
+        <v>0.15495400000000001</v>
       </c>
       <c r="AC18">
-        <v>8.8553999999999994E-2</v>
+        <v>0.14168700000000001</v>
       </c>
       <c r="AD18">
-        <v>0.111497</v>
+        <v>0.178396</v>
       </c>
       <c r="AE18">
-        <v>0.105655</v>
+        <v>0.169048</v>
       </c>
       <c r="AF18">
-        <v>0.11450399999999999</v>
+        <v>0.18320600000000001</v>
       </c>
       <c r="AG18">
-        <v>0.11347400000000001</v>
+        <v>0.181559</v>
       </c>
       <c r="AH18">
-        <v>9.536E-2</v>
+        <v>0.15403500000000001</v>
       </c>
       <c r="AI18">
-        <v>9.3917E-2</v>
+        <v>0.15096200000000001</v>
       </c>
       <c r="AJ18">
-        <v>0.18054700000000001</v>
+        <v>0.28887600000000002</v>
       </c>
       <c r="AK18">
-        <v>0.17292299999999999</v>
+        <v>0.27667700000000001</v>
       </c>
       <c r="AL18">
-        <v>0.188443</v>
+        <v>0.30088700000000002</v>
       </c>
       <c r="AM18">
-        <v>0.18004300000000001</v>
+        <v>0.289877</v>
       </c>
       <c r="AN18">
-        <v>0.161352</v>
+        <v>0.26072600000000001</v>
       </c>
       <c r="AO18">
-        <v>0.16334499999999999</v>
+        <v>0.268787</v>
       </c>
       <c r="AP18">
         <v>57.034219</v>
@@ -8108,58 +8108,58 @@
         <v>22.168112000000001</v>
       </c>
       <c r="X19">
-        <v>0.104384</v>
+        <v>0.167014</v>
       </c>
       <c r="Y19">
-        <v>9.5860000000000001E-2</v>
+        <v>0.16048200000000001</v>
       </c>
       <c r="Z19">
-        <v>0.10888</v>
+        <v>0.174208</v>
       </c>
       <c r="AA19">
-        <v>9.8775000000000002E-2</v>
+        <v>0.15804000000000001</v>
       </c>
       <c r="AB19">
-        <v>8.8958999999999996E-2</v>
+        <v>0.14233399999999999</v>
       </c>
       <c r="AC19">
-        <v>8.4974999999999995E-2</v>
+        <v>0.13595499999999999</v>
       </c>
       <c r="AD19">
-        <v>0.109704</v>
+        <v>0.17552599999999999</v>
       </c>
       <c r="AE19">
-        <v>0.10401100000000001</v>
+        <v>0.16641700000000001</v>
       </c>
       <c r="AF19">
-        <v>0.11308799999999999</v>
+        <v>0.18094099999999999</v>
       </c>
       <c r="AG19">
-        <v>0.105919</v>
+        <v>0.16947000000000001</v>
       </c>
       <c r="AH19">
-        <v>9.2271000000000006E-2</v>
+        <v>0.14970900000000001</v>
       </c>
       <c r="AI19">
-        <v>9.7495999999999999E-2</v>
+        <v>0.156362</v>
       </c>
       <c r="AJ19">
-        <v>0.17796100000000001</v>
+        <v>0.28473700000000002</v>
       </c>
       <c r="AK19">
-        <v>0.16622200000000001</v>
+        <v>0.265955</v>
       </c>
       <c r="AL19">
-        <v>0.18637500000000001</v>
+        <v>0.29806100000000002</v>
       </c>
       <c r="AM19">
-        <v>0.174119</v>
+        <v>0.28288400000000002</v>
       </c>
       <c r="AN19">
-        <v>0.15276100000000001</v>
+        <v>0.25272699999999998</v>
       </c>
       <c r="AO19">
-        <v>0.17022000000000001</v>
+        <v>0.27658300000000002</v>
       </c>
       <c r="AP19">
         <v>57.281899000000003</v>
@@ -8317,58 +8317,58 @@
         <v>22.409489000000001</v>
       </c>
       <c r="X20">
-        <v>0.10561</v>
+        <v>0.16897699999999999</v>
       </c>
       <c r="Y20">
-        <v>9.9137000000000003E-2</v>
+        <v>0.166823</v>
       </c>
       <c r="Z20">
-        <v>0.104879</v>
+        <v>0.16780600000000001</v>
       </c>
       <c r="AA20">
-        <v>9.7837999999999994E-2</v>
+        <v>0.15654000000000001</v>
       </c>
       <c r="AB20">
-        <v>8.2311999999999996E-2</v>
+        <v>0.13170000000000001</v>
       </c>
       <c r="AC20">
-        <v>8.3400000000000002E-2</v>
+        <v>0.133433</v>
       </c>
       <c r="AD20">
-        <v>0.108818</v>
+        <v>0.17410900000000001</v>
       </c>
       <c r="AE20">
-        <v>0.10703</v>
+        <v>0.17124900000000001</v>
       </c>
       <c r="AF20">
-        <v>0.109537</v>
+        <v>0.175259</v>
       </c>
       <c r="AG20">
-        <v>0.10360900000000001</v>
+        <v>0.165774</v>
       </c>
       <c r="AH20">
-        <v>9.1048000000000004E-2</v>
+        <v>0.14799100000000001</v>
       </c>
       <c r="AI20">
-        <v>0.100193</v>
+        <v>0.16070000000000001</v>
       </c>
       <c r="AJ20">
-        <v>0.17700399999999999</v>
+        <v>0.28320600000000001</v>
       </c>
       <c r="AK20">
-        <v>0.16886599999999999</v>
+        <v>0.27018599999999998</v>
       </c>
       <c r="AL20">
-        <v>0.17777599999999999</v>
+        <v>0.28894399999999998</v>
       </c>
       <c r="AM20">
-        <v>0.16772200000000001</v>
+        <v>0.27585500000000002</v>
       </c>
       <c r="AN20">
-        <v>0.14919399999999999</v>
+        <v>0.249755</v>
       </c>
       <c r="AO20">
-        <v>0.17979400000000001</v>
+        <v>0.28684900000000002</v>
       </c>
       <c r="AP20">
         <v>57.328440999999998</v>
@@ -8526,58 +8526,58 @@
         <v>23.368158999999999</v>
       </c>
       <c r="X21">
-        <v>0.10684399999999999</v>
+        <v>0.17095099999999999</v>
       </c>
       <c r="Y21">
-        <v>0.118463</v>
+        <v>0.18589</v>
       </c>
       <c r="Z21">
-        <v>0.10850600000000001</v>
+        <v>0.17360999999999999</v>
       </c>
       <c r="AA21">
-        <v>9.8548999999999998E-2</v>
+        <v>0.15767800000000001</v>
       </c>
       <c r="AB21">
-        <v>8.8875999999999997E-2</v>
+        <v>0.142202</v>
       </c>
       <c r="AC21">
-        <v>9.1478000000000004E-2</v>
+        <v>0.146365</v>
       </c>
       <c r="AD21">
-        <v>0.109335</v>
+        <v>0.17493600000000001</v>
       </c>
       <c r="AE21">
-        <v>0.120432</v>
+        <v>0.192691</v>
       </c>
       <c r="AF21">
-        <v>0.11544699999999999</v>
+        <v>0.18471399999999999</v>
       </c>
       <c r="AG21">
-        <v>0.104925</v>
+        <v>0.16788</v>
       </c>
       <c r="AH21">
-        <v>9.4492999999999994E-2</v>
+        <v>0.152778</v>
       </c>
       <c r="AI21">
-        <v>0.105465</v>
+        <v>0.16852300000000001</v>
       </c>
       <c r="AJ21">
-        <v>0.17952599999999999</v>
+        <v>0.287242</v>
       </c>
       <c r="AK21">
-        <v>0.190723</v>
+        <v>0.30515700000000001</v>
       </c>
       <c r="AL21">
-        <v>0.18418000000000001</v>
+        <v>0.29593799999999998</v>
       </c>
       <c r="AM21">
-        <v>0.17244000000000001</v>
+        <v>0.280914</v>
       </c>
       <c r="AN21">
-        <v>0.157805</v>
+        <v>0.25761000000000001</v>
       </c>
       <c r="AO21">
-        <v>0.189496</v>
+        <v>0.29704900000000001</v>
       </c>
       <c r="AP21">
         <v>57.291612000000001</v>
@@ -8735,58 +8735,58 @@
         <v>24.341812000000001</v>
       </c>
       <c r="X22">
-        <v>0.10732700000000001</v>
+        <v>0.17172499999999999</v>
       </c>
       <c r="Y22">
-        <v>0.13461600000000001</v>
+        <v>0.20230999999999999</v>
       </c>
       <c r="Z22">
-        <v>0.12044299999999999</v>
+        <v>0.19270899999999999</v>
       </c>
       <c r="AA22">
-        <v>0.10415099999999999</v>
+        <v>0.16664100000000001</v>
       </c>
       <c r="AB22">
-        <v>9.3674999999999994E-2</v>
+        <v>0.14988000000000001</v>
       </c>
       <c r="AC22">
-        <v>0.103307</v>
+        <v>0.165298</v>
       </c>
       <c r="AD22">
-        <v>0.10899200000000001</v>
+        <v>0.17438699999999999</v>
       </c>
       <c r="AE22">
-        <v>0.13131899999999999</v>
+        <v>0.21011099999999999</v>
       </c>
       <c r="AF22">
-        <v>0.12775800000000001</v>
+        <v>0.20441200000000001</v>
       </c>
       <c r="AG22">
-        <v>0.104892</v>
+        <v>0.167827</v>
       </c>
       <c r="AH22">
-        <v>9.8216999999999999E-2</v>
+        <v>0.15801899999999999</v>
       </c>
       <c r="AI22">
-        <v>0.11070000000000001</v>
+        <v>0.176208</v>
       </c>
       <c r="AJ22">
-        <v>0.18217800000000001</v>
+        <v>0.29148499999999999</v>
       </c>
       <c r="AK22">
-        <v>0.20474800000000001</v>
+        <v>0.327596</v>
       </c>
       <c r="AL22">
-        <v>0.201736</v>
+        <v>0.31477100000000002</v>
       </c>
       <c r="AM22">
-        <v>0.179617</v>
+        <v>0.28867999999999999</v>
       </c>
       <c r="AN22">
-        <v>0.16556000000000001</v>
+        <v>0.26550299999999999</v>
       </c>
       <c r="AO22">
-        <v>0.19525300000000001</v>
+        <v>0.30359599999999998</v>
       </c>
       <c r="AP22">
         <v>57.581780000000002</v>
@@ -8944,58 +8944,58 @@
         <v>25.251446000000001</v>
       </c>
       <c r="X23">
-        <v>0.106298</v>
+        <v>0.17007700000000001</v>
       </c>
       <c r="Y23">
-        <v>0.135243</v>
+        <v>0.205146</v>
       </c>
       <c r="Z23">
-        <v>0.120139</v>
+        <v>0.192223</v>
       </c>
       <c r="AA23">
-        <v>0.100961</v>
+        <v>0.16153699999999999</v>
       </c>
       <c r="AB23">
-        <v>9.4993999999999995E-2</v>
+        <v>0.15199099999999999</v>
       </c>
       <c r="AC23">
-        <v>0.10771500000000001</v>
+        <v>0.17235500000000001</v>
       </c>
       <c r="AD23">
-        <v>0.10827100000000001</v>
+        <v>0.173233</v>
       </c>
       <c r="AE23">
-        <v>0.133682</v>
+        <v>0.213891</v>
       </c>
       <c r="AF23">
-        <v>0.12964200000000001</v>
+        <v>0.207428</v>
       </c>
       <c r="AG23">
-        <v>0.101687</v>
+        <v>0.16269900000000001</v>
       </c>
       <c r="AH23">
-        <v>0.100366</v>
+        <v>0.16108</v>
       </c>
       <c r="AI23">
-        <v>0.11315699999999999</v>
+        <v>0.179843</v>
       </c>
       <c r="AJ23">
-        <v>0.17999100000000001</v>
+        <v>0.28798600000000002</v>
       </c>
       <c r="AK23">
-        <v>0.203679</v>
+        <v>0.32588699999999998</v>
       </c>
       <c r="AL23">
-        <v>0.20177400000000001</v>
+        <v>0.31514399999999998</v>
       </c>
       <c r="AM23">
-        <v>0.181285</v>
+        <v>0.29071599999999997</v>
       </c>
       <c r="AN23">
-        <v>0.16939699999999999</v>
+        <v>0.26986100000000002</v>
       </c>
       <c r="AO23">
-        <v>0.19668099999999999</v>
+        <v>0.30570199999999997</v>
       </c>
       <c r="AP23">
         <v>57.670943999999999</v>
@@ -9153,58 +9153,58 @@
         <v>24.647252999999999</v>
       </c>
       <c r="X24">
-        <v>9.7280000000000005E-2</v>
+        <v>0.15564700000000001</v>
       </c>
       <c r="Y24">
-        <v>0.11226700000000001</v>
+        <v>0.17483799999999999</v>
       </c>
       <c r="Z24">
-        <v>0.125303</v>
+        <v>0.200484</v>
       </c>
       <c r="AA24">
-        <v>0.112244</v>
+        <v>0.17959</v>
       </c>
       <c r="AB24">
-        <v>9.9029000000000006E-2</v>
+        <v>0.158447</v>
       </c>
       <c r="AC24">
-        <v>8.7093000000000004E-2</v>
+        <v>0.139344</v>
       </c>
       <c r="AD24">
-        <v>0.108665</v>
+        <v>0.17386399999999999</v>
       </c>
       <c r="AE24">
-        <v>0.123071</v>
+        <v>0.196913</v>
       </c>
       <c r="AF24">
-        <v>0.14052300000000001</v>
+        <v>0.22483700000000001</v>
       </c>
       <c r="AG24">
-        <v>0.12842100000000001</v>
+        <v>0.20547399999999999</v>
       </c>
       <c r="AH24">
-        <v>0.112488</v>
+        <v>0.17868400000000001</v>
       </c>
       <c r="AI24">
-        <v>9.8711999999999994E-2</v>
+        <v>0.15776100000000001</v>
       </c>
       <c r="AJ24">
-        <v>0.175071</v>
+        <v>0.28011399999999997</v>
       </c>
       <c r="AK24">
-        <v>0.18712799999999999</v>
+        <v>0.299404</v>
       </c>
       <c r="AL24">
-        <v>0.208256</v>
+        <v>0.32439800000000002</v>
       </c>
       <c r="AM24">
-        <v>0.20535300000000001</v>
+        <v>0.31931199999999998</v>
       </c>
       <c r="AN24">
-        <v>0.18435299999999999</v>
+        <v>0.291908</v>
       </c>
       <c r="AO24">
-        <v>0.16968</v>
+        <v>0.27389599999999997</v>
       </c>
       <c r="AP24">
         <v>56.102150999999999</v>
@@ -9362,58 +9362,58 @@
         <v>24.317485999999999</v>
       </c>
       <c r="X25">
-        <v>9.8749000000000003E-2</v>
+        <v>0.157998</v>
       </c>
       <c r="Y25">
-        <v>0.10935400000000001</v>
+        <v>0.17177999999999999</v>
       </c>
       <c r="Z25">
-        <v>0.12790899999999999</v>
+        <v>0.204654</v>
       </c>
       <c r="AA25">
-        <v>0.115203</v>
+        <v>0.18432399999999999</v>
       </c>
       <c r="AB25">
-        <v>0.101032</v>
+        <v>0.16165199999999999</v>
       </c>
       <c r="AC25">
-        <v>8.4394999999999998E-2</v>
+        <v>0.13502600000000001</v>
       </c>
       <c r="AD25">
-        <v>0.109886</v>
+        <v>0.175818</v>
       </c>
       <c r="AE25">
-        <v>0.119572</v>
+        <v>0.19131400000000001</v>
       </c>
       <c r="AF25">
-        <v>0.14211799999999999</v>
+        <v>0.22738900000000001</v>
       </c>
       <c r="AG25">
-        <v>0.12894700000000001</v>
+        <v>0.206315</v>
       </c>
       <c r="AH25">
-        <v>0.112275</v>
+        <v>0.178368</v>
       </c>
       <c r="AI25">
-        <v>9.7104999999999997E-2</v>
+        <v>0.15540100000000001</v>
       </c>
       <c r="AJ25">
-        <v>0.177733</v>
+        <v>0.28437299999999999</v>
       </c>
       <c r="AK25">
-        <v>0.18340300000000001</v>
+        <v>0.29344500000000001</v>
       </c>
       <c r="AL25">
-        <v>0.20977799999999999</v>
+        <v>0.325851</v>
       </c>
       <c r="AM25">
-        <v>0.20652499999999999</v>
+        <v>0.32048300000000002</v>
       </c>
       <c r="AN25">
-        <v>0.184917</v>
+        <v>0.29148000000000002</v>
       </c>
       <c r="AO25">
-        <v>0.16656099999999999</v>
+        <v>0.27055699999999999</v>
       </c>
       <c r="AP25">
         <v>56.076560999999998</v>
@@ -9571,58 +9571,58 @@
         <v>24.029889000000001</v>
       </c>
       <c r="X26">
-        <v>9.9963999999999997E-2</v>
+        <v>0.159942</v>
       </c>
       <c r="Y26">
-        <v>0.10156999999999999</v>
+        <v>0.16406299999999999</v>
       </c>
       <c r="Z26">
-        <v>0.124946</v>
+        <v>0.19991400000000001</v>
       </c>
       <c r="AA26">
-        <v>0.114846</v>
+        <v>0.183754</v>
       </c>
       <c r="AB26">
-        <v>9.9154999999999993E-2</v>
+        <v>0.15864700000000001</v>
       </c>
       <c r="AC26">
-        <v>8.6238999999999996E-2</v>
+        <v>0.13797899999999999</v>
       </c>
       <c r="AD26">
-        <v>0.11156000000000001</v>
+        <v>0.17849599999999999</v>
       </c>
       <c r="AE26">
-        <v>0.11348999999999999</v>
+        <v>0.181584</v>
       </c>
       <c r="AF26">
-        <v>0.13999700000000001</v>
+        <v>0.223995</v>
       </c>
       <c r="AG26">
-        <v>0.12784999999999999</v>
+        <v>0.20456099999999999</v>
       </c>
       <c r="AH26">
-        <v>0.110246</v>
+        <v>0.175425</v>
       </c>
       <c r="AI26">
-        <v>9.5686999999999994E-2</v>
+        <v>0.15324599999999999</v>
       </c>
       <c r="AJ26">
-        <v>0.17996000000000001</v>
+        <v>0.287937</v>
       </c>
       <c r="AK26">
-        <v>0.17230999999999999</v>
+        <v>0.27569500000000002</v>
       </c>
       <c r="AL26">
-        <v>0.203846</v>
+        <v>0.31913399999999997</v>
       </c>
       <c r="AM26">
-        <v>0.19895299999999999</v>
+        <v>0.31256</v>
       </c>
       <c r="AN26">
-        <v>0.181809</v>
+        <v>0.287213</v>
       </c>
       <c r="AO26">
-        <v>0.16262499999999999</v>
+        <v>0.26654899999999998</v>
       </c>
       <c r="AP26">
         <v>55.904803000000001</v>
@@ -9780,58 +9780,58 @@
         <v>23.349371999999999</v>
       </c>
       <c r="X27">
-        <v>9.9431000000000005E-2</v>
+        <v>0.15909000000000001</v>
       </c>
       <c r="Y27">
-        <v>9.6248E-2</v>
+        <v>0.15795100000000001</v>
       </c>
       <c r="Z27">
-        <v>0.116826</v>
+        <v>0.186922</v>
       </c>
       <c r="AA27">
-        <v>0.111721</v>
+        <v>0.178753</v>
       </c>
       <c r="AB27">
-        <v>9.7479999999999997E-2</v>
+        <v>0.155968</v>
       </c>
       <c r="AC27">
-        <v>8.5127999999999995E-2</v>
+        <v>0.13620199999999999</v>
       </c>
       <c r="AD27">
-        <v>0.110987</v>
+        <v>0.17757899999999999</v>
       </c>
       <c r="AE27">
-        <v>0.10768999999999999</v>
+        <v>0.17230500000000001</v>
       </c>
       <c r="AF27">
-        <v>0.13178999999999999</v>
+        <v>0.210864</v>
       </c>
       <c r="AG27">
-        <v>0.12534999999999999</v>
+        <v>0.20055899999999999</v>
       </c>
       <c r="AH27">
-        <v>0.10599699999999999</v>
+        <v>0.169351</v>
       </c>
       <c r="AI27">
-        <v>9.3284000000000006E-2</v>
+        <v>0.14988399999999999</v>
       </c>
       <c r="AJ27">
-        <v>0.179532</v>
+        <v>0.28725099999999998</v>
       </c>
       <c r="AK27">
-        <v>0.16512399999999999</v>
+        <v>0.26419900000000002</v>
       </c>
       <c r="AL27">
-        <v>0.197967</v>
+        <v>0.312332</v>
       </c>
       <c r="AM27">
-        <v>0.19644500000000001</v>
+        <v>0.30899399999999999</v>
       </c>
       <c r="AN27">
-        <v>0.17608399999999999</v>
+        <v>0.28015000000000001</v>
       </c>
       <c r="AO27">
-        <v>0.15948499999999999</v>
+        <v>0.26378800000000002</v>
       </c>
       <c r="AP27">
         <v>55.382914999999997</v>
@@ -9989,58 +9989,58 @@
         <v>22.679245000000002</v>
       </c>
       <c r="X28">
-        <v>9.6952999999999998E-2</v>
+        <v>0.15512300000000001</v>
       </c>
       <c r="Y28">
-        <v>9.6263000000000001E-2</v>
+        <v>0.155449</v>
       </c>
       <c r="Z28">
-        <v>0.10689800000000001</v>
+        <v>0.17103599999999999</v>
       </c>
       <c r="AA28">
-        <v>0.100868</v>
+        <v>0.161389</v>
       </c>
       <c r="AB28">
-        <v>9.1704999999999995E-2</v>
+        <v>0.146728</v>
       </c>
       <c r="AC28">
-        <v>8.2893999999999995E-2</v>
+        <v>0.13262399999999999</v>
       </c>
       <c r="AD28">
-        <v>0.10893</v>
+        <v>0.174288</v>
       </c>
       <c r="AE28">
-        <v>0.106804</v>
+        <v>0.17088700000000001</v>
       </c>
       <c r="AF28">
-        <v>0.12037100000000001</v>
+        <v>0.19259299999999999</v>
       </c>
       <c r="AG28">
-        <v>0.114381</v>
+        <v>0.18301000000000001</v>
       </c>
       <c r="AH28">
-        <v>0.100033</v>
+        <v>0.16087000000000001</v>
       </c>
       <c r="AI28">
-        <v>9.2841999999999994E-2</v>
+        <v>0.14937500000000001</v>
       </c>
       <c r="AJ28">
-        <v>0.174926</v>
+        <v>0.27988099999999999</v>
       </c>
       <c r="AK28">
-        <v>0.168852</v>
+        <v>0.27016299999999999</v>
       </c>
       <c r="AL28">
-        <v>0.187523</v>
+        <v>0.300062</v>
       </c>
       <c r="AM28">
-        <v>0.18588499999999999</v>
+        <v>0.29667500000000002</v>
       </c>
       <c r="AN28">
-        <v>0.167431</v>
+        <v>0.27035199999999998</v>
       </c>
       <c r="AO28">
-        <v>0.15934400000000001</v>
+        <v>0.26433899999999999</v>
       </c>
       <c r="AP28">
         <v>55.108046999999999</v>
@@ -10198,58 +10198,58 @@
         <v>22.106109</v>
       </c>
       <c r="X29">
-        <v>9.3937000000000007E-2</v>
+        <v>0.15029799999999999</v>
       </c>
       <c r="Y29">
-        <v>9.0448000000000001E-2</v>
+        <v>0.149974</v>
       </c>
       <c r="Z29">
-        <v>9.7022999999999998E-2</v>
+        <v>0.15523700000000001</v>
       </c>
       <c r="AA29">
-        <v>9.5343999999999998E-2</v>
+        <v>0.15254999999999999</v>
       </c>
       <c r="AB29">
-        <v>8.7178000000000005E-2</v>
+        <v>0.139485</v>
       </c>
       <c r="AC29">
-        <v>8.8229000000000002E-2</v>
+        <v>0.14116600000000001</v>
       </c>
       <c r="AD29">
-        <v>0.105627</v>
+        <v>0.16900399999999999</v>
       </c>
       <c r="AE29">
-        <v>0.102965</v>
+        <v>0.164745</v>
       </c>
       <c r="AF29">
-        <v>0.109917</v>
+        <v>0.175868</v>
       </c>
       <c r="AG29">
-        <v>0.107195</v>
+        <v>0.171512</v>
       </c>
       <c r="AH29">
-        <v>9.5156000000000004E-2</v>
+        <v>0.15390999999999999</v>
       </c>
       <c r="AI29">
-        <v>9.5545000000000005E-2</v>
+        <v>0.15334800000000001</v>
       </c>
       <c r="AJ29">
-        <v>0.17229900000000001</v>
+        <v>0.27567900000000001</v>
       </c>
       <c r="AK29">
-        <v>0.16556599999999999</v>
+        <v>0.26490599999999997</v>
       </c>
       <c r="AL29">
-        <v>0.174294</v>
+        <v>0.28522999999999998</v>
       </c>
       <c r="AM29">
-        <v>0.17488799999999999</v>
+        <v>0.28400999999999998</v>
       </c>
       <c r="AN29">
-        <v>0.15920500000000001</v>
+        <v>0.26125900000000002</v>
       </c>
       <c r="AO29">
-        <v>0.16406100000000001</v>
+        <v>0.26958199999999999</v>
       </c>
       <c r="AP29">
         <v>55.521422999999999</v>
@@ -10407,58 +10407,58 @@
         <v>22.016487000000001</v>
       </c>
       <c r="X30">
-        <v>9.5590999999999995E-2</v>
+        <v>0.152944</v>
       </c>
       <c r="Y30">
-        <v>9.1398999999999994E-2</v>
+        <v>0.15190200000000001</v>
       </c>
       <c r="Z30">
-        <v>9.8114999999999994E-2</v>
+        <v>0.15698400000000001</v>
       </c>
       <c r="AA30">
-        <v>9.3099000000000001E-2</v>
+        <v>0.14895800000000001</v>
       </c>
       <c r="AB30">
-        <v>8.8643E-2</v>
+        <v>0.14182800000000001</v>
       </c>
       <c r="AC30">
-        <v>8.9001999999999998E-2</v>
+        <v>0.142403</v>
       </c>
       <c r="AD30">
-        <v>0.10691000000000001</v>
+        <v>0.17105600000000001</v>
       </c>
       <c r="AE30">
-        <v>0.105311</v>
+        <v>0.16849800000000001</v>
       </c>
       <c r="AF30">
-        <v>0.111586</v>
+        <v>0.178537</v>
       </c>
       <c r="AG30">
-        <v>0.10549699999999999</v>
+        <v>0.168795</v>
       </c>
       <c r="AH30">
-        <v>9.4112000000000001E-2</v>
+        <v>0.15230199999999999</v>
       </c>
       <c r="AI30">
-        <v>9.8569000000000004E-2</v>
+        <v>0.15801100000000001</v>
       </c>
       <c r="AJ30">
-        <v>0.171402</v>
+        <v>0.27424300000000001</v>
       </c>
       <c r="AK30">
-        <v>0.16370799999999999</v>
+        <v>0.26193300000000003</v>
       </c>
       <c r="AL30">
-        <v>0.177236</v>
+        <v>0.28837400000000002</v>
       </c>
       <c r="AM30">
-        <v>0.172984</v>
+        <v>0.28169499999999997</v>
       </c>
       <c r="AN30">
-        <v>0.15670700000000001</v>
+        <v>0.25770700000000002</v>
       </c>
       <c r="AO30">
-        <v>0.16927300000000001</v>
+        <v>0.27598299999999998</v>
       </c>
       <c r="AP30">
         <v>56.255023000000001</v>
@@ -10616,58 +10616,58 @@
         <v>22.124084</v>
       </c>
       <c r="X31">
-        <v>9.8933999999999994E-2</v>
+        <v>0.15829399999999999</v>
       </c>
       <c r="Y31">
-        <v>0.103313</v>
+        <v>0.16391</v>
       </c>
       <c r="Z31">
-        <v>0.104161</v>
+        <v>0.166657</v>
       </c>
       <c r="AA31">
-        <v>9.7009999999999999E-2</v>
+        <v>0.15521699999999999</v>
       </c>
       <c r="AB31">
-        <v>8.9375999999999997E-2</v>
+        <v>0.14300099999999999</v>
       </c>
       <c r="AC31">
-        <v>8.6207000000000006E-2</v>
+        <v>0.137928</v>
       </c>
       <c r="AD31">
-        <v>0.108575</v>
+        <v>0.17372000000000001</v>
       </c>
       <c r="AE31">
-        <v>0.113359</v>
+        <v>0.18137400000000001</v>
       </c>
       <c r="AF31">
-        <v>0.11960899999999999</v>
+        <v>0.19137399999999999</v>
       </c>
       <c r="AG31">
-        <v>0.11214</v>
+        <v>0.179423</v>
       </c>
       <c r="AH31">
-        <v>9.5587000000000005E-2</v>
+        <v>0.15423799999999999</v>
       </c>
       <c r="AI31">
-        <v>0.101344</v>
+        <v>0.16251699999999999</v>
       </c>
       <c r="AJ31">
-        <v>0.16808100000000001</v>
+        <v>0.26893</v>
       </c>
       <c r="AK31">
-        <v>0.174259</v>
+        <v>0.27881400000000001</v>
       </c>
       <c r="AL31">
-        <v>0.191274</v>
+        <v>0.30363000000000001</v>
       </c>
       <c r="AM31">
-        <v>0.18351000000000001</v>
+        <v>0.292238</v>
       </c>
       <c r="AN31">
-        <v>0.160582</v>
+        <v>0.26036799999999999</v>
       </c>
       <c r="AO31">
-        <v>0.175567</v>
+        <v>0.28361999999999998</v>
       </c>
       <c r="AP31">
         <v>57.009366999999997</v>
@@ -10825,58 +10825,58 @@
         <v>22.733825</v>
       </c>
       <c r="X32">
-        <v>0.103438</v>
+        <v>0.16550200000000001</v>
       </c>
       <c r="Y32">
-        <v>0.111489</v>
+        <v>0.17524799999999999</v>
       </c>
       <c r="Z32">
-        <v>0.106958</v>
+        <v>0.17113200000000001</v>
       </c>
       <c r="AA32">
-        <v>0.101117</v>
+        <v>0.16178699999999999</v>
       </c>
       <c r="AB32">
-        <v>9.1439999999999994E-2</v>
+        <v>0.14630399999999999</v>
       </c>
       <c r="AC32">
-        <v>9.0018000000000001E-2</v>
+        <v>0.14402699999999999</v>
       </c>
       <c r="AD32">
-        <v>0.110472</v>
+        <v>0.176755</v>
       </c>
       <c r="AE32">
-        <v>0.12148299999999999</v>
+        <v>0.19437299999999999</v>
       </c>
       <c r="AF32">
-        <v>0.123227</v>
+        <v>0.197163</v>
       </c>
       <c r="AG32">
-        <v>0.113159</v>
+        <v>0.18105499999999999</v>
       </c>
       <c r="AH32">
-        <v>9.8371E-2</v>
+        <v>0.15809799999999999</v>
       </c>
       <c r="AI32">
-        <v>0.106115</v>
+        <v>0.16982</v>
       </c>
       <c r="AJ32">
-        <v>0.17080400000000001</v>
+        <v>0.27328599999999997</v>
       </c>
       <c r="AK32">
-        <v>0.187056</v>
+        <v>0.29929</v>
       </c>
       <c r="AL32">
-        <v>0.19642100000000001</v>
+        <v>0.30962400000000001</v>
       </c>
       <c r="AM32">
-        <v>0.183448</v>
+        <v>0.29293200000000003</v>
       </c>
       <c r="AN32">
-        <v>0.16449900000000001</v>
+        <v>0.26425300000000002</v>
       </c>
       <c r="AO32">
-        <v>0.182445</v>
+        <v>0.29176999999999997</v>
       </c>
       <c r="AP32">
         <v>57.697463999999997</v>
@@ -11034,58 +11034,58 @@
         <v>23.980665999999999</v>
       </c>
       <c r="X33">
-        <v>0.10607</v>
+        <v>0.169713</v>
       </c>
       <c r="Y33">
-        <v>0.114096</v>
+        <v>0.18190100000000001</v>
       </c>
       <c r="Z33">
-        <v>0.11187999999999999</v>
+        <v>0.179008</v>
       </c>
       <c r="AA33">
-        <v>0.110511</v>
+        <v>0.176818</v>
       </c>
       <c r="AB33">
-        <v>9.5760999999999999E-2</v>
+        <v>0.15321799999999999</v>
       </c>
       <c r="AC33">
-        <v>9.6567E-2</v>
+        <v>0.15450700000000001</v>
       </c>
       <c r="AD33">
-        <v>0.114824</v>
+        <v>0.18371899999999999</v>
       </c>
       <c r="AE33">
-        <v>0.12486</v>
+        <v>0.19977600000000001</v>
       </c>
       <c r="AF33">
-        <v>0.123955</v>
+        <v>0.198327</v>
       </c>
       <c r="AG33">
-        <v>0.11559800000000001</v>
+        <v>0.18495600000000001</v>
       </c>
       <c r="AH33">
-        <v>0.102164</v>
+        <v>0.16343199999999999</v>
       </c>
       <c r="AI33">
-        <v>0.11182599999999999</v>
+        <v>0.17832200000000001</v>
       </c>
       <c r="AJ33">
-        <v>0.179866</v>
+        <v>0.28778599999999999</v>
       </c>
       <c r="AK33">
-        <v>0.19278000000000001</v>
+        <v>0.30844700000000003</v>
       </c>
       <c r="AL33">
-        <v>0.19806599999999999</v>
+        <v>0.311977</v>
       </c>
       <c r="AM33">
-        <v>0.18662200000000001</v>
+        <v>0.29685400000000001</v>
       </c>
       <c r="AN33">
-        <v>0.16861899999999999</v>
+        <v>0.26902300000000001</v>
       </c>
       <c r="AO33">
-        <v>0.18918599999999999</v>
+        <v>0.29938100000000001</v>
       </c>
       <c r="AP33">
         <v>58.218203000000003</v>
@@ -11243,58 +11243,58 @@
         <v>25.135527</v>
       </c>
       <c r="X34">
-        <v>0.105002</v>
+        <v>0.16800399999999999</v>
       </c>
       <c r="Y34">
-        <v>0.114993</v>
+        <v>0.18505099999999999</v>
       </c>
       <c r="Z34">
-        <v>0.111953</v>
+        <v>0.17912400000000001</v>
       </c>
       <c r="AA34">
-        <v>0.10965800000000001</v>
+        <v>0.175453</v>
       </c>
       <c r="AB34">
-        <v>9.7933999999999993E-2</v>
+        <v>0.156695</v>
       </c>
       <c r="AC34">
-        <v>0.102418</v>
+        <v>0.16387399999999999</v>
       </c>
       <c r="AD34">
-        <v>0.11483400000000001</v>
+        <v>0.18373400000000001</v>
       </c>
       <c r="AE34">
-        <v>0.12592100000000001</v>
+        <v>0.20147399999999999</v>
       </c>
       <c r="AF34">
-        <v>0.12399399999999999</v>
+        <v>0.19839000000000001</v>
       </c>
       <c r="AG34">
-        <v>0.114981</v>
+        <v>0.18396999999999999</v>
       </c>
       <c r="AH34">
-        <v>0.104645</v>
+        <v>0.16692799999999999</v>
       </c>
       <c r="AI34">
-        <v>0.116424</v>
+        <v>0.184915</v>
       </c>
       <c r="AJ34">
-        <v>0.181205</v>
+        <v>0.28992800000000002</v>
       </c>
       <c r="AK34">
-        <v>0.192082</v>
+        <v>0.30733100000000002</v>
       </c>
       <c r="AL34">
-        <v>0.19778699999999999</v>
+        <v>0.31183699999999998</v>
       </c>
       <c r="AM34">
-        <v>0.18882299999999999</v>
+        <v>0.299373</v>
       </c>
       <c r="AN34">
-        <v>0.17215800000000001</v>
+        <v>0.27295700000000001</v>
       </c>
       <c r="AO34">
-        <v>0.19464799999999999</v>
+        <v>0.30488300000000002</v>
       </c>
       <c r="AP34">
         <v>57.655861000000002</v>
@@ -11452,58 +11452,58 @@
         <v>26.152830000000002</v>
       </c>
       <c r="X35">
-        <v>9.9542000000000005E-2</v>
+        <v>0.15926699999999999</v>
       </c>
       <c r="Y35">
-        <v>0.100952</v>
+        <v>0.16191</v>
       </c>
       <c r="Z35">
-        <v>0.122239</v>
+        <v>0.19558200000000001</v>
       </c>
       <c r="AA35">
-        <v>0.113079</v>
+        <v>0.180927</v>
       </c>
       <c r="AB35">
-        <v>0.101521</v>
+        <v>0.16243299999999999</v>
       </c>
       <c r="AC35">
-        <v>9.3892000000000003E-2</v>
+        <v>0.15023</v>
       </c>
       <c r="AD35">
-        <v>0.108262</v>
+        <v>0.17321900000000001</v>
       </c>
       <c r="AE35">
-        <v>0.112486</v>
+        <v>0.179978</v>
       </c>
       <c r="AF35">
-        <v>0.13350699999999999</v>
+        <v>0.213612</v>
       </c>
       <c r="AG35">
-        <v>0.12267400000000001</v>
+        <v>0.19627900000000001</v>
       </c>
       <c r="AH35">
-        <v>0.115107</v>
+        <v>0.182616</v>
       </c>
       <c r="AI35">
-        <v>0.103577</v>
+        <v>0.16497999999999999</v>
       </c>
       <c r="AJ35">
-        <v>0.17429700000000001</v>
+        <v>0.27887499999999998</v>
       </c>
       <c r="AK35">
-        <v>0.17488799999999999</v>
+        <v>0.27982000000000001</v>
       </c>
       <c r="AL35">
-        <v>0.208261</v>
+        <v>0.32425300000000001</v>
       </c>
       <c r="AM35">
-        <v>0.19715199999999999</v>
+        <v>0.31116199999999999</v>
       </c>
       <c r="AN35">
-        <v>0.192888</v>
+        <v>0.30302899999999999</v>
       </c>
       <c r="AO35">
-        <v>0.180813</v>
+        <v>0.285549</v>
       </c>
       <c r="AP35">
         <v>54.266747000000002</v>
@@ -11661,58 +11661,58 @@
         <v>25.845967999999999</v>
       </c>
       <c r="X36">
-        <v>0.10077800000000001</v>
+        <v>0.161244</v>
       </c>
       <c r="Y36">
-        <v>0.100119</v>
+        <v>0.16036700000000001</v>
       </c>
       <c r="Z36">
-        <v>0.122845</v>
+        <v>0.196552</v>
       </c>
       <c r="AA36">
-        <v>0.114702</v>
+        <v>0.18352299999999999</v>
       </c>
       <c r="AB36">
-        <v>0.101858</v>
+        <v>0.16297200000000001</v>
       </c>
       <c r="AC36">
-        <v>9.3294000000000002E-2</v>
+        <v>0.14927399999999999</v>
       </c>
       <c r="AD36">
-        <v>0.108877</v>
+        <v>0.174203</v>
       </c>
       <c r="AE36">
-        <v>0.11029899999999999</v>
+        <v>0.176478</v>
       </c>
       <c r="AF36">
-        <v>0.13322999999999999</v>
+        <v>0.213168</v>
       </c>
       <c r="AG36">
-        <v>0.123543</v>
+        <v>0.19766900000000001</v>
       </c>
       <c r="AH36">
-        <v>0.11478099999999999</v>
+        <v>0.18221899999999999</v>
       </c>
       <c r="AI36">
-        <v>0.102367</v>
+        <v>0.16316900000000001</v>
       </c>
       <c r="AJ36">
-        <v>0.17547399999999999</v>
+        <v>0.28075899999999998</v>
       </c>
       <c r="AK36">
-        <v>0.17431199999999999</v>
+        <v>0.27889900000000001</v>
       </c>
       <c r="AL36">
-        <v>0.20544299999999999</v>
+        <v>0.32111899999999999</v>
       </c>
       <c r="AM36">
-        <v>0.202214</v>
+        <v>0.31648599999999999</v>
       </c>
       <c r="AN36">
-        <v>0.19273699999999999</v>
+        <v>0.30229600000000001</v>
       </c>
       <c r="AO36">
-        <v>0.17821999999999999</v>
+        <v>0.282779</v>
       </c>
       <c r="AP36">
         <v>53.950201999999997</v>
@@ -11870,58 +11870,58 @@
         <v>25.177835999999999</v>
       </c>
       <c r="X37">
-        <v>0.102062</v>
+        <v>0.1633</v>
       </c>
       <c r="Y37">
-        <v>9.7811999999999996E-2</v>
+        <v>0.157304</v>
       </c>
       <c r="Z37">
-        <v>0.120476</v>
+        <v>0.19276199999999999</v>
       </c>
       <c r="AA37">
-        <v>0.11511399999999999</v>
+        <v>0.18418200000000001</v>
       </c>
       <c r="AB37">
-        <v>9.8977999999999997E-2</v>
+        <v>0.15836600000000001</v>
       </c>
       <c r="AC37">
-        <v>8.9888999999999997E-2</v>
+        <v>0.14382</v>
       </c>
       <c r="AD37">
-        <v>0.11155900000000001</v>
+        <v>0.17849499999999999</v>
       </c>
       <c r="AE37">
-        <v>0.10896699999999999</v>
+        <v>0.174347</v>
       </c>
       <c r="AF37">
-        <v>0.13290199999999999</v>
+        <v>0.212643</v>
       </c>
       <c r="AG37">
-        <v>0.12698599999999999</v>
+        <v>0.203178</v>
       </c>
       <c r="AH37">
-        <v>0.11293499999999999</v>
+        <v>0.17960000000000001</v>
       </c>
       <c r="AI37">
-        <v>9.9978999999999998E-2</v>
+        <v>0.15967700000000001</v>
       </c>
       <c r="AJ37">
-        <v>0.178535</v>
+        <v>0.28565499999999999</v>
       </c>
       <c r="AK37">
-        <v>0.169654</v>
+        <v>0.27144600000000002</v>
       </c>
       <c r="AL37">
-        <v>0.196548</v>
+        <v>0.311191</v>
       </c>
       <c r="AM37">
-        <v>0.205236</v>
+        <v>0.31963900000000001</v>
       </c>
       <c r="AN37">
-        <v>0.18807699999999999</v>
+        <v>0.297014</v>
       </c>
       <c r="AO37">
-        <v>0.17192399999999999</v>
+        <v>0.27690700000000001</v>
       </c>
       <c r="AP37">
         <v>53.920955999999997</v>
@@ -12025,7 +12025,7 @@
         <v>56.921348000000002</v>
       </c>
       <c r="F38">
-        <v>59.769855</v>
+        <v>59.769855999999997</v>
       </c>
       <c r="G38">
         <v>62.468463</v>
@@ -12079,58 +12079,58 @@
         <v>24.326028000000001</v>
       </c>
       <c r="X38">
-        <v>0.10254099999999999</v>
+        <v>0.16406699999999999</v>
       </c>
       <c r="Y38">
-        <v>9.5864000000000005E-2</v>
+        <v>0.154721</v>
       </c>
       <c r="Z38">
-        <v>0.119064</v>
+        <v>0.19050300000000001</v>
       </c>
       <c r="AA38">
-        <v>0.113708</v>
+        <v>0.18193200000000001</v>
       </c>
       <c r="AB38">
-        <v>9.5564999999999997E-2</v>
+        <v>0.15290500000000001</v>
       </c>
       <c r="AC38">
-        <v>9.3404000000000001E-2</v>
+        <v>0.149446</v>
       </c>
       <c r="AD38">
-        <v>0.113507</v>
+        <v>0.18161099999999999</v>
       </c>
       <c r="AE38">
-        <v>0.108297</v>
+        <v>0.17327600000000001</v>
       </c>
       <c r="AF38">
-        <v>0.13248099999999999</v>
+        <v>0.21196899999999999</v>
       </c>
       <c r="AG38">
-        <v>0.122583</v>
+        <v>0.196133</v>
       </c>
       <c r="AH38">
-        <v>0.109538</v>
+        <v>0.174738</v>
       </c>
       <c r="AI38">
-        <v>9.7276000000000001E-2</v>
+        <v>0.155829</v>
       </c>
       <c r="AJ38">
-        <v>0.18346100000000001</v>
+        <v>0.29353699999999999</v>
       </c>
       <c r="AK38">
-        <v>0.169821</v>
+        <v>0.27171299999999998</v>
       </c>
       <c r="AL38">
-        <v>0.20352400000000001</v>
+        <v>0.31817000000000001</v>
       </c>
       <c r="AM38">
-        <v>0.20177300000000001</v>
+        <v>0.31563600000000003</v>
       </c>
       <c r="AN38">
-        <v>0.18192700000000001</v>
+        <v>0.28970499999999999</v>
       </c>
       <c r="AO38">
-        <v>0.167799</v>
+        <v>0.2732</v>
       </c>
       <c r="AP38">
         <v>54.027293</v>
@@ -12288,58 +12288,58 @@
         <v>23.812733999999999</v>
       </c>
       <c r="X39">
-        <v>0.101339</v>
+        <v>0.16214300000000001</v>
       </c>
       <c r="Y39">
-        <v>9.7014000000000003E-2</v>
+        <v>0.154699</v>
       </c>
       <c r="Z39">
-        <v>0.11539199999999999</v>
+        <v>0.18462799999999999</v>
       </c>
       <c r="AA39">
-        <v>0.108944</v>
+        <v>0.17430999999999999</v>
       </c>
       <c r="AB39">
-        <v>9.6270999999999995E-2</v>
+        <v>0.154033</v>
       </c>
       <c r="AC39">
-        <v>0.102671</v>
+        <v>0.16428300000000001</v>
       </c>
       <c r="AD39">
-        <v>0.113695</v>
+        <v>0.18191099999999999</v>
       </c>
       <c r="AE39">
-        <v>0.109066</v>
+        <v>0.17450499999999999</v>
       </c>
       <c r="AF39">
-        <v>0.12898100000000001</v>
+        <v>0.20637</v>
       </c>
       <c r="AG39">
-        <v>0.118296</v>
+        <v>0.189274</v>
       </c>
       <c r="AH39">
-        <v>0.10648000000000001</v>
+        <v>0.170235</v>
       </c>
       <c r="AI39">
-        <v>9.5589999999999994E-2</v>
+        <v>0.15352099999999999</v>
       </c>
       <c r="AJ39">
-        <v>0.17977699999999999</v>
+        <v>0.28764299999999998</v>
       </c>
       <c r="AK39">
-        <v>0.17266400000000001</v>
+        <v>0.27626299999999998</v>
       </c>
       <c r="AL39">
-        <v>0.20210900000000001</v>
+        <v>0.31650899999999998</v>
       </c>
       <c r="AM39">
-        <v>0.19048499999999999</v>
+        <v>0.30219400000000002</v>
       </c>
       <c r="AN39">
-        <v>0.175123</v>
+        <v>0.28149999999999997</v>
       </c>
       <c r="AO39">
-        <v>0.166881</v>
+        <v>0.27276299999999998</v>
       </c>
       <c r="AP39">
         <v>54.078144000000002</v>
@@ -12497,58 +12497,58 @@
         <v>23.484497999999999</v>
       </c>
       <c r="X40">
-        <v>9.8327999999999999E-2</v>
+        <v>0.15732399999999999</v>
       </c>
       <c r="Y40">
-        <v>9.5451999999999995E-2</v>
+        <v>0.15360299999999999</v>
       </c>
       <c r="Z40">
-        <v>0.11326899999999999</v>
+        <v>0.18123</v>
       </c>
       <c r="AA40">
-        <v>9.6060999999999994E-2</v>
+        <v>0.153698</v>
       </c>
       <c r="AB40">
-        <v>9.7239000000000006E-2</v>
+        <v>0.155583</v>
       </c>
       <c r="AC40">
-        <v>9.0887999999999997E-2</v>
+        <v>0.14541699999999999</v>
       </c>
       <c r="AD40">
-        <v>0.112261</v>
+        <v>0.179618</v>
       </c>
       <c r="AE40">
-        <v>0.110569</v>
+        <v>0.17691000000000001</v>
       </c>
       <c r="AF40">
-        <v>0.125664</v>
+        <v>0.20106299999999999</v>
       </c>
       <c r="AG40">
-        <v>0.108671</v>
+        <v>0.173873</v>
       </c>
       <c r="AH40">
-        <v>0.103048</v>
+        <v>0.165244</v>
       </c>
       <c r="AI40">
-        <v>9.5916000000000001E-2</v>
+        <v>0.15417800000000001</v>
       </c>
       <c r="AJ40">
-        <v>0.18274899999999999</v>
+        <v>0.29239799999999999</v>
       </c>
       <c r="AK40">
-        <v>0.175457</v>
+        <v>0.28073100000000001</v>
       </c>
       <c r="AL40">
-        <v>0.205428</v>
+        <v>0.31990400000000002</v>
       </c>
       <c r="AM40">
-        <v>0.17699699999999999</v>
+        <v>0.28737299999999999</v>
       </c>
       <c r="AN40">
-        <v>0.169048</v>
+        <v>0.27412199999999998</v>
       </c>
       <c r="AO40">
-        <v>0.17005600000000001</v>
+        <v>0.27636500000000003</v>
       </c>
       <c r="AP40">
         <v>54.036439999999999</v>
@@ -12706,58 +12706,58 @@
         <v>23.196137</v>
       </c>
       <c r="X41">
-        <v>9.6849000000000005E-2</v>
+        <v>0.15495800000000001</v>
       </c>
       <c r="Y41">
-        <v>9.4263E-2</v>
+        <v>0.153562</v>
       </c>
       <c r="Z41">
-        <v>0.110233</v>
+        <v>0.176372</v>
       </c>
       <c r="AA41">
-        <v>9.3442999999999998E-2</v>
+        <v>0.14951</v>
       </c>
       <c r="AB41">
-        <v>9.3382000000000007E-2</v>
+        <v>0.14941099999999999</v>
       </c>
       <c r="AC41">
-        <v>8.7645000000000001E-2</v>
+        <v>0.14022699999999999</v>
       </c>
       <c r="AD41">
-        <v>0.11163099999999999</v>
+        <v>0.17860899999999999</v>
       </c>
       <c r="AE41">
-        <v>0.113341</v>
+        <v>0.18134600000000001</v>
       </c>
       <c r="AF41">
-        <v>0.122601</v>
+        <v>0.196162</v>
       </c>
       <c r="AG41">
-        <v>0.107658</v>
+        <v>0.17225199999999999</v>
       </c>
       <c r="AH41">
-        <v>0.100623</v>
+        <v>0.16170599999999999</v>
       </c>
       <c r="AI41">
-        <v>9.7730999999999998E-2</v>
+        <v>0.157163</v>
       </c>
       <c r="AJ41">
-        <v>0.18456900000000001</v>
+        <v>0.29531099999999999</v>
       </c>
       <c r="AK41">
-        <v>0.17286000000000001</v>
+        <v>0.27657599999999999</v>
       </c>
       <c r="AL41">
-        <v>0.19553499999999999</v>
+        <v>0.30876599999999998</v>
       </c>
       <c r="AM41">
-        <v>0.17885400000000001</v>
+        <v>0.28856100000000001</v>
       </c>
       <c r="AN41">
-        <v>0.16753199999999999</v>
+        <v>0.27102700000000002</v>
       </c>
       <c r="AO41">
-        <v>0.172982</v>
+        <v>0.28055799999999997</v>
       </c>
       <c r="AP41">
         <v>54.294035000000001</v>
@@ -12918,58 +12918,58 @@
         <v>23.206536</v>
       </c>
       <c r="X42">
-        <v>9.6842999999999999E-2</v>
+        <v>0.154948</v>
       </c>
       <c r="Y42">
-        <v>9.0274999999999994E-2</v>
+        <v>0.15292900000000001</v>
       </c>
       <c r="Z42">
-        <v>0.109054</v>
+        <v>0.174486</v>
       </c>
       <c r="AA42">
-        <v>9.4450999999999993E-2</v>
+        <v>0.15112100000000001</v>
       </c>
       <c r="AB42">
-        <v>8.7534000000000001E-2</v>
+        <v>0.14005400000000001</v>
       </c>
       <c r="AC42">
-        <v>8.4536E-2</v>
+        <v>0.13524800000000001</v>
       </c>
       <c r="AD42">
-        <v>0.109941</v>
+        <v>0.17590500000000001</v>
       </c>
       <c r="AE42">
-        <v>0.11156000000000001</v>
+        <v>0.17849699999999999</v>
       </c>
       <c r="AF42">
-        <v>0.121355</v>
+        <v>0.19416700000000001</v>
       </c>
       <c r="AG42">
-        <v>0.111071</v>
+        <v>0.17771400000000001</v>
       </c>
       <c r="AH42">
-        <v>9.9498000000000003E-2</v>
+        <v>0.16005800000000001</v>
       </c>
       <c r="AI42">
-        <v>0.100636</v>
+        <v>0.161832</v>
       </c>
       <c r="AJ42">
-        <v>0.17706</v>
+        <v>0.28329599999999999</v>
       </c>
       <c r="AK42">
-        <v>0.16558600000000001</v>
+        <v>0.26493800000000001</v>
       </c>
       <c r="AL42">
-        <v>0.19236500000000001</v>
+        <v>0.30503999999999998</v>
       </c>
       <c r="AM42">
-        <v>0.18402499999999999</v>
+        <v>0.29382799999999998</v>
       </c>
       <c r="AN42">
-        <v>0.16597799999999999</v>
+        <v>0.268957</v>
       </c>
       <c r="AO42">
-        <v>0.176839</v>
+        <v>0.285887</v>
       </c>
       <c r="AP42">
         <v>55.092776999999998</v>
@@ -13130,58 +13130,58 @@
         <v>24.215477</v>
       </c>
       <c r="X43">
-        <v>9.9136000000000002E-2</v>
+        <v>0.15861800000000001</v>
       </c>
       <c r="Y43">
-        <v>9.7234000000000001E-2</v>
+        <v>0.16158</v>
       </c>
       <c r="Z43">
-        <v>0.10931299999999999</v>
+        <v>0.174901</v>
       </c>
       <c r="AA43">
-        <v>9.7935999999999995E-2</v>
+        <v>0.156698</v>
       </c>
       <c r="AB43">
-        <v>8.9469000000000007E-2</v>
+        <v>0.143151</v>
       </c>
       <c r="AC43">
-        <v>9.7309000000000007E-2</v>
+        <v>0.155697</v>
       </c>
       <c r="AD43">
-        <v>0.109636</v>
+        <v>0.17541799999999999</v>
       </c>
       <c r="AE43">
-        <v>0.116011</v>
+        <v>0.185617</v>
       </c>
       <c r="AF43">
-        <v>0.11883199999999999</v>
+        <v>0.19013099999999999</v>
       </c>
       <c r="AG43">
-        <v>0.111956</v>
+        <v>0.17912900000000001</v>
       </c>
       <c r="AH43">
-        <v>0.10095999999999999</v>
+        <v>0.16203100000000001</v>
       </c>
       <c r="AI43">
-        <v>0.10864699999999999</v>
+        <v>0.173569</v>
       </c>
       <c r="AJ43">
-        <v>0.17289099999999999</v>
+        <v>0.27662599999999998</v>
       </c>
       <c r="AK43">
-        <v>0.16681099999999999</v>
+        <v>0.266897</v>
       </c>
       <c r="AL43">
-        <v>0.186552</v>
+        <v>0.29894199999999999</v>
       </c>
       <c r="AM43">
-        <v>0.18257000000000001</v>
+        <v>0.293016</v>
       </c>
       <c r="AN43">
-        <v>0.16639899999999999</v>
+        <v>0.269098</v>
       </c>
       <c r="AO43">
-        <v>0.185639</v>
+        <v>0.29539700000000002</v>
       </c>
       <c r="AP43">
         <v>56.301794000000001</v>
@@ -13342,58 +13342,58 @@
         <v>25.377915999999999</v>
       </c>
       <c r="X44">
-        <v>9.9905999999999995E-2</v>
+        <v>0.15984999999999999</v>
       </c>
       <c r="Y44">
-        <v>0.110906</v>
+        <v>0.174844</v>
       </c>
       <c r="Z44">
-        <v>0.11079700000000001</v>
+        <v>0.17727499999999999</v>
       </c>
       <c r="AA44">
-        <v>9.9672999999999998E-2</v>
+        <v>0.15947700000000001</v>
       </c>
       <c r="AB44">
-        <v>8.9696999999999999E-2</v>
+        <v>0.143515</v>
       </c>
       <c r="AC44">
-        <v>0.104439</v>
+        <v>0.16710700000000001</v>
       </c>
       <c r="AD44">
-        <v>0.10838</v>
+        <v>0.17340800000000001</v>
       </c>
       <c r="AE44">
-        <v>0.121367</v>
+        <v>0.194187</v>
       </c>
       <c r="AF44">
-        <v>0.121077</v>
+        <v>0.19372400000000001</v>
       </c>
       <c r="AG44">
-        <v>0.111666</v>
+        <v>0.17866499999999999</v>
       </c>
       <c r="AH44">
-        <v>0.103245</v>
+        <v>0.16520299999999999</v>
       </c>
       <c r="AI44">
-        <v>0.11654</v>
+        <v>0.18505199999999999</v>
       </c>
       <c r="AJ44">
-        <v>0.170984</v>
+        <v>0.27357399999999998</v>
       </c>
       <c r="AK44">
-        <v>0.17669799999999999</v>
+        <v>0.28271600000000002</v>
       </c>
       <c r="AL44">
-        <v>0.18632499999999999</v>
+        <v>0.29878399999999999</v>
       </c>
       <c r="AM44">
-        <v>0.180864</v>
+        <v>0.29208200000000001</v>
       </c>
       <c r="AN44">
-        <v>0.167708</v>
+        <v>0.27058500000000002</v>
       </c>
       <c r="AO44">
-        <v>0.194385</v>
+        <v>0.30443799999999999</v>
       </c>
       <c r="AP44">
         <v>57.085160999999999</v>
@@ -13554,58 +13554,58 @@
         <v>26.304984999999999</v>
       </c>
       <c r="X45">
-        <v>9.9733000000000002E-2</v>
+        <v>0.15957299999999999</v>
       </c>
       <c r="Y45">
-        <v>0.114297</v>
+        <v>0.179512</v>
       </c>
       <c r="Z45">
-        <v>0.111082</v>
+        <v>0.177731</v>
       </c>
       <c r="AA45">
-        <v>0.100734</v>
+        <v>0.16117400000000001</v>
       </c>
       <c r="AB45">
-        <v>9.2213000000000003E-2</v>
+        <v>0.14754</v>
       </c>
       <c r="AC45">
-        <v>0.109084</v>
+        <v>0.174544</v>
       </c>
       <c r="AD45">
-        <v>0.107784</v>
+        <v>0.172455</v>
       </c>
       <c r="AE45">
-        <v>0.12306599999999999</v>
+        <v>0.196905</v>
       </c>
       <c r="AF45">
-        <v>0.123502</v>
+        <v>0.197604</v>
       </c>
       <c r="AG45">
-        <v>0.114343</v>
+        <v>0.182949</v>
       </c>
       <c r="AH45">
-        <v>0.105311</v>
+        <v>0.16805600000000001</v>
       </c>
       <c r="AI45">
-        <v>0.12109300000000001</v>
+        <v>0.191576</v>
       </c>
       <c r="AJ45">
-        <v>0.17164699999999999</v>
+        <v>0.27463500000000002</v>
       </c>
       <c r="AK45">
-        <v>0.179615</v>
+        <v>0.28738399999999997</v>
       </c>
       <c r="AL45">
-        <v>0.187833</v>
+        <v>0.300348</v>
       </c>
       <c r="AM45">
-        <v>0.185173</v>
+        <v>0.296516</v>
       </c>
       <c r="AN45">
-        <v>0.17038200000000001</v>
+        <v>0.27320100000000003</v>
       </c>
       <c r="AO45">
-        <v>0.19930100000000001</v>
+        <v>0.30936000000000002</v>
       </c>
       <c r="AP45">
         <v>56.935929000000002</v>
@@ -13763,58 +13763,58 @@
         <v>26.704937999999999</v>
       </c>
       <c r="X46">
-        <v>9.9459000000000006E-2</v>
+        <v>0.159135</v>
       </c>
       <c r="Y46">
-        <v>9.5296000000000006E-2</v>
+        <v>0.15454699999999999</v>
       </c>
       <c r="Z46">
-        <v>0.11773</v>
+        <v>0.18836800000000001</v>
       </c>
       <c r="AA46">
-        <v>0.11577</v>
+        <v>0.18523200000000001</v>
       </c>
       <c r="AB46">
-        <v>9.9779000000000007E-2</v>
+        <v>0.15964700000000001</v>
       </c>
       <c r="AC46">
-        <v>9.1914999999999997E-2</v>
+        <v>0.147064</v>
       </c>
       <c r="AD46">
-        <v>0.10976900000000001</v>
+        <v>0.17563100000000001</v>
       </c>
       <c r="AE46">
-        <v>0.111027</v>
+        <v>0.177643</v>
       </c>
       <c r="AF46">
-        <v>0.13145599999999999</v>
+        <v>0.21032999999999999</v>
       </c>
       <c r="AG46">
-        <v>0.12809000000000001</v>
+        <v>0.20494299999999999</v>
       </c>
       <c r="AH46">
-        <v>0.115825</v>
+        <v>0.18381</v>
       </c>
       <c r="AI46">
-        <v>0.103617</v>
+        <v>0.165515</v>
       </c>
       <c r="AJ46">
-        <v>0.17845</v>
+        <v>0.28551900000000002</v>
       </c>
       <c r="AK46">
-        <v>0.165412</v>
+        <v>0.26465899999999998</v>
       </c>
       <c r="AL46">
-        <v>0.20771500000000001</v>
+        <v>0.323187</v>
       </c>
       <c r="AM46">
-        <v>0.20364299999999999</v>
+        <v>0.31745400000000001</v>
       </c>
       <c r="AN46">
-        <v>0.19377900000000001</v>
+        <v>0.30653599999999998</v>
       </c>
       <c r="AO46">
-        <v>0.18335699999999999</v>
+        <v>0.29053099999999998</v>
       </c>
       <c r="AP46">
         <v>53.374856000000001</v>
@@ -13972,58 +13972,58 @@
         <v>26.391248000000001</v>
       </c>
       <c r="X47">
-        <v>0.10027</v>
+        <v>0.16043199999999999</v>
       </c>
       <c r="Y47">
-        <v>9.6026E-2</v>
+        <v>0.154469</v>
       </c>
       <c r="Z47">
-        <v>0.115547</v>
+        <v>0.18487500000000001</v>
       </c>
       <c r="AA47">
-        <v>0.114645</v>
+        <v>0.18343300000000001</v>
       </c>
       <c r="AB47">
-        <v>9.8543000000000006E-2</v>
+        <v>0.157669</v>
       </c>
       <c r="AC47">
-        <v>8.8213E-2</v>
+        <v>0.14113600000000001</v>
       </c>
       <c r="AD47">
-        <v>0.10963299999999999</v>
+        <v>0.17541300000000001</v>
       </c>
       <c r="AE47">
-        <v>0.108889</v>
+        <v>0.17422199999999999</v>
       </c>
       <c r="AF47">
-        <v>0.12775900000000001</v>
+        <v>0.20441400000000001</v>
       </c>
       <c r="AG47">
-        <v>0.125107</v>
+        <v>0.20017099999999999</v>
       </c>
       <c r="AH47">
-        <v>0.11476699999999999</v>
+        <v>0.18251300000000001</v>
       </c>
       <c r="AI47">
-        <v>0.101891</v>
+        <v>0.16301299999999999</v>
       </c>
       <c r="AJ47">
-        <v>0.17745900000000001</v>
+        <v>0.28393499999999999</v>
       </c>
       <c r="AK47">
-        <v>0.16680200000000001</v>
+        <v>0.26688299999999998</v>
       </c>
       <c r="AL47">
-        <v>0.19973299999999999</v>
+        <v>0.31447900000000001</v>
       </c>
       <c r="AM47">
-        <v>0.204207</v>
+        <v>0.31822499999999998</v>
       </c>
       <c r="AN47">
-        <v>0.19280600000000001</v>
+        <v>0.30560799999999999</v>
       </c>
       <c r="AO47">
-        <v>0.181363</v>
+        <v>0.28845100000000001</v>
       </c>
       <c r="AP47">
         <v>53.152132000000002</v>
@@ -14181,58 +14181,58 @@
         <v>25.941465999999998</v>
       </c>
       <c r="X48">
-        <v>0.10075000000000001</v>
+        <v>0.16120000000000001</v>
       </c>
       <c r="Y48">
-        <v>9.8006999999999997E-2</v>
+        <v>0.15581800000000001</v>
       </c>
       <c r="Z48">
-        <v>0.110023</v>
+        <v>0.176037</v>
       </c>
       <c r="AA48">
-        <v>0.108305</v>
+        <v>0.173288</v>
       </c>
       <c r="AB48">
-        <v>9.3552999999999997E-2</v>
+        <v>0.14968400000000001</v>
       </c>
       <c r="AC48">
-        <v>8.8216000000000003E-2</v>
+        <v>0.14114299999999999</v>
       </c>
       <c r="AD48">
-        <v>0.110045</v>
+        <v>0.17607100000000001</v>
       </c>
       <c r="AE48">
-        <v>0.107836</v>
+        <v>0.172538</v>
       </c>
       <c r="AF48">
-        <v>0.12216200000000001</v>
+        <v>0.19545899999999999</v>
       </c>
       <c r="AG48">
-        <v>0.117482</v>
+        <v>0.187971</v>
       </c>
       <c r="AH48">
-        <v>0.111748</v>
+        <v>0.178401</v>
       </c>
       <c r="AI48">
-        <v>9.9764000000000005E-2</v>
+        <v>0.159861</v>
       </c>
       <c r="AJ48">
-        <v>0.17669199999999999</v>
+        <v>0.28270800000000001</v>
       </c>
       <c r="AK48">
-        <v>0.167791</v>
+        <v>0.26846599999999998</v>
       </c>
       <c r="AL48">
-        <v>0.186332</v>
+        <v>0.299454</v>
       </c>
       <c r="AM48">
-        <v>0.19897100000000001</v>
+        <v>0.31251099999999998</v>
       </c>
       <c r="AN48">
-        <v>0.18790899999999999</v>
+        <v>0.30070400000000003</v>
       </c>
       <c r="AO48">
-        <v>0.17783299999999999</v>
+        <v>0.28490599999999999</v>
       </c>
       <c r="AP48">
         <v>52.88702</v>
@@ -14390,58 +14390,58 @@
         <v>25.334513000000001</v>
       </c>
       <c r="X49">
-        <v>0.101059</v>
+        <v>0.161694</v>
       </c>
       <c r="Y49">
-        <v>9.8905000000000007E-2</v>
+        <v>0.15692500000000001</v>
       </c>
       <c r="Z49">
-        <v>0.111627</v>
+        <v>0.17860300000000001</v>
       </c>
       <c r="AA49">
-        <v>9.5978999999999995E-2</v>
+        <v>0.15356700000000001</v>
       </c>
       <c r="AB49">
-        <v>8.8636999999999994E-2</v>
+        <v>0.141819</v>
       </c>
       <c r="AC49">
-        <v>8.9913000000000007E-2</v>
+        <v>0.14385899999999999</v>
       </c>
       <c r="AD49">
-        <v>0.110596</v>
+        <v>0.176954</v>
       </c>
       <c r="AE49">
-        <v>0.107429</v>
+        <v>0.17188600000000001</v>
       </c>
       <c r="AF49">
-        <v>0.12357700000000001</v>
+        <v>0.19772300000000001</v>
       </c>
       <c r="AG49">
-        <v>0.106111</v>
+        <v>0.16977800000000001</v>
       </c>
       <c r="AH49">
-        <v>0.10904700000000001</v>
+        <v>0.17458099999999999</v>
       </c>
       <c r="AI49">
-        <v>9.7821000000000005E-2</v>
+        <v>0.15701799999999999</v>
       </c>
       <c r="AJ49">
-        <v>0.17494599999999999</v>
+        <v>0.279914</v>
       </c>
       <c r="AK49">
-        <v>0.16944300000000001</v>
+        <v>0.27110800000000002</v>
       </c>
       <c r="AL49">
-        <v>0.191971</v>
+        <v>0.305147</v>
       </c>
       <c r="AM49">
-        <v>0.18840000000000001</v>
+        <v>0.30138100000000001</v>
       </c>
       <c r="AN49">
-        <v>0.18280099999999999</v>
+        <v>0.295012</v>
       </c>
       <c r="AO49">
-        <v>0.17450199999999999</v>
+        <v>0.281775</v>
       </c>
       <c r="AP49">
         <v>52.784903999999997</v>
@@ -14599,58 +14599,58 @@
         <v>24.981535000000001</v>
       </c>
       <c r="X50">
-        <v>0.101034</v>
+        <v>0.16165399999999999</v>
       </c>
       <c r="Y50">
-        <v>9.7783999999999996E-2</v>
+        <v>0.15718099999999999</v>
       </c>
       <c r="Z50">
-        <v>0.113006</v>
+        <v>0.180809</v>
       </c>
       <c r="AA50">
-        <v>9.6093999999999999E-2</v>
+        <v>0.153751</v>
       </c>
       <c r="AB50">
-        <v>9.2457999999999999E-2</v>
+        <v>0.14793300000000001</v>
       </c>
       <c r="AC50">
-        <v>9.5412999999999998E-2</v>
+        <v>0.152665</v>
       </c>
       <c r="AD50">
-        <v>0.111968</v>
+        <v>0.179149</v>
       </c>
       <c r="AE50">
-        <v>0.109851</v>
+        <v>0.175762</v>
       </c>
       <c r="AF50">
-        <v>0.127526</v>
+        <v>0.204042</v>
       </c>
       <c r="AG50">
-        <v>0.10680199999999999</v>
+        <v>0.17088400000000001</v>
       </c>
       <c r="AH50">
-        <v>0.109126</v>
+        <v>0.17443600000000001</v>
       </c>
       <c r="AI50">
-        <v>9.7572000000000006E-2</v>
+        <v>0.15660399999999999</v>
       </c>
       <c r="AJ50">
-        <v>0.176292</v>
+        <v>0.28206700000000001</v>
       </c>
       <c r="AK50">
-        <v>0.17274300000000001</v>
+        <v>0.27638800000000002</v>
       </c>
       <c r="AL50">
-        <v>0.197132</v>
+        <v>0.31090099999999998</v>
       </c>
       <c r="AM50">
-        <v>0.18640499999999999</v>
+        <v>0.29801100000000003</v>
       </c>
       <c r="AN50">
-        <v>0.18362400000000001</v>
+        <v>0.29353600000000002</v>
       </c>
       <c r="AO50">
-        <v>0.17318600000000001</v>
+        <v>0.28075600000000001</v>
       </c>
       <c r="AP50">
         <v>52.853639999999999</v>
@@ -14808,58 +14808,58 @@
         <v>25.007138000000001</v>
       </c>
       <c r="X51">
-        <v>9.7915000000000002E-2</v>
+        <v>0.156664</v>
       </c>
       <c r="Y51">
-        <v>9.5852000000000007E-2</v>
+        <v>0.157665</v>
       </c>
       <c r="Z51">
-        <v>0.110998</v>
+        <v>0.17759800000000001</v>
       </c>
       <c r="AA51">
-        <v>8.8844000000000006E-2</v>
+        <v>0.142151</v>
       </c>
       <c r="AB51">
-        <v>9.1175999999999993E-2</v>
+        <v>0.14588200000000001</v>
       </c>
       <c r="AC51">
-        <v>9.0558E-2</v>
+        <v>0.14489199999999999</v>
       </c>
       <c r="AD51">
-        <v>0.110079</v>
+        <v>0.17612700000000001</v>
       </c>
       <c r="AE51">
-        <v>0.112631</v>
+        <v>0.18021000000000001</v>
       </c>
       <c r="AF51">
-        <v>0.125754</v>
+        <v>0.201207</v>
       </c>
       <c r="AG51">
-        <v>0.100671</v>
+        <v>0.16107299999999999</v>
       </c>
       <c r="AH51">
-        <v>0.107408</v>
+        <v>0.17185400000000001</v>
       </c>
       <c r="AI51">
-        <v>9.8014000000000004E-2</v>
+        <v>0.157335</v>
       </c>
       <c r="AJ51">
-        <v>0.176983</v>
+        <v>0.28317300000000001</v>
       </c>
       <c r="AK51">
-        <v>0.17443400000000001</v>
+        <v>0.27909400000000001</v>
       </c>
       <c r="AL51">
-        <v>0.19193399999999999</v>
+        <v>0.30543100000000001</v>
       </c>
       <c r="AM51">
-        <v>0.17961099999999999</v>
+        <v>0.29045599999999999</v>
       </c>
       <c r="AN51">
-        <v>0.182509</v>
+        <v>0.29072799999999999</v>
       </c>
       <c r="AO51">
-        <v>0.17553099999999999</v>
+        <v>0.283333</v>
       </c>
       <c r="AP51">
         <v>53.278695999999997</v>
@@ -15017,58 +15017,58 @@
         <v>25.153503000000001</v>
       </c>
       <c r="X52">
-        <v>9.6601999999999993E-2</v>
+        <v>0.154562</v>
       </c>
       <c r="Y52">
-        <v>0.104355</v>
+        <v>0.16530400000000001</v>
       </c>
       <c r="Z52">
-        <v>0.114162</v>
+        <v>0.18265999999999999</v>
       </c>
       <c r="AA52">
-        <v>9.3473000000000001E-2</v>
+        <v>0.14955599999999999</v>
       </c>
       <c r="AB52">
-        <v>9.1194999999999998E-2</v>
+        <v>0.14591199999999999</v>
       </c>
       <c r="AC52">
-        <v>8.7609999999999993E-2</v>
+        <v>0.14017199999999999</v>
       </c>
       <c r="AD52">
-        <v>0.10942300000000001</v>
+        <v>0.17507600000000001</v>
       </c>
       <c r="AE52">
-        <v>0.120231</v>
+        <v>0.19237000000000001</v>
       </c>
       <c r="AF52">
-        <v>0.127273</v>
+        <v>0.20363800000000001</v>
       </c>
       <c r="AG52">
-        <v>0.106628</v>
+        <v>0.17060500000000001</v>
       </c>
       <c r="AH52">
-        <v>0.10555</v>
+        <v>0.16906299999999999</v>
       </c>
       <c r="AI52">
-        <v>9.9358000000000002E-2</v>
+        <v>0.15955900000000001</v>
       </c>
       <c r="AJ52">
-        <v>0.179559</v>
+        <v>0.28729500000000002</v>
       </c>
       <c r="AK52">
-        <v>0.18135599999999999</v>
+        <v>0.29016900000000001</v>
       </c>
       <c r="AL52">
-        <v>0.18610199999999999</v>
+        <v>0.29877100000000001</v>
       </c>
       <c r="AM52">
-        <v>0.181834</v>
+        <v>0.29227399999999998</v>
       </c>
       <c r="AN52">
-        <v>0.17893100000000001</v>
+        <v>0.28583599999999998</v>
       </c>
       <c r="AO52">
-        <v>0.17834900000000001</v>
+        <v>0.28688599999999997</v>
       </c>
       <c r="AP52">
         <v>53.732441999999999</v>
@@ -15226,58 +15226,58 @@
         <v>25.536252000000001</v>
       </c>
       <c r="X53">
-        <v>9.5986000000000002E-2</v>
+        <v>0.15357699999999999</v>
       </c>
       <c r="Y53">
-        <v>0.10470500000000001</v>
+        <v>0.16783000000000001</v>
       </c>
       <c r="Z53">
-        <v>0.113152</v>
+        <v>0.18104400000000001</v>
       </c>
       <c r="AA53">
-        <v>9.4581999999999999E-2</v>
+        <v>0.15133099999999999</v>
       </c>
       <c r="AB53">
-        <v>9.0089000000000002E-2</v>
+        <v>0.14414199999999999</v>
       </c>
       <c r="AC53">
-        <v>8.3333000000000004E-2</v>
+        <v>0.133323</v>
       </c>
       <c r="AD53">
-        <v>0.107213</v>
+        <v>0.171541</v>
       </c>
       <c r="AE53">
-        <v>0.12085</v>
+        <v>0.19336</v>
       </c>
       <c r="AF53">
-        <v>0.124739</v>
+        <v>0.19958200000000001</v>
       </c>
       <c r="AG53">
-        <v>0.107324</v>
+        <v>0.17171800000000001</v>
       </c>
       <c r="AH53">
-        <v>0.103867</v>
+        <v>0.16655200000000001</v>
       </c>
       <c r="AI53">
-        <v>0.10269499999999999</v>
+        <v>0.16472300000000001</v>
       </c>
       <c r="AJ53">
-        <v>0.174849</v>
+        <v>0.27975899999999998</v>
       </c>
       <c r="AK53">
-        <v>0.17871500000000001</v>
+        <v>0.28594399999999998</v>
       </c>
       <c r="AL53">
-        <v>0.18402299999999999</v>
+        <v>0.29617500000000002</v>
       </c>
       <c r="AM53">
-        <v>0.18110100000000001</v>
+        <v>0.29171399999999997</v>
       </c>
       <c r="AN53">
-        <v>0.17510000000000001</v>
+        <v>0.281086</v>
       </c>
       <c r="AO53">
-        <v>0.18296899999999999</v>
+        <v>0.29236400000000001</v>
       </c>
       <c r="AP53">
         <v>54.331598999999997</v>
@@ -15435,58 +15435,58 @@
         <v>26.293769999999999</v>
       </c>
       <c r="X54">
-        <v>9.7212999999999994E-2</v>
+        <v>0.15554100000000001</v>
       </c>
       <c r="Y54">
-        <v>0.10716100000000001</v>
+        <v>0.17130000000000001</v>
       </c>
       <c r="Z54">
-        <v>0.115123</v>
+        <v>0.184197</v>
       </c>
       <c r="AA54">
-        <v>0.102094</v>
+        <v>0.16335</v>
       </c>
       <c r="AB54">
-        <v>9.4729999999999995E-2</v>
+        <v>0.15156800000000001</v>
       </c>
       <c r="AC54">
-        <v>9.4417000000000001E-2</v>
+        <v>0.15106800000000001</v>
       </c>
       <c r="AD54">
-        <v>0.106262</v>
+        <v>0.170019</v>
       </c>
       <c r="AE54">
-        <v>0.12062299999999999</v>
+        <v>0.192997</v>
       </c>
       <c r="AF54">
-        <v>0.122965</v>
+        <v>0.196745</v>
       </c>
       <c r="AG54">
-        <v>0.114316</v>
+        <v>0.18290600000000001</v>
       </c>
       <c r="AH54">
-        <v>0.104129</v>
+        <v>0.16676099999999999</v>
       </c>
       <c r="AI54">
-        <v>0.10922800000000001</v>
+        <v>0.174292</v>
       </c>
       <c r="AJ54">
-        <v>0.17247199999999999</v>
+        <v>0.27595599999999998</v>
       </c>
       <c r="AK54">
-        <v>0.17660000000000001</v>
+        <v>0.282559</v>
       </c>
       <c r="AL54">
-        <v>0.18637000000000001</v>
+        <v>0.29874200000000001</v>
       </c>
       <c r="AM54">
-        <v>0.18603700000000001</v>
+        <v>0.296991</v>
       </c>
       <c r="AN54">
-        <v>0.17326</v>
+        <v>0.27850000000000003</v>
       </c>
       <c r="AO54">
-        <v>0.18970400000000001</v>
+        <v>0.299572</v>
       </c>
       <c r="AP54">
         <v>54.846483999999997</v>
@@ -15644,58 +15644,58 @@
         <v>27.138377999999999</v>
       </c>
       <c r="X55">
-        <v>9.6919000000000005E-2</v>
+        <v>0.15507000000000001</v>
       </c>
       <c r="Y55">
-        <v>0.10996</v>
+        <v>0.175259</v>
       </c>
       <c r="Z55">
-        <v>0.11780400000000001</v>
+        <v>0.18848599999999999</v>
       </c>
       <c r="AA55">
-        <v>0.10223699999999999</v>
+        <v>0.163579</v>
       </c>
       <c r="AB55">
-        <v>9.5494999999999997E-2</v>
+        <v>0.15279200000000001</v>
       </c>
       <c r="AC55">
-        <v>0.10370500000000001</v>
+        <v>0.165935</v>
       </c>
       <c r="AD55">
-        <v>0.102965</v>
+        <v>0.164744</v>
       </c>
       <c r="AE55">
-        <v>0.12060800000000001</v>
+        <v>0.192972</v>
       </c>
       <c r="AF55">
-        <v>0.12740799999999999</v>
+        <v>0.20385300000000001</v>
       </c>
       <c r="AG55">
-        <v>0.11669499999999999</v>
+        <v>0.18671199999999999</v>
       </c>
       <c r="AH55">
-        <v>0.10437299999999999</v>
+        <v>0.167023</v>
       </c>
       <c r="AI55">
-        <v>0.116063</v>
+        <v>0.1842</v>
       </c>
       <c r="AJ55">
-        <v>0.16977200000000001</v>
+        <v>0.27163500000000002</v>
       </c>
       <c r="AK55">
-        <v>0.17965600000000001</v>
+        <v>0.28744999999999998</v>
       </c>
       <c r="AL55">
-        <v>0.19311200000000001</v>
+        <v>0.30640299999999998</v>
       </c>
       <c r="AM55">
-        <v>0.19445799999999999</v>
+        <v>0.30592000000000003</v>
       </c>
       <c r="AN55">
-        <v>0.17224700000000001</v>
+        <v>0.27717000000000003</v>
       </c>
       <c r="AO55">
-        <v>0.19622500000000001</v>
+        <v>0.30634699999999998</v>
       </c>
       <c r="AP55">
         <v>55.130985000000003</v>
@@ -15853,58 +15853,58 @@
         <v>27.677672999999999</v>
       </c>
       <c r="X56">
-        <v>9.7216999999999998E-2</v>
+        <v>0.15554799999999999</v>
       </c>
       <c r="Y56">
-        <v>0.113249</v>
+        <v>0.17824200000000001</v>
       </c>
       <c r="Z56">
-        <v>0.11890199999999999</v>
+        <v>0.190243</v>
       </c>
       <c r="AA56">
-        <v>0.10224999999999999</v>
+        <v>0.1636</v>
       </c>
       <c r="AB56">
-        <v>9.7795999999999994E-2</v>
+        <v>0.156473</v>
       </c>
       <c r="AC56">
-        <v>0.106393</v>
+        <v>0.170237</v>
       </c>
       <c r="AD56">
-        <v>0.101856</v>
+        <v>0.162969</v>
       </c>
       <c r="AE56">
-        <v>0.121229</v>
+        <v>0.193966</v>
       </c>
       <c r="AF56">
-        <v>0.12992699999999999</v>
+        <v>0.20788300000000001</v>
       </c>
       <c r="AG56">
-        <v>0.11629100000000001</v>
+        <v>0.18606500000000001</v>
       </c>
       <c r="AH56">
-        <v>0.104806</v>
+        <v>0.16758600000000001</v>
       </c>
       <c r="AI56">
-        <v>0.119147</v>
+        <v>0.18867900000000001</v>
       </c>
       <c r="AJ56">
-        <v>0.17000699999999999</v>
+        <v>0.272011</v>
       </c>
       <c r="AK56">
-        <v>0.18199699999999999</v>
+        <v>0.29119600000000001</v>
       </c>
       <c r="AL56">
-        <v>0.196519</v>
+        <v>0.31019799999999997</v>
       </c>
       <c r="AM56">
-        <v>0.19519</v>
+        <v>0.30695099999999997</v>
       </c>
       <c r="AN56">
-        <v>0.172703</v>
+        <v>0.277395</v>
       </c>
       <c r="AO56">
-        <v>0.199238</v>
+        <v>0.30948100000000001</v>
       </c>
       <c r="AP56">
         <v>55.913235999999998</v>
@@ -16062,58 +16062,58 @@
         <v>26.982433</v>
       </c>
       <c r="X57">
-        <v>9.6029000000000003E-2</v>
+        <v>0.153646</v>
       </c>
       <c r="Y57">
-        <v>9.4867999999999994E-2</v>
+        <v>0.15470800000000001</v>
       </c>
       <c r="Z57">
-        <v>0.109031</v>
+        <v>0.17444999999999999</v>
       </c>
       <c r="AA57">
-        <v>9.5582E-2</v>
+        <v>0.15293200000000001</v>
       </c>
       <c r="AB57">
-        <v>9.3254000000000004E-2</v>
+        <v>0.14920600000000001</v>
       </c>
       <c r="AC57">
-        <v>9.0981000000000006E-2</v>
+        <v>0.145567</v>
       </c>
       <c r="AD57">
-        <v>0.10989</v>
+        <v>0.17582400000000001</v>
       </c>
       <c r="AE57">
-        <v>0.114624</v>
+        <v>0.18339800000000001</v>
       </c>
       <c r="AF57">
-        <v>0.124446</v>
+        <v>0.19911400000000001</v>
       </c>
       <c r="AG57">
-        <v>0.1087</v>
+        <v>0.17392099999999999</v>
       </c>
       <c r="AH57">
-        <v>0.114371</v>
+        <v>0.18201200000000001</v>
       </c>
       <c r="AI57">
-        <v>0.104134</v>
+        <v>0.16669800000000001</v>
       </c>
       <c r="AJ57">
-        <v>0.18049899999999999</v>
+        <v>0.28879899999999997</v>
       </c>
       <c r="AK57">
-        <v>0.171238</v>
+        <v>0.27398</v>
       </c>
       <c r="AL57">
-        <v>0.191498</v>
+        <v>0.30410300000000001</v>
       </c>
       <c r="AM57">
-        <v>0.177592</v>
+        <v>0.28828799999999999</v>
       </c>
       <c r="AN57">
-        <v>0.193222</v>
+        <v>0.30746600000000002</v>
       </c>
       <c r="AO57">
-        <v>0.185333</v>
+        <v>0.29471799999999998</v>
       </c>
       <c r="AP57">
         <v>52.441097999999997</v>
@@ -16271,58 +16271,58 @@
         <v>26.946006000000001</v>
       </c>
       <c r="X58">
-        <v>9.6282000000000006E-2</v>
+        <v>0.15405099999999999</v>
       </c>
       <c r="Y58">
-        <v>9.1574000000000003E-2</v>
+        <v>0.15137500000000001</v>
       </c>
       <c r="Z58">
-        <v>0.106072</v>
+        <v>0.169715</v>
       </c>
       <c r="AA58">
-        <v>9.5782000000000006E-2</v>
+        <v>0.153252</v>
       </c>
       <c r="AB58">
-        <v>9.4257999999999995E-2</v>
+        <v>0.150813</v>
       </c>
       <c r="AC58">
-        <v>8.5874000000000006E-2</v>
+        <v>0.13739100000000001</v>
       </c>
       <c r="AD58">
-        <v>0.109407</v>
+        <v>0.17505200000000001</v>
       </c>
       <c r="AE58">
-        <v>0.11039599999999999</v>
+        <v>0.17663400000000001</v>
       </c>
       <c r="AF58">
-        <v>0.120533</v>
+        <v>0.192853</v>
       </c>
       <c r="AG58">
-        <v>0.107986</v>
+        <v>0.17277699999999999</v>
       </c>
       <c r="AH58">
-        <v>0.11506</v>
+        <v>0.183143</v>
       </c>
       <c r="AI58">
-        <v>0.10304099999999999</v>
+        <v>0.165075</v>
       </c>
       <c r="AJ58">
-        <v>0.17805499999999999</v>
+        <v>0.284889</v>
       </c>
       <c r="AK58">
-        <v>0.168931</v>
+        <v>0.27028999999999997</v>
       </c>
       <c r="AL58">
-        <v>0.18590100000000001</v>
+        <v>0.29801800000000001</v>
       </c>
       <c r="AM58">
-        <v>0.180172</v>
+        <v>0.29141299999999998</v>
       </c>
       <c r="AN58">
-        <v>0.19590099999999999</v>
+        <v>0.31006699999999998</v>
       </c>
       <c r="AO58">
-        <v>0.18407599999999999</v>
+        <v>0.293437</v>
       </c>
       <c r="AP58">
         <v>51.989404</v>
@@ -16480,58 +16480,58 @@
         <v>27.055491</v>
       </c>
       <c r="X59">
-        <v>9.8669000000000007E-2</v>
+        <v>0.15786900000000001</v>
       </c>
       <c r="Y59">
-        <v>9.2435000000000003E-2</v>
+        <v>0.15117</v>
       </c>
       <c r="Z59">
-        <v>0.102383</v>
+        <v>0.16381200000000001</v>
       </c>
       <c r="AA59">
-        <v>0.10352500000000001</v>
+        <v>0.16564000000000001</v>
       </c>
       <c r="AB59">
-        <v>0.10047</v>
+        <v>0.16075200000000001</v>
       </c>
       <c r="AC59">
-        <v>8.9958999999999997E-2</v>
+        <v>0.14393400000000001</v>
       </c>
       <c r="AD59">
-        <v>0.108835</v>
+        <v>0.17413600000000001</v>
       </c>
       <c r="AE59">
-        <v>0.105758</v>
+        <v>0.169213</v>
       </c>
       <c r="AF59">
-        <v>0.11638800000000001</v>
+        <v>0.18622</v>
       </c>
       <c r="AG59">
-        <v>0.115635</v>
+        <v>0.18501500000000001</v>
       </c>
       <c r="AH59">
-        <v>0.11645899999999999</v>
+        <v>0.18515000000000001</v>
       </c>
       <c r="AI59">
-        <v>0.10304000000000001</v>
+        <v>0.16481999999999999</v>
       </c>
       <c r="AJ59">
-        <v>0.177699</v>
+        <v>0.28431899999999999</v>
       </c>
       <c r="AK59">
-        <v>0.168462</v>
+        <v>0.26953899999999997</v>
       </c>
       <c r="AL59">
-        <v>0.180787</v>
+        <v>0.29219600000000001</v>
       </c>
       <c r="AM59">
-        <v>0.19216900000000001</v>
+        <v>0.30402800000000002</v>
       </c>
       <c r="AN59">
-        <v>0.19903499999999999</v>
+        <v>0.31265999999999999</v>
       </c>
       <c r="AO59">
-        <v>0.184086</v>
+        <v>0.29295300000000002</v>
       </c>
       <c r="AP59">
         <v>51.799374999999998</v>
@@ -16689,58 +16689,58 @@
         <v>26.856221000000001</v>
       </c>
       <c r="X60">
-        <v>0.102663</v>
+        <v>0.16425999999999999</v>
       </c>
       <c r="Y60">
-        <v>9.5827999999999997E-2</v>
+        <v>0.154026</v>
       </c>
       <c r="Z60">
-        <v>0.106794</v>
+        <v>0.17086999999999999</v>
       </c>
       <c r="AA60">
-        <v>0.105874</v>
+        <v>0.16939899999999999</v>
       </c>
       <c r="AB60">
-        <v>0.105695</v>
+        <v>0.16911200000000001</v>
       </c>
       <c r="AC60">
-        <v>9.2482999999999996E-2</v>
+        <v>0.147975</v>
       </c>
       <c r="AD60">
-        <v>0.10703799999999999</v>
+        <v>0.171261</v>
       </c>
       <c r="AE60">
-        <v>0.10362399999999999</v>
+        <v>0.165799</v>
       </c>
       <c r="AF60">
-        <v>0.119104</v>
+        <v>0.19056600000000001</v>
       </c>
       <c r="AG60">
-        <v>0.11705500000000001</v>
+        <v>0.18728800000000001</v>
       </c>
       <c r="AH60">
-        <v>0.11647299999999999</v>
+        <v>0.18515499999999999</v>
       </c>
       <c r="AI60">
-        <v>0.102148</v>
+        <v>0.16339100000000001</v>
       </c>
       <c r="AJ60">
-        <v>0.174758</v>
+        <v>0.27961200000000003</v>
       </c>
       <c r="AK60">
-        <v>0.16926099999999999</v>
+        <v>0.27081699999999997</v>
       </c>
       <c r="AL60">
-        <v>0.18653500000000001</v>
+        <v>0.29839199999999999</v>
       </c>
       <c r="AM60">
-        <v>0.194968</v>
+        <v>0.307116</v>
       </c>
       <c r="AN60">
-        <v>0.19797300000000001</v>
+        <v>0.31129499999999999</v>
       </c>
       <c r="AO60">
-        <v>0.182616</v>
+        <v>0.29140199999999999</v>
       </c>
       <c r="AP60">
         <v>51.908683000000003</v>
@@ -16898,58 +16898,58 @@
         <v>26.379049999999999</v>
       </c>
       <c r="X61">
-        <v>0.108094</v>
+        <v>0.172953</v>
       </c>
       <c r="Y61">
-        <v>9.9918000000000007E-2</v>
+        <v>0.15890799999999999</v>
       </c>
       <c r="Z61">
-        <v>0.11688999999999999</v>
+        <v>0.187024</v>
       </c>
       <c r="AA61">
-        <v>0.103057</v>
+        <v>0.16489100000000001</v>
       </c>
       <c r="AB61">
-        <v>0.102325</v>
+        <v>0.16372</v>
       </c>
       <c r="AC61">
-        <v>8.6683999999999997E-2</v>
+        <v>0.13869100000000001</v>
       </c>
       <c r="AD61">
-        <v>0.10668800000000001</v>
+        <v>0.17070099999999999</v>
       </c>
       <c r="AE61">
-        <v>0.107086</v>
+        <v>0.17133699999999999</v>
       </c>
       <c r="AF61">
-        <v>0.12834100000000001</v>
+        <v>0.205345</v>
       </c>
       <c r="AG61">
-        <v>0.117005</v>
+        <v>0.18720800000000001</v>
       </c>
       <c r="AH61">
-        <v>0.115413</v>
+        <v>0.183535</v>
       </c>
       <c r="AI61">
-        <v>9.9954000000000001E-2</v>
+        <v>0.160248</v>
       </c>
       <c r="AJ61">
-        <v>0.17381099999999999</v>
+        <v>0.27809699999999998</v>
       </c>
       <c r="AK61">
-        <v>0.172815</v>
+        <v>0.27650400000000003</v>
       </c>
       <c r="AL61">
-        <v>0.198293</v>
+        <v>0.31158999999999998</v>
       </c>
       <c r="AM61">
-        <v>0.18987000000000001</v>
+        <v>0.301873</v>
       </c>
       <c r="AN61">
-        <v>0.19297500000000001</v>
+        <v>0.30582199999999998</v>
       </c>
       <c r="AO61">
-        <v>0.17935699999999999</v>
+        <v>0.28849399999999997</v>
       </c>
       <c r="AP61">
         <v>52.427047999999999</v>
@@ -17107,58 +17107,58 @@
         <v>26.202017000000001</v>
       </c>
       <c r="X62">
-        <v>0.10306</v>
+        <v>0.16489699999999999</v>
       </c>
       <c r="Y62">
-        <v>0.10491499999999999</v>
+        <v>0.164745</v>
       </c>
       <c r="Z62">
-        <v>0.12053899999999999</v>
+        <v>0.19286300000000001</v>
       </c>
       <c r="AA62">
-        <v>0.109789</v>
+        <v>0.17566200000000001</v>
       </c>
       <c r="AB62">
-        <v>0.100547</v>
+        <v>0.16087599999999999</v>
       </c>
       <c r="AC62">
-        <v>8.1767999999999993E-2</v>
+        <v>0.13082099999999999</v>
       </c>
       <c r="AD62">
-        <v>0.103744</v>
+        <v>0.165991</v>
       </c>
       <c r="AE62">
-        <v>0.109671</v>
+        <v>0.17547399999999999</v>
       </c>
       <c r="AF62">
-        <v>0.13031999999999999</v>
+        <v>0.208512</v>
       </c>
       <c r="AG62">
-        <v>0.119085</v>
+        <v>0.19053600000000001</v>
       </c>
       <c r="AH62">
-        <v>0.113971</v>
+        <v>0.18135000000000001</v>
       </c>
       <c r="AI62">
-        <v>9.8712999999999995E-2</v>
+        <v>0.158554</v>
       </c>
       <c r="AJ62">
-        <v>0.17102400000000001</v>
+        <v>0.27363900000000002</v>
       </c>
       <c r="AK62">
-        <v>0.17910599999999999</v>
+        <v>0.28656900000000002</v>
       </c>
       <c r="AL62">
-        <v>0.20511099999999999</v>
+        <v>0.31918000000000002</v>
       </c>
       <c r="AM62">
-        <v>0.19528499999999999</v>
+        <v>0.30720799999999998</v>
       </c>
       <c r="AN62">
-        <v>0.188855</v>
+        <v>0.300649</v>
       </c>
       <c r="AO62">
-        <v>0.17808099999999999</v>
+        <v>0.28757500000000003</v>
       </c>
       <c r="AP62">
         <v>53.105452999999997</v>
@@ -17316,58 +17316,58 @@
         <v>26.404330999999999</v>
       </c>
       <c r="X63">
-        <v>9.7947999999999993E-2</v>
+        <v>0.15671599999999999</v>
       </c>
       <c r="Y63">
-        <v>0.111346</v>
+        <v>0.17052400000000001</v>
       </c>
       <c r="Z63">
-        <v>0.114679</v>
+        <v>0.18348700000000001</v>
       </c>
       <c r="AA63">
-        <v>0.107575</v>
+        <v>0.17212</v>
       </c>
       <c r="AB63">
-        <v>0.10090499999999999</v>
+        <v>0.16144700000000001</v>
       </c>
       <c r="AC63">
-        <v>8.9044999999999999E-2</v>
+        <v>0.14247000000000001</v>
       </c>
       <c r="AD63">
-        <v>0.103893</v>
+        <v>0.16622899999999999</v>
       </c>
       <c r="AE63">
-        <v>0.11132300000000001</v>
+        <v>0.178117</v>
       </c>
       <c r="AF63">
-        <v>0.12628200000000001</v>
+        <v>0.20205000000000001</v>
       </c>
       <c r="AG63">
-        <v>0.11895699999999999</v>
+        <v>0.190331</v>
       </c>
       <c r="AH63">
-        <v>0.11230999999999999</v>
+        <v>0.17877100000000001</v>
       </c>
       <c r="AI63">
-        <v>0.100411</v>
+        <v>0.16105800000000001</v>
       </c>
       <c r="AJ63">
-        <v>0.17036599999999999</v>
+        <v>0.27258599999999999</v>
       </c>
       <c r="AK63">
-        <v>0.18038599999999999</v>
+        <v>0.28861700000000001</v>
       </c>
       <c r="AL63">
-        <v>0.19181400000000001</v>
+        <v>0.30485600000000002</v>
       </c>
       <c r="AM63">
-        <v>0.19325999999999999</v>
+        <v>0.304811</v>
       </c>
       <c r="AN63">
-        <v>0.185835</v>
+        <v>0.296039</v>
       </c>
       <c r="AO63">
-        <v>0.179788</v>
+        <v>0.289576</v>
       </c>
       <c r="AP63">
         <v>53.79813</v>
@@ -17525,58 +17525,58 @@
         <v>26.937526999999999</v>
       </c>
       <c r="X64">
-        <v>9.3826999999999994E-2</v>
+        <v>0.15012300000000001</v>
       </c>
       <c r="Y64">
-        <v>0.115449</v>
+        <v>0.173377</v>
       </c>
       <c r="Z64">
-        <v>0.107624</v>
+        <v>0.17219899999999999</v>
       </c>
       <c r="AA64">
-        <v>9.7195000000000004E-2</v>
+        <v>0.15551100000000001</v>
       </c>
       <c r="AB64">
-        <v>0.10299</v>
+        <v>0.16478400000000001</v>
       </c>
       <c r="AC64">
-        <v>0.10204299999999999</v>
+        <v>0.16327900000000001</v>
       </c>
       <c r="AD64">
-        <v>0.10111299999999999</v>
+        <v>0.16178100000000001</v>
       </c>
       <c r="AE64">
-        <v>0.11373800000000001</v>
+        <v>0.181981</v>
       </c>
       <c r="AF64">
-        <v>0.118002</v>
+        <v>0.188804</v>
       </c>
       <c r="AG64">
-        <v>0.111001</v>
+        <v>0.17760200000000001</v>
       </c>
       <c r="AH64">
-        <v>0.108375</v>
+        <v>0.17313100000000001</v>
       </c>
       <c r="AI64">
-        <v>0.103713</v>
+        <v>0.16589300000000001</v>
       </c>
       <c r="AJ64">
-        <v>0.167157</v>
+        <v>0.26745200000000002</v>
       </c>
       <c r="AK64">
-        <v>0.18610099999999999</v>
+        <v>0.297761</v>
       </c>
       <c r="AL64">
-        <v>0.19225999999999999</v>
+        <v>0.30510100000000001</v>
       </c>
       <c r="AM64">
-        <v>0.18679499999999999</v>
+        <v>0.29833999999999999</v>
       </c>
       <c r="AN64">
-        <v>0.182197</v>
+        <v>0.29120400000000002</v>
       </c>
       <c r="AO64">
-        <v>0.18417700000000001</v>
+        <v>0.29407699999999998</v>
       </c>
       <c r="AP64">
         <v>54.441397000000002</v>
@@ -17734,58 +17734,58 @@
         <v>27.057599</v>
       </c>
       <c r="X65">
-        <v>9.2515E-2</v>
+        <v>0.14802399999999999</v>
       </c>
       <c r="Y65">
-        <v>0.107197</v>
+        <v>0.16640199999999999</v>
       </c>
       <c r="Z65">
-        <v>0.10754</v>
+        <v>0.17206399999999999</v>
       </c>
       <c r="AA65">
-        <v>9.0624999999999997E-2</v>
+        <v>0.14499899999999999</v>
       </c>
       <c r="AB65">
-        <v>0.105725</v>
+        <v>0.16916</v>
       </c>
       <c r="AC65">
-        <v>0.100608</v>
+        <v>0.16097900000000001</v>
       </c>
       <c r="AD65">
-        <v>0.10036100000000001</v>
+        <v>0.160577</v>
       </c>
       <c r="AE65">
-        <v>0.112168</v>
+        <v>0.17946799999999999</v>
       </c>
       <c r="AF65">
-        <v>0.11751399999999999</v>
+        <v>0.188023</v>
       </c>
       <c r="AG65">
-        <v>0.113068</v>
+        <v>0.18090800000000001</v>
       </c>
       <c r="AH65">
-        <v>0.106124</v>
+        <v>0.16981199999999999</v>
       </c>
       <c r="AI65">
-        <v>0.10654</v>
+        <v>0.17016600000000001</v>
       </c>
       <c r="AJ65">
-        <v>0.169766</v>
+        <v>0.27162599999999998</v>
       </c>
       <c r="AK65">
-        <v>0.18129400000000001</v>
+        <v>0.29006999999999999</v>
       </c>
       <c r="AL65">
-        <v>0.195211</v>
+        <v>0.30808000000000002</v>
       </c>
       <c r="AM65">
-        <v>0.18956500000000001</v>
+        <v>0.30080699999999999</v>
       </c>
       <c r="AN65">
-        <v>0.18120700000000001</v>
+        <v>0.28870400000000002</v>
       </c>
       <c r="AO65">
-        <v>0.18801399999999999</v>
+        <v>0.29822500000000002</v>
       </c>
       <c r="AP65">
         <v>55.034219999999998</v>
@@ -17943,58 +17943,58 @@
         <v>26.960943</v>
       </c>
       <c r="X66">
-        <v>9.1852000000000003E-2</v>
+        <v>0.14696300000000001</v>
       </c>
       <c r="Y66">
-        <v>0.10254099999999999</v>
+        <v>0.16205</v>
       </c>
       <c r="Z66">
-        <v>0.11279599999999999</v>
+        <v>0.180474</v>
       </c>
       <c r="AA66">
-        <v>9.9765999999999994E-2</v>
+        <v>0.15962499999999999</v>
       </c>
       <c r="AB66">
-        <v>0.104725</v>
+        <v>0.16756099999999999</v>
       </c>
       <c r="AC66">
-        <v>0.103517</v>
+        <v>0.165635</v>
       </c>
       <c r="AD66">
-        <v>9.8914000000000002E-2</v>
+        <v>0.15826299999999999</v>
       </c>
       <c r="AE66">
-        <v>0.10902000000000001</v>
+        <v>0.174432</v>
       </c>
       <c r="AF66">
-        <v>0.12138400000000001</v>
+        <v>0.194214</v>
       </c>
       <c r="AG66">
-        <v>0.11298900000000001</v>
+        <v>0.180783</v>
       </c>
       <c r="AH66">
-        <v>0.103855</v>
+        <v>0.16652600000000001</v>
       </c>
       <c r="AI66">
-        <v>0.10958</v>
+        <v>0.174702</v>
       </c>
       <c r="AJ66">
-        <v>0.16869000000000001</v>
+        <v>0.26990500000000001</v>
       </c>
       <c r="AK66">
-        <v>0.175537</v>
+        <v>0.28085900000000003</v>
       </c>
       <c r="AL66">
-        <v>0.199438</v>
+        <v>0.312948</v>
       </c>
       <c r="AM66">
-        <v>0.19603000000000001</v>
+        <v>0.307367</v>
       </c>
       <c r="AN66">
-        <v>0.17938200000000001</v>
+        <v>0.285885</v>
       </c>
       <c r="AO66">
-        <v>0.19267200000000001</v>
+        <v>0.30289700000000003</v>
       </c>
       <c r="AP66">
         <v>55.582715999999998</v>
@@ -18152,58 +18152,58 @@
         <v>27.044771000000001</v>
       </c>
       <c r="X67">
-        <v>9.1907000000000003E-2</v>
+        <v>0.14705099999999999</v>
       </c>
       <c r="Y67">
-        <v>0.104597</v>
+        <v>0.16259599999999999</v>
       </c>
       <c r="Z67">
-        <v>0.114676</v>
+        <v>0.18348200000000001</v>
       </c>
       <c r="AA67">
-        <v>0.105377</v>
+        <v>0.168603</v>
       </c>
       <c r="AB67">
-        <v>0.102705</v>
+        <v>0.164327</v>
       </c>
       <c r="AC67">
-        <v>0.104226</v>
+        <v>0.16677</v>
       </c>
       <c r="AD67">
-        <v>9.9569000000000005E-2</v>
+        <v>0.15931000000000001</v>
       </c>
       <c r="AE67">
-        <v>0.10967200000000001</v>
+        <v>0.17547499999999999</v>
       </c>
       <c r="AF67">
-        <v>0.12371799999999999</v>
+        <v>0.19794900000000001</v>
       </c>
       <c r="AG67">
-        <v>0.112987</v>
+        <v>0.18078</v>
       </c>
       <c r="AH67">
-        <v>0.1031</v>
+        <v>0.16541400000000001</v>
       </c>
       <c r="AI67">
-        <v>0.111168</v>
+        <v>0.177061</v>
       </c>
       <c r="AJ67">
-        <v>0.16842699999999999</v>
+        <v>0.269484</v>
       </c>
       <c r="AK67">
-        <v>0.17473900000000001</v>
+        <v>0.27958300000000003</v>
       </c>
       <c r="AL67">
-        <v>0.20084099999999999</v>
+        <v>0.31451499999999999</v>
       </c>
       <c r="AM67">
-        <v>0.19561300000000001</v>
+        <v>0.30701400000000001</v>
       </c>
       <c r="AN67">
-        <v>0.17825099999999999</v>
+        <v>0.28421800000000003</v>
       </c>
       <c r="AO67">
-        <v>0.19456999999999999</v>
+        <v>0.30483399999999999</v>
       </c>
       <c r="AP67">
         <v>56.372726</v>
@@ -18361,58 +18361,58 @@
         <v>27.567014</v>
       </c>
       <c r="X68">
-        <v>9.6324000000000007E-2</v>
+        <v>0.15411900000000001</v>
       </c>
       <c r="Y68">
-        <v>0.10596800000000001</v>
+        <v>0.16711599999999999</v>
       </c>
       <c r="Z68">
-        <v>9.1123999999999997E-2</v>
+        <v>0.14579900000000001</v>
       </c>
       <c r="AA68">
-        <v>8.6051000000000002E-2</v>
+        <v>0.137681</v>
       </c>
       <c r="AB68">
-        <v>8.9689000000000005E-2</v>
+        <v>0.14350199999999999</v>
       </c>
       <c r="AC68">
-        <v>8.5557999999999995E-2</v>
+        <v>0.13688800000000001</v>
       </c>
       <c r="AD68">
-        <v>0.11214300000000001</v>
+        <v>0.17942900000000001</v>
       </c>
       <c r="AE68">
-        <v>0.11885999999999999</v>
+        <v>0.19017600000000001</v>
       </c>
       <c r="AF68">
-        <v>0.10596899999999999</v>
+        <v>0.16955100000000001</v>
       </c>
       <c r="AG68">
-        <v>0.10070900000000001</v>
+        <v>0.161134</v>
       </c>
       <c r="AH68">
-        <v>0.112292</v>
+        <v>0.17924999999999999</v>
       </c>
       <c r="AI68">
-        <v>0.10750899999999999</v>
+        <v>0.171901</v>
       </c>
       <c r="AJ68">
-        <v>0.182723</v>
+        <v>0.29235699999999998</v>
       </c>
       <c r="AK68">
-        <v>0.175958</v>
+        <v>0.281532</v>
       </c>
       <c r="AL68">
-        <v>0.17404500000000001</v>
+        <v>0.283418</v>
       </c>
       <c r="AM68">
-        <v>0.17107700000000001</v>
+        <v>0.27966999999999997</v>
       </c>
       <c r="AN68">
-        <v>0.18763099999999999</v>
+        <v>0.30279400000000001</v>
       </c>
       <c r="AO68">
-        <v>0.187752</v>
+        <v>0.29883900000000002</v>
       </c>
       <c r="AP68">
         <v>52.153160999999997</v>
@@ -18570,58 +18570,58 @@
         <v>27.670864999999999</v>
       </c>
       <c r="X69">
-        <v>9.6488000000000004E-2</v>
+        <v>0.15437999999999999</v>
       </c>
       <c r="Y69">
-        <v>9.6987000000000004E-2</v>
+        <v>0.15937899999999999</v>
       </c>
       <c r="Z69">
-        <v>8.9598999999999998E-2</v>
+        <v>0.14335800000000001</v>
       </c>
       <c r="AA69">
-        <v>8.7246000000000004E-2</v>
+        <v>0.13959299999999999</v>
       </c>
       <c r="AB69">
-        <v>9.0728000000000003E-2</v>
+        <v>0.14516599999999999</v>
       </c>
       <c r="AC69">
-        <v>8.4084999999999993E-2</v>
+        <v>0.13452900000000001</v>
       </c>
       <c r="AD69">
-        <v>0.112058</v>
+        <v>0.17929300000000001</v>
       </c>
       <c r="AE69">
-        <v>0.11473999999999999</v>
+        <v>0.183584</v>
       </c>
       <c r="AF69">
-        <v>0.104708</v>
+        <v>0.16753299999999999</v>
       </c>
       <c r="AG69">
-        <v>0.10226200000000001</v>
+        <v>0.16361800000000001</v>
       </c>
       <c r="AH69">
-        <v>0.11325</v>
+        <v>0.180788</v>
       </c>
       <c r="AI69">
-        <v>0.107114</v>
+        <v>0.17125899999999999</v>
       </c>
       <c r="AJ69">
-        <v>0.18165799999999999</v>
+        <v>0.29065299999999999</v>
       </c>
       <c r="AK69">
-        <v>0.17272999999999999</v>
+        <v>0.276368</v>
       </c>
       <c r="AL69">
-        <v>0.173539</v>
+        <v>0.28278199999999998</v>
       </c>
       <c r="AM69">
-        <v>0.17538899999999999</v>
+        <v>0.284696</v>
       </c>
       <c r="AN69">
-        <v>0.190548</v>
+        <v>0.30595</v>
       </c>
       <c r="AO69">
-        <v>0.18723799999999999</v>
+        <v>0.29835699999999998</v>
       </c>
       <c r="AP69">
         <v>51.459231000000003</v>
@@ -18779,58 +18779,58 @@
         <v>27.83381</v>
       </c>
       <c r="X70">
-        <v>9.8364999999999994E-2</v>
+        <v>0.157383</v>
       </c>
       <c r="Y70">
-        <v>9.2643000000000003E-2</v>
+        <v>0.15312400000000001</v>
       </c>
       <c r="Z70">
-        <v>9.3376000000000001E-2</v>
+        <v>0.14940100000000001</v>
       </c>
       <c r="AA70">
-        <v>9.6054E-2</v>
+        <v>0.15368599999999999</v>
       </c>
       <c r="AB70">
-        <v>9.4754000000000005E-2</v>
+        <v>0.15160599999999999</v>
       </c>
       <c r="AC70">
-        <v>8.8527999999999996E-2</v>
+        <v>0.14164199999999999</v>
       </c>
       <c r="AD70">
-        <v>0.11044</v>
+        <v>0.176703</v>
       </c>
       <c r="AE70">
-        <v>0.107733</v>
+        <v>0.172373</v>
       </c>
       <c r="AF70">
-        <v>0.10662099999999999</v>
+        <v>0.170594</v>
       </c>
       <c r="AG70">
-        <v>0.11058</v>
+        <v>0.176929</v>
       </c>
       <c r="AH70">
-        <v>0.11530899999999999</v>
+        <v>0.18376100000000001</v>
       </c>
       <c r="AI70">
-        <v>0.10568900000000001</v>
+        <v>0.16905999999999999</v>
       </c>
       <c r="AJ70">
-        <v>0.17921000000000001</v>
+        <v>0.28673599999999999</v>
       </c>
       <c r="AK70">
-        <v>0.16925899999999999</v>
+        <v>0.270814</v>
       </c>
       <c r="AL70">
-        <v>0.175954</v>
+        <v>0.28563300000000003</v>
       </c>
       <c r="AM70">
-        <v>0.18663199999999999</v>
+        <v>0.29769699999999999</v>
       </c>
       <c r="AN70">
-        <v>0.196608</v>
+        <v>0.31173099999999998</v>
       </c>
       <c r="AO70">
-        <v>0.18671299999999999</v>
+        <v>0.29752200000000001</v>
       </c>
       <c r="AP70">
         <v>51.362788999999999</v>
@@ -18988,58 +18988,58 @@
         <v>27.508448000000001</v>
       </c>
       <c r="X71">
-        <v>0.101063</v>
+        <v>0.16170200000000001</v>
       </c>
       <c r="Y71">
-        <v>9.3479000000000007E-2</v>
+        <v>0.152223</v>
       </c>
       <c r="Z71">
-        <v>9.8853999999999997E-2</v>
+        <v>0.158167</v>
       </c>
       <c r="AA71">
-        <v>9.7803000000000001E-2</v>
+        <v>0.15648500000000001</v>
       </c>
       <c r="AB71">
-        <v>9.7306000000000004E-2</v>
+        <v>0.15568899999999999</v>
       </c>
       <c r="AC71">
-        <v>8.7014999999999995E-2</v>
+        <v>0.13922000000000001</v>
       </c>
       <c r="AD71">
-        <v>0.107186</v>
+        <v>0.17149800000000001</v>
       </c>
       <c r="AE71">
-        <v>0.104074</v>
+        <v>0.166519</v>
       </c>
       <c r="AF71">
-        <v>0.108373</v>
+        <v>0.173398</v>
       </c>
       <c r="AG71">
-        <v>0.110669</v>
+        <v>0.17707100000000001</v>
       </c>
       <c r="AH71">
-        <v>0.11580500000000001</v>
+        <v>0.184448</v>
       </c>
       <c r="AI71">
-        <v>0.103362</v>
+        <v>0.16559499999999999</v>
       </c>
       <c r="AJ71">
-        <v>0.17843899999999999</v>
+        <v>0.28550199999999998</v>
       </c>
       <c r="AK71">
-        <v>0.16861499999999999</v>
+        <v>0.26978400000000002</v>
       </c>
       <c r="AL71">
-        <v>0.17690700000000001</v>
+        <v>0.287296</v>
       </c>
       <c r="AM71">
-        <v>0.192472</v>
+        <v>0.30453599999999997</v>
       </c>
       <c r="AN71">
-        <v>0.19861699999999999</v>
+        <v>0.31353900000000001</v>
       </c>
       <c r="AO71">
-        <v>0.18504200000000001</v>
+        <v>0.29563699999999998</v>
       </c>
       <c r="AP71">
         <v>51.50553</v>
@@ -19197,58 +19197,58 @@
         <v>26.966116</v>
       </c>
       <c r="X72">
-        <v>0.104075</v>
+        <v>0.166521</v>
       </c>
       <c r="Y72">
-        <v>9.6228999999999995E-2</v>
+        <v>0.154111</v>
       </c>
       <c r="Z72">
-        <v>0.107873</v>
+        <v>0.172596</v>
       </c>
       <c r="AA72">
-        <v>0.102753</v>
+        <v>0.164405</v>
       </c>
       <c r="AB72">
-        <v>9.9685999999999997E-2</v>
+        <v>0.159497</v>
       </c>
       <c r="AC72">
-        <v>8.5868E-2</v>
+        <v>0.13738400000000001</v>
       </c>
       <c r="AD72">
-        <v>0.10606400000000001</v>
+        <v>0.16970199999999999</v>
       </c>
       <c r="AE72">
-        <v>0.10338</v>
+        <v>0.165408</v>
       </c>
       <c r="AF72">
-        <v>0.11559</v>
+        <v>0.184944</v>
       </c>
       <c r="AG72">
-        <v>0.115083</v>
+        <v>0.18413299999999999</v>
       </c>
       <c r="AH72">
-        <v>0.115208</v>
+        <v>0.18351200000000001</v>
       </c>
       <c r="AI72">
-        <v>0.101067</v>
+        <v>0.16220200000000001</v>
       </c>
       <c r="AJ72">
-        <v>0.17902000000000001</v>
+        <v>0.28643200000000002</v>
       </c>
       <c r="AK72">
-        <v>0.16891500000000001</v>
+        <v>0.270264</v>
       </c>
       <c r="AL72">
-        <v>0.18523000000000001</v>
+        <v>0.29699199999999998</v>
       </c>
       <c r="AM72">
-        <v>0.19142000000000001</v>
+        <v>0.303703</v>
       </c>
       <c r="AN72">
-        <v>0.19522200000000001</v>
+        <v>0.31012299999999998</v>
       </c>
       <c r="AO72">
-        <v>0.18260000000000001</v>
+        <v>0.29315200000000002</v>
       </c>
       <c r="AP72">
         <v>51.940700999999997</v>
@@ -19406,58 +19406,58 @@
         <v>26.705480000000001</v>
       </c>
       <c r="X73">
-        <v>0.100607</v>
+        <v>0.160972</v>
       </c>
       <c r="Y73">
-        <v>9.6942E-2</v>
+        <v>0.15415000000000001</v>
       </c>
       <c r="Z73">
-        <v>0.111168</v>
+        <v>0.177868</v>
       </c>
       <c r="AA73">
-        <v>0.10445699999999999</v>
+        <v>0.167131</v>
       </c>
       <c r="AB73">
-        <v>9.7809999999999994E-2</v>
+        <v>0.156496</v>
       </c>
       <c r="AC73">
-        <v>8.3082000000000003E-2</v>
+        <v>0.13292499999999999</v>
       </c>
       <c r="AD73">
-        <v>0.103021</v>
+        <v>0.16483300000000001</v>
       </c>
       <c r="AE73">
-        <v>0.101578</v>
+        <v>0.162525</v>
       </c>
       <c r="AF73">
-        <v>0.120684</v>
+        <v>0.19309399999999999</v>
       </c>
       <c r="AG73">
-        <v>0.116148</v>
+        <v>0.185836</v>
       </c>
       <c r="AH73">
-        <v>0.113624</v>
+        <v>0.18113000000000001</v>
       </c>
       <c r="AI73">
-        <v>9.9416000000000004E-2</v>
+        <v>0.159774</v>
       </c>
       <c r="AJ73">
-        <v>0.17931800000000001</v>
+        <v>0.28690900000000003</v>
       </c>
       <c r="AK73">
-        <v>0.17035800000000001</v>
+        <v>0.27257399999999998</v>
       </c>
       <c r="AL73">
-        <v>0.19175800000000001</v>
+        <v>0.304089</v>
       </c>
       <c r="AM73">
-        <v>0.19153200000000001</v>
+        <v>0.30341899999999999</v>
       </c>
       <c r="AN73">
-        <v>0.19069800000000001</v>
+        <v>0.30497200000000002</v>
       </c>
       <c r="AO73">
-        <v>0.180844</v>
+        <v>0.29139900000000002</v>
       </c>
       <c r="AP73">
         <v>52.634300000000003</v>
@@ -19615,58 +19615,58 @@
         <v>26.738671</v>
       </c>
       <c r="X74">
-        <v>9.5466999999999996E-2</v>
+        <v>0.15274799999999999</v>
       </c>
       <c r="Y74">
-        <v>9.5529000000000003E-2</v>
+        <v>0.150842</v>
       </c>
       <c r="Z74">
-        <v>0.105726</v>
+        <v>0.16916100000000001</v>
       </c>
       <c r="AA74">
-        <v>9.9747000000000002E-2</v>
+        <v>0.15959599999999999</v>
       </c>
       <c r="AB74">
-        <v>9.6189999999999998E-2</v>
+        <v>0.15390400000000001</v>
       </c>
       <c r="AC74">
-        <v>8.9478000000000002E-2</v>
+        <v>0.14316400000000001</v>
       </c>
       <c r="AD74">
-        <v>0.101397</v>
+        <v>0.16223499999999999</v>
       </c>
       <c r="AE74">
-        <v>9.8138000000000003E-2</v>
+        <v>0.15702099999999999</v>
       </c>
       <c r="AF74">
-        <v>0.116492</v>
+        <v>0.186387</v>
       </c>
       <c r="AG74">
-        <v>0.111121</v>
+        <v>0.17779400000000001</v>
       </c>
       <c r="AH74">
-        <v>0.111803</v>
+        <v>0.17834900000000001</v>
       </c>
       <c r="AI74">
-        <v>0.100203</v>
+        <v>0.16078600000000001</v>
       </c>
       <c r="AJ74">
-        <v>0.174403</v>
+        <v>0.27904499999999999</v>
       </c>
       <c r="AK74">
-        <v>0.16625599999999999</v>
+        <v>0.26601000000000002</v>
       </c>
       <c r="AL74">
-        <v>0.186363</v>
+        <v>0.29800199999999999</v>
       </c>
       <c r="AM74">
-        <v>0.185252</v>
+        <v>0.29653800000000002</v>
       </c>
       <c r="AN74">
-        <v>0.185863</v>
+        <v>0.29917700000000003</v>
       </c>
       <c r="AO74">
-        <v>0.18138499999999999</v>
+        <v>0.29175699999999999</v>
       </c>
       <c r="AP74">
         <v>53.276454999999999</v>
@@ -19824,58 +19824,58 @@
         <v>26.693521</v>
       </c>
       <c r="X75">
-        <v>9.1257000000000005E-2</v>
+        <v>0.146012</v>
       </c>
       <c r="Y75">
-        <v>8.9722999999999997E-2</v>
+        <v>0.142516</v>
       </c>
       <c r="Z75">
-        <v>9.6794000000000005E-2</v>
+        <v>0.15487100000000001</v>
       </c>
       <c r="AA75">
-        <v>9.6560000000000007E-2</v>
+        <v>0.15449599999999999</v>
       </c>
       <c r="AB75">
-        <v>9.6884999999999999E-2</v>
+        <v>0.15501599999999999</v>
       </c>
       <c r="AC75">
-        <v>9.5180000000000001E-2</v>
+        <v>0.15229200000000001</v>
       </c>
       <c r="AD75">
-        <v>9.8990999999999996E-2</v>
+        <v>0.158386</v>
       </c>
       <c r="AE75">
-        <v>9.4256000000000006E-2</v>
+        <v>0.150809</v>
       </c>
       <c r="AF75">
-        <v>0.106228</v>
+        <v>0.169964</v>
       </c>
       <c r="AG75">
-        <v>0.107015</v>
+        <v>0.17122399999999999</v>
       </c>
       <c r="AH75">
-        <v>0.108652</v>
+        <v>0.17372599999999999</v>
       </c>
       <c r="AI75">
-        <v>0.10115</v>
+        <v>0.16211900000000001</v>
       </c>
       <c r="AJ75">
-        <v>0.17280499999999999</v>
+        <v>0.27648899999999998</v>
       </c>
       <c r="AK75">
-        <v>0.16118499999999999</v>
+        <v>0.25789600000000001</v>
       </c>
       <c r="AL75">
-        <v>0.18099199999999999</v>
+        <v>0.29113099999999997</v>
       </c>
       <c r="AM75">
-        <v>0.18643000000000001</v>
+        <v>0.29652400000000001</v>
       </c>
       <c r="AN75">
-        <v>0.18253900000000001</v>
+        <v>0.29429300000000003</v>
       </c>
       <c r="AO75">
-        <v>0.18273</v>
+        <v>0.29294399999999998</v>
       </c>
       <c r="AP75">
         <v>54.213653000000001</v>
@@ -20033,58 +20033,58 @@
         <v>26.458656999999999</v>
       </c>
       <c r="X76">
-        <v>8.7767999999999999E-2</v>
+        <v>0.140428</v>
       </c>
       <c r="Y76">
-        <v>7.6761999999999997E-2</v>
+        <v>0.129222</v>
       </c>
       <c r="Z76">
-        <v>8.8516999999999998E-2</v>
+        <v>0.141627</v>
       </c>
       <c r="AA76">
-        <v>8.4548999999999999E-2</v>
+        <v>0.13527900000000001</v>
       </c>
       <c r="AB76">
-        <v>9.5585000000000003E-2</v>
+        <v>0.15293599999999999</v>
       </c>
       <c r="AC76">
-        <v>9.1422000000000003E-2</v>
+        <v>0.14627499999999999</v>
       </c>
       <c r="AD76">
-        <v>9.7392999999999993E-2</v>
+        <v>0.15582799999999999</v>
       </c>
       <c r="AE76">
-        <v>8.9443999999999996E-2</v>
+        <v>0.14311099999999999</v>
       </c>
       <c r="AF76">
-        <v>9.7379999999999994E-2</v>
+        <v>0.155808</v>
       </c>
       <c r="AG76">
-        <v>0.100297</v>
+        <v>0.16047600000000001</v>
       </c>
       <c r="AH76">
-        <v>0.10524699999999999</v>
+        <v>0.16878099999999999</v>
       </c>
       <c r="AI76">
-        <v>0.101643</v>
+        <v>0.16292699999999999</v>
       </c>
       <c r="AJ76">
-        <v>0.172213</v>
+        <v>0.27554000000000001</v>
       </c>
       <c r="AK76">
-        <v>0.15137900000000001</v>
+        <v>0.24220700000000001</v>
       </c>
       <c r="AL76">
-        <v>0.17302200000000001</v>
+        <v>0.282138</v>
       </c>
       <c r="AM76">
-        <v>0.178204</v>
+        <v>0.28750999999999999</v>
       </c>
       <c r="AN76">
-        <v>0.179533</v>
+        <v>0.28976600000000002</v>
       </c>
       <c r="AO76">
-        <v>0.18336</v>
+        <v>0.29371399999999998</v>
       </c>
       <c r="AP76">
         <v>55.237898000000001</v>
@@ -20242,58 +20242,58 @@
         <v>26.19623</v>
       </c>
       <c r="X77">
-        <v>8.3765999999999993E-2</v>
+        <v>0.13402500000000001</v>
       </c>
       <c r="Y77">
-        <v>6.8332000000000004E-2</v>
+        <v>0.12007</v>
       </c>
       <c r="Z77">
-        <v>8.3781999999999995E-2</v>
+        <v>0.134051</v>
       </c>
       <c r="AA77">
-        <v>8.1117999999999996E-2</v>
+        <v>0.12978899999999999</v>
       </c>
       <c r="AB77">
-        <v>9.0889999999999999E-2</v>
+        <v>0.145425</v>
       </c>
       <c r="AC77">
-        <v>9.3382999999999994E-2</v>
+        <v>0.14941499999999999</v>
       </c>
       <c r="AD77">
-        <v>9.4589999999999994E-2</v>
+        <v>0.15134400000000001</v>
       </c>
       <c r="AE77">
-        <v>8.4803000000000003E-2</v>
+        <v>0.135685</v>
       </c>
       <c r="AF77">
-        <v>9.1571E-2</v>
+        <v>0.146513</v>
       </c>
       <c r="AG77">
-        <v>9.2553999999999997E-2</v>
+        <v>0.148086</v>
       </c>
       <c r="AH77">
-        <v>0.10138900000000001</v>
+        <v>0.16327800000000001</v>
       </c>
       <c r="AI77">
-        <v>0.102825</v>
+        <v>0.16469200000000001</v>
       </c>
       <c r="AJ77">
-        <v>0.16567899999999999</v>
+        <v>0.26508700000000002</v>
       </c>
       <c r="AK77">
-        <v>0.14342099999999999</v>
+        <v>0.22947300000000001</v>
       </c>
       <c r="AL77">
-        <v>0.164491</v>
+        <v>0.27244699999999999</v>
       </c>
       <c r="AM77">
-        <v>0.168018</v>
+        <v>0.27611599999999997</v>
       </c>
       <c r="AN77">
-        <v>0.175374</v>
+        <v>0.28456599999999999</v>
       </c>
       <c r="AO77">
-        <v>0.18588299999999999</v>
+        <v>0.29603499999999999</v>
       </c>
       <c r="AP77">
         <v>56.050545</v>
@@ -20451,58 +20451,58 @@
         <v>26.116133999999999</v>
       </c>
       <c r="X78">
-        <v>8.2208000000000003E-2</v>
+        <v>0.13153200000000001</v>
       </c>
       <c r="Y78">
-        <v>6.7951999999999999E-2</v>
+        <v>0.118435</v>
       </c>
       <c r="Z78">
-        <v>8.2400000000000001E-2</v>
+        <v>0.13184000000000001</v>
       </c>
       <c r="AA78">
-        <v>8.0759999999999998E-2</v>
+        <v>0.129215</v>
       </c>
       <c r="AB78">
-        <v>8.6944999999999995E-2</v>
+        <v>0.13911299999999999</v>
       </c>
       <c r="AC78">
-        <v>9.2230000000000006E-2</v>
+        <v>0.14757000000000001</v>
       </c>
       <c r="AD78">
-        <v>9.4548999999999994E-2</v>
+        <v>0.151278</v>
       </c>
       <c r="AE78">
-        <v>8.4612000000000007E-2</v>
+        <v>0.135379</v>
       </c>
       <c r="AF78">
-        <v>9.0785000000000005E-2</v>
+        <v>0.145256</v>
       </c>
       <c r="AG78">
-        <v>8.8678000000000007E-2</v>
+        <v>0.14188500000000001</v>
       </c>
       <c r="AH78">
-        <v>9.9374000000000004E-2</v>
+        <v>0.16042500000000001</v>
       </c>
       <c r="AI78">
-        <v>0.103394</v>
+        <v>0.16555300000000001</v>
       </c>
       <c r="AJ78">
-        <v>0.162935</v>
+        <v>0.26069599999999998</v>
       </c>
       <c r="AK78">
-        <v>0.14125099999999999</v>
+        <v>0.22600100000000001</v>
       </c>
       <c r="AL78">
-        <v>0.16059899999999999</v>
+        <v>0.268013</v>
       </c>
       <c r="AM78">
-        <v>0.161774</v>
+        <v>0.26935700000000001</v>
       </c>
       <c r="AN78">
-        <v>0.172539</v>
+        <v>0.281219</v>
       </c>
       <c r="AO78">
-        <v>0.186584</v>
+        <v>0.29670800000000003</v>
       </c>
       <c r="AP78">
         <v>56.860033000000001</v>
@@ -20663,58 +20663,58 @@
         <v>29.871227999999999</v>
       </c>
       <c r="X79">
-        <v>0.100048</v>
+        <v>0.160077</v>
       </c>
       <c r="Y79">
-        <v>0.109177</v>
+        <v>0.17192399999999999</v>
       </c>
       <c r="Z79">
-        <v>8.9636999999999994E-2</v>
+        <v>0.14341999999999999</v>
       </c>
       <c r="AA79">
-        <v>8.8235999999999995E-2</v>
+        <v>0.141177</v>
       </c>
       <c r="AB79">
-        <v>9.7258999999999998E-2</v>
+        <v>0.155614</v>
       </c>
       <c r="AC79">
-        <v>0.107964</v>
+        <v>0.17275499999999999</v>
       </c>
       <c r="AD79">
-        <v>0.116245</v>
+        <v>0.18599099999999999</v>
       </c>
       <c r="AE79">
-        <v>0.11785900000000001</v>
+        <v>0.18857399999999999</v>
       </c>
       <c r="AF79">
-        <v>0.101115</v>
+        <v>0.16178400000000001</v>
       </c>
       <c r="AG79">
-        <v>0.10660500000000001</v>
+        <v>0.170569</v>
       </c>
       <c r="AH79">
-        <v>0.116836</v>
+        <v>0.185497</v>
       </c>
       <c r="AI79">
-        <v>0.11668000000000001</v>
+        <v>0.18509</v>
       </c>
       <c r="AJ79">
-        <v>0.18296399999999999</v>
+        <v>0.292742</v>
       </c>
       <c r="AK79">
-        <v>0.17675099999999999</v>
+        <v>0.28280100000000002</v>
       </c>
       <c r="AL79">
-        <v>0.17294799999999999</v>
+        <v>0.28155799999999997</v>
       </c>
       <c r="AM79">
-        <v>0.17513100000000001</v>
+        <v>0.28418700000000002</v>
       </c>
       <c r="AN79">
-        <v>0.18859200000000001</v>
+        <v>0.303226</v>
       </c>
       <c r="AO79">
-        <v>0.19731000000000001</v>
+        <v>0.30859900000000001</v>
       </c>
       <c r="AP79">
         <v>52.660507000000003</v>
@@ -20875,58 +20875,58 @@
         <v>29.745797</v>
       </c>
       <c r="X80">
-        <v>9.8197000000000007E-2</v>
+        <v>0.15711600000000001</v>
       </c>
       <c r="Y80">
-        <v>0.10416400000000001</v>
+        <v>0.166745</v>
       </c>
       <c r="Z80">
-        <v>9.0799000000000005E-2</v>
+        <v>0.14527899999999999</v>
       </c>
       <c r="AA80">
-        <v>8.9885000000000007E-2</v>
+        <v>0.143816</v>
       </c>
       <c r="AB80">
-        <v>9.6357999999999999E-2</v>
+        <v>0.154172</v>
       </c>
       <c r="AC80">
-        <v>0.106672</v>
+        <v>0.17068700000000001</v>
       </c>
       <c r="AD80">
-        <v>0.113598</v>
+        <v>0.181756</v>
       </c>
       <c r="AE80">
-        <v>0.11523</v>
+        <v>0.184367</v>
       </c>
       <c r="AF80">
-        <v>0.104088</v>
+        <v>0.16653999999999999</v>
       </c>
       <c r="AG80">
-        <v>0.10899499999999999</v>
+        <v>0.17439199999999999</v>
       </c>
       <c r="AH80">
-        <v>0.116593</v>
+        <v>0.18541299999999999</v>
       </c>
       <c r="AI80">
-        <v>0.1149</v>
+        <v>0.182536</v>
       </c>
       <c r="AJ80">
-        <v>0.183421</v>
+        <v>0.29347299999999998</v>
       </c>
       <c r="AK80">
-        <v>0.17607500000000001</v>
+        <v>0.281721</v>
       </c>
       <c r="AL80">
-        <v>0.17533199999999999</v>
+        <v>0.28413899999999997</v>
       </c>
       <c r="AM80">
-        <v>0.18018600000000001</v>
+        <v>0.29009000000000001</v>
       </c>
       <c r="AN80">
-        <v>0.18756200000000001</v>
+        <v>0.30334299999999997</v>
       </c>
       <c r="AO80">
-        <v>0.19484399999999999</v>
+        <v>0.30649900000000002</v>
       </c>
       <c r="AP80">
         <v>52.410794000000003</v>
@@ -21087,58 +21087,58 @@
         <v>29.306874000000001</v>
       </c>
       <c r="X81">
-        <v>9.6243999999999996E-2</v>
+        <v>0.15398999999999999</v>
       </c>
       <c r="Y81">
-        <v>0.10076599999999999</v>
+        <v>0.161158</v>
       </c>
       <c r="Z81">
-        <v>9.5167000000000002E-2</v>
+        <v>0.15226799999999999</v>
       </c>
       <c r="AA81">
-        <v>0.10526099999999999</v>
+        <v>0.16841800000000001</v>
       </c>
       <c r="AB81">
-        <v>0.100124</v>
+        <v>0.16019800000000001</v>
       </c>
       <c r="AC81">
-        <v>9.8759E-2</v>
+        <v>0.15801899999999999</v>
       </c>
       <c r="AD81">
-        <v>0.10989400000000001</v>
+        <v>0.17583099999999999</v>
       </c>
       <c r="AE81">
-        <v>0.109857</v>
+        <v>0.17577100000000001</v>
       </c>
       <c r="AF81">
-        <v>0.107166</v>
+        <v>0.17146500000000001</v>
       </c>
       <c r="AG81">
-        <v>0.119811</v>
+        <v>0.19169800000000001</v>
       </c>
       <c r="AH81">
-        <v>0.11686199999999999</v>
+        <v>0.18593100000000001</v>
       </c>
       <c r="AI81">
-        <v>0.110357</v>
+        <v>0.17605299999999999</v>
       </c>
       <c r="AJ81">
-        <v>0.18555099999999999</v>
+        <v>0.29688199999999998</v>
       </c>
       <c r="AK81">
-        <v>0.17061999999999999</v>
+        <v>0.27299299999999999</v>
       </c>
       <c r="AL81">
-        <v>0.17666999999999999</v>
+        <v>0.286383</v>
       </c>
       <c r="AM81">
-        <v>0.19384000000000001</v>
+        <v>0.30554700000000001</v>
       </c>
       <c r="AN81">
-        <v>0.19078100000000001</v>
+        <v>0.307035</v>
       </c>
       <c r="AO81">
-        <v>0.190109</v>
+        <v>0.302201</v>
       </c>
       <c r="AP81">
         <v>51.829605999999998</v>
@@ -21299,58 +21299,58 @@
         <v>29.117522999999998</v>
       </c>
       <c r="X82">
-        <v>9.4753000000000004E-2</v>
+        <v>0.15160399999999999</v>
       </c>
       <c r="Y82">
-        <v>9.7403000000000003E-2</v>
+        <v>0.15603300000000001</v>
       </c>
       <c r="Z82">
-        <v>0.10113800000000001</v>
+        <v>0.16182099999999999</v>
       </c>
       <c r="AA82">
-        <v>0.110821</v>
+        <v>0.177313</v>
       </c>
       <c r="AB82">
-        <v>0.102698</v>
+        <v>0.16431699999999999</v>
       </c>
       <c r="AC82">
-        <v>9.4130000000000005E-2</v>
+        <v>0.15060699999999999</v>
       </c>
       <c r="AD82">
-        <v>0.106542</v>
+        <v>0.17046800000000001</v>
       </c>
       <c r="AE82">
-        <v>0.104528</v>
+        <v>0.167245</v>
       </c>
       <c r="AF82">
-        <v>0.11068699999999999</v>
+        <v>0.17710000000000001</v>
       </c>
       <c r="AG82">
-        <v>0.12298000000000001</v>
+        <v>0.196768</v>
       </c>
       <c r="AH82">
-        <v>0.117034</v>
+        <v>0.18617700000000001</v>
       </c>
       <c r="AI82">
-        <v>0.107422</v>
+        <v>0.171706</v>
       </c>
       <c r="AJ82">
-        <v>0.18357699999999999</v>
+        <v>0.29372399999999999</v>
       </c>
       <c r="AK82">
-        <v>0.16609599999999999</v>
+        <v>0.26575399999999999</v>
       </c>
       <c r="AL82">
-        <v>0.18038999999999999</v>
+        <v>0.29133100000000001</v>
       </c>
       <c r="AM82">
-        <v>0.20185600000000001</v>
+        <v>0.31503900000000001</v>
       </c>
       <c r="AN82">
-        <v>0.19606799999999999</v>
+        <v>0.31207699999999999</v>
       </c>
       <c r="AO82">
-        <v>0.18809100000000001</v>
+        <v>0.29995899999999998</v>
       </c>
       <c r="AP82">
         <v>51.609923999999999</v>
@@ -21511,58 +21511,58 @@
         <v>28.876951999999999</v>
       </c>
       <c r="X83">
-        <v>9.5256999999999994E-2</v>
+        <v>0.15240999999999999</v>
       </c>
       <c r="Y83">
-        <v>9.5382999999999996E-2</v>
+        <v>0.151949</v>
       </c>
       <c r="Z83">
-        <v>0.11264</v>
+        <v>0.180225</v>
       </c>
       <c r="AA83">
-        <v>0.116295</v>
+        <v>0.18607299999999999</v>
       </c>
       <c r="AB83">
-        <v>0.10694099999999999</v>
+        <v>0.17110600000000001</v>
       </c>
       <c r="AC83">
-        <v>9.5746999999999999E-2</v>
+        <v>0.153198</v>
       </c>
       <c r="AD83">
-        <v>0.104537</v>
+        <v>0.16725999999999999</v>
       </c>
       <c r="AE83">
-        <v>0.100591</v>
+        <v>0.160945</v>
       </c>
       <c r="AF83">
-        <v>0.119129</v>
+        <v>0.190606</v>
       </c>
       <c r="AG83">
-        <v>0.123319</v>
+        <v>0.19731099999999999</v>
       </c>
       <c r="AH83">
-        <v>0.117246</v>
+        <v>0.18632499999999999</v>
       </c>
       <c r="AI83">
-        <v>0.10582</v>
+        <v>0.16916700000000001</v>
       </c>
       <c r="AJ83">
-        <v>0.18204699999999999</v>
+        <v>0.29127500000000001</v>
       </c>
       <c r="AK83">
-        <v>0.16376099999999999</v>
+        <v>0.26201799999999997</v>
       </c>
       <c r="AL83">
-        <v>0.19756399999999999</v>
+        <v>0.31037999999999999</v>
       </c>
       <c r="AM83">
-        <v>0.20211999999999999</v>
+        <v>0.31555299999999997</v>
       </c>
       <c r="AN83">
-        <v>0.19998299999999999</v>
+        <v>0.31537799999999999</v>
       </c>
       <c r="AO83">
-        <v>0.187361</v>
+        <v>0.29869600000000002</v>
       </c>
       <c r="AP83">
         <v>51.917831999999997</v>
@@ -21723,58 +21723,58 @@
         <v>28.433926</v>
       </c>
       <c r="X84">
-        <v>9.3838000000000005E-2</v>
+        <v>0.15014</v>
       </c>
       <c r="Y84">
-        <v>9.1699000000000003E-2</v>
+        <v>0.146425</v>
       </c>
       <c r="Z84">
-        <v>0.11219999999999999</v>
+        <v>0.17952099999999999</v>
       </c>
       <c r="AA84">
-        <v>0.114844</v>
+        <v>0.183751</v>
       </c>
       <c r="AB84">
-        <v>0.10512299999999999</v>
+        <v>0.16819700000000001</v>
       </c>
       <c r="AC84">
-        <v>9.3465000000000006E-2</v>
+        <v>0.14954200000000001</v>
       </c>
       <c r="AD84">
-        <v>0.103007</v>
+        <v>0.16481100000000001</v>
       </c>
       <c r="AE84">
-        <v>9.7171999999999994E-2</v>
+        <v>0.155474</v>
       </c>
       <c r="AF84">
-        <v>0.11787499999999999</v>
+        <v>0.18860099999999999</v>
       </c>
       <c r="AG84">
-        <v>0.119147</v>
+        <v>0.190635</v>
       </c>
       <c r="AH84">
-        <v>0.11575299999999999</v>
+        <v>0.18409600000000001</v>
       </c>
       <c r="AI84">
-        <v>0.1042</v>
+        <v>0.166655</v>
       </c>
       <c r="AJ84">
-        <v>0.17916399999999999</v>
+        <v>0.286663</v>
       </c>
       <c r="AK84">
-        <v>0.16365099999999999</v>
+        <v>0.26184200000000002</v>
       </c>
       <c r="AL84">
-        <v>0.19934299999999999</v>
+        <v>0.31287300000000001</v>
       </c>
       <c r="AM84">
-        <v>0.200047</v>
+        <v>0.31362099999999998</v>
       </c>
       <c r="AN84">
-        <v>0.19853499999999999</v>
+        <v>0.31352000000000002</v>
       </c>
       <c r="AO84">
-        <v>0.186583</v>
+        <v>0.297375</v>
       </c>
       <c r="AP84">
         <v>52.672466999999997</v>
@@ -21935,58 +21935,58 @@
         <v>28.080532999999999</v>
       </c>
       <c r="X85">
-        <v>9.0491000000000002E-2</v>
+        <v>0.144786</v>
       </c>
       <c r="Y85">
-        <v>8.8467000000000004E-2</v>
+        <v>0.139268</v>
       </c>
       <c r="Z85">
-        <v>0.10166600000000001</v>
+        <v>0.162665</v>
       </c>
       <c r="AA85">
-        <v>0.10523100000000001</v>
+        <v>0.16836899999999999</v>
       </c>
       <c r="AB85">
-        <v>0.100559</v>
+        <v>0.16089400000000001</v>
       </c>
       <c r="AC85">
-        <v>0.10012799999999999</v>
+        <v>0.16021199999999999</v>
       </c>
       <c r="AD85">
-        <v>0.101462</v>
+        <v>0.16233900000000001</v>
       </c>
       <c r="AE85">
-        <v>9.5576999999999995E-2</v>
+        <v>0.152923</v>
       </c>
       <c r="AF85">
-        <v>0.108464</v>
+        <v>0.173543</v>
       </c>
       <c r="AG85">
-        <v>0.11518200000000001</v>
+        <v>0.18429100000000001</v>
       </c>
       <c r="AH85">
-        <v>0.11382</v>
+        <v>0.18115500000000001</v>
       </c>
       <c r="AI85">
-        <v>0.103216</v>
+        <v>0.16502700000000001</v>
       </c>
       <c r="AJ85">
-        <v>0.17562800000000001</v>
+        <v>0.281005</v>
       </c>
       <c r="AK85">
-        <v>0.16220100000000001</v>
+        <v>0.25952199999999997</v>
       </c>
       <c r="AL85">
-        <v>0.18857399999999999</v>
+        <v>0.30033399999999999</v>
       </c>
       <c r="AM85">
-        <v>0.19400800000000001</v>
+        <v>0.30638599999999999</v>
       </c>
       <c r="AN85">
-        <v>0.19492200000000001</v>
+        <v>0.30894500000000003</v>
       </c>
       <c r="AO85">
-        <v>0.18507799999999999</v>
+        <v>0.29543399999999997</v>
       </c>
       <c r="AP85">
         <v>53.530177000000002</v>
@@ -22147,58 +22147,58 @@
         <v>27.680022000000001</v>
       </c>
       <c r="X86">
-        <v>8.4005999999999997E-2</v>
+        <v>0.134409</v>
       </c>
       <c r="Y86">
-        <v>7.6163999999999996E-2</v>
+        <v>0.124948</v>
       </c>
       <c r="Z86">
-        <v>8.6024000000000003E-2</v>
+        <v>0.13763700000000001</v>
       </c>
       <c r="AA86">
-        <v>9.2787999999999995E-2</v>
+        <v>0.14846000000000001</v>
       </c>
       <c r="AB86">
-        <v>9.6926999999999999E-2</v>
+        <v>0.155083</v>
       </c>
       <c r="AC86">
-        <v>9.4187999999999994E-2</v>
+        <v>0.150704</v>
       </c>
       <c r="AD86">
-        <v>9.8109000000000002E-2</v>
+        <v>0.156974</v>
       </c>
       <c r="AE86">
-        <v>9.2000999999999999E-2</v>
+        <v>0.147201</v>
       </c>
       <c r="AF86">
-        <v>9.7058000000000005E-2</v>
+        <v>0.15529399999999999</v>
       </c>
       <c r="AG86">
-        <v>0.112362</v>
+        <v>0.17977899999999999</v>
       </c>
       <c r="AH86">
-        <v>0.11226899999999999</v>
+        <v>0.17872099999999999</v>
       </c>
       <c r="AI86">
-        <v>0.101956</v>
+        <v>0.16305900000000001</v>
       </c>
       <c r="AJ86">
-        <v>0.17049800000000001</v>
+        <v>0.27279700000000001</v>
       </c>
       <c r="AK86">
-        <v>0.154778</v>
+        <v>0.247645</v>
       </c>
       <c r="AL86">
-        <v>0.173126</v>
+        <v>0.28238799999999997</v>
       </c>
       <c r="AM86">
-        <v>0.186525</v>
+        <v>0.29780899999999999</v>
       </c>
       <c r="AN86">
-        <v>0.19225300000000001</v>
+        <v>0.30466500000000002</v>
       </c>
       <c r="AO86">
-        <v>0.182563</v>
+        <v>0.29270299999999999</v>
       </c>
       <c r="AP86">
         <v>54.536377000000002</v>
@@ -22359,58 +22359,58 @@
         <v>27.008975</v>
       </c>
       <c r="X87">
-        <v>8.0116999999999994E-2</v>
+        <v>0.128187</v>
       </c>
       <c r="Y87">
-        <v>6.6539000000000001E-2</v>
+        <v>0.113327</v>
       </c>
       <c r="Z87">
-        <v>7.8025999999999998E-2</v>
+        <v>0.12484099999999999</v>
       </c>
       <c r="AA87">
-        <v>9.0993000000000004E-2</v>
+        <v>0.145589</v>
       </c>
       <c r="AB87">
-        <v>9.4765000000000002E-2</v>
+        <v>0.15162400000000001</v>
       </c>
       <c r="AC87">
-        <v>8.4778999999999993E-2</v>
+        <v>0.13564100000000001</v>
       </c>
       <c r="AD87">
-        <v>9.5651E-2</v>
+        <v>0.15304100000000001</v>
       </c>
       <c r="AE87">
-        <v>8.7105000000000002E-2</v>
+        <v>0.13936799999999999</v>
       </c>
       <c r="AF87">
-        <v>9.0728000000000003E-2</v>
+        <v>0.14516499999999999</v>
       </c>
       <c r="AG87">
-        <v>0.11057</v>
+        <v>0.17691200000000001</v>
       </c>
       <c r="AH87">
-        <v>0.10999100000000001</v>
+        <v>0.17530599999999999</v>
       </c>
       <c r="AI87">
-        <v>9.8907999999999996E-2</v>
+        <v>0.15876899999999999</v>
       </c>
       <c r="AJ87">
-        <v>0.16871700000000001</v>
+        <v>0.26994699999999999</v>
       </c>
       <c r="AK87">
-        <v>0.14768400000000001</v>
+        <v>0.236294</v>
       </c>
       <c r="AL87">
-        <v>0.166821</v>
+        <v>0.27520800000000001</v>
       </c>
       <c r="AM87">
-        <v>0.18243899999999999</v>
+        <v>0.29285800000000001</v>
       </c>
       <c r="AN87">
-        <v>0.19020300000000001</v>
+        <v>0.30077300000000001</v>
       </c>
       <c r="AO87">
-        <v>0.17883199999999999</v>
+        <v>0.28915400000000002</v>
       </c>
       <c r="AP87">
         <v>55.537951999999997</v>
@@ -22571,58 +22571,58 @@
         <v>26.842728000000001</v>
       </c>
       <c r="X88">
-        <v>7.7700000000000005E-2</v>
+        <v>0.12432</v>
       </c>
       <c r="Y88">
-        <v>6.3320000000000001E-2</v>
+        <v>0.108138</v>
       </c>
       <c r="Z88">
-        <v>7.8281000000000003E-2</v>
+        <v>0.125249</v>
       </c>
       <c r="AA88">
-        <v>9.2862E-2</v>
+        <v>0.14857899999999999</v>
       </c>
       <c r="AB88">
-        <v>9.5408000000000007E-2</v>
+        <v>0.15265200000000001</v>
       </c>
       <c r="AC88">
-        <v>8.9486999999999997E-2</v>
+        <v>0.143179</v>
       </c>
       <c r="AD88">
-        <v>9.4383999999999996E-2</v>
+        <v>0.15101400000000001</v>
       </c>
       <c r="AE88">
-        <v>8.3902000000000004E-2</v>
+        <v>0.134243</v>
       </c>
       <c r="AF88">
-        <v>9.3965000000000007E-2</v>
+        <v>0.15034400000000001</v>
       </c>
       <c r="AG88">
-        <v>0.113251</v>
+        <v>0.181202</v>
       </c>
       <c r="AH88">
-        <v>0.10778600000000001</v>
+        <v>0.172046</v>
       </c>
       <c r="AI88">
-        <v>9.9770999999999999E-2</v>
+        <v>0.15984300000000001</v>
       </c>
       <c r="AJ88">
-        <v>0.16565199999999999</v>
+        <v>0.26504299999999997</v>
       </c>
       <c r="AK88">
-        <v>0.141758</v>
+        <v>0.22681299999999999</v>
       </c>
       <c r="AL88">
-        <v>0.173397</v>
+        <v>0.282086</v>
       </c>
       <c r="AM88">
-        <v>0.18615000000000001</v>
+        <v>0.295904</v>
       </c>
       <c r="AN88">
-        <v>0.18759799999999999</v>
+        <v>0.29638900000000001</v>
       </c>
       <c r="AO88">
-        <v>0.180085</v>
+        <v>0.28978799999999999</v>
       </c>
       <c r="AP88">
         <v>56.302576000000002</v>
@@ -22783,58 +22783,58 @@
         <v>26.825106000000002</v>
       </c>
       <c r="X89">
-        <v>7.7426999999999996E-2</v>
+        <v>0.12388299999999999</v>
       </c>
       <c r="Y89">
-        <v>6.4665E-2</v>
+        <v>0.10911999999999999</v>
       </c>
       <c r="Z89">
-        <v>8.0917000000000003E-2</v>
+        <v>0.129467</v>
       </c>
       <c r="AA89">
-        <v>9.4211000000000003E-2</v>
+        <v>0.15073800000000001</v>
       </c>
       <c r="AB89">
-        <v>9.5929E-2</v>
+        <v>0.15348700000000001</v>
       </c>
       <c r="AC89">
-        <v>9.0895000000000004E-2</v>
+        <v>0.14543300000000001</v>
       </c>
       <c r="AD89">
-        <v>9.3829999999999997E-2</v>
+        <v>0.15012800000000001</v>
       </c>
       <c r="AE89">
-        <v>8.3960000000000007E-2</v>
+        <v>0.13433500000000001</v>
       </c>
       <c r="AF89">
-        <v>9.8044000000000006E-2</v>
+        <v>0.15687100000000001</v>
       </c>
       <c r="AG89">
-        <v>0.114203</v>
+        <v>0.182726</v>
       </c>
       <c r="AH89">
-        <v>0.10632</v>
+        <v>0.16995299999999999</v>
       </c>
       <c r="AI89">
-        <v>0.10054200000000001</v>
+        <v>0.16089400000000001</v>
       </c>
       <c r="AJ89">
-        <v>0.164379</v>
+        <v>0.26300600000000002</v>
       </c>
       <c r="AK89">
-        <v>0.14211699999999999</v>
+        <v>0.22738700000000001</v>
       </c>
       <c r="AL89">
-        <v>0.178061</v>
+        <v>0.28719</v>
       </c>
       <c r="AM89">
-        <v>0.186719</v>
+        <v>0.29628399999999999</v>
       </c>
       <c r="AN89">
-        <v>0.184726</v>
+        <v>0.29270000000000002</v>
       </c>
       <c r="AO89">
-        <v>0.18080299999999999</v>
+        <v>0.29025400000000001</v>
       </c>
       <c r="AP89">
         <v>56.583643000000002</v>
@@ -22992,58 +22992,58 @@
         <v>30.313134999999999</v>
       </c>
       <c r="X90">
-        <v>0.102092</v>
+        <v>0.16334899999999999</v>
       </c>
       <c r="Y90">
-        <v>0.107168</v>
+        <v>0.168353</v>
       </c>
       <c r="Z90">
-        <v>9.1157000000000002E-2</v>
+        <v>0.14585100000000001</v>
       </c>
       <c r="AA90">
-        <v>9.3246999999999997E-2</v>
+        <v>0.14919499999999999</v>
       </c>
       <c r="AB90">
-        <v>0.10219</v>
+        <v>0.16350400000000001</v>
       </c>
       <c r="AC90">
-        <v>0.10018100000000001</v>
+        <v>0.16029399999999999</v>
       </c>
       <c r="AD90">
-        <v>0.11537</v>
+        <v>0.18459200000000001</v>
       </c>
       <c r="AE90">
-        <v>0.115776</v>
+        <v>0.18524199999999999</v>
       </c>
       <c r="AF90">
-        <v>9.9955000000000002E-2</v>
+        <v>0.15992799999999999</v>
       </c>
       <c r="AG90">
-        <v>0.107955</v>
+        <v>0.17272699999999999</v>
       </c>
       <c r="AH90">
-        <v>0.120267</v>
+        <v>0.18995300000000001</v>
       </c>
       <c r="AI90">
-        <v>0.116566</v>
+        <v>0.18521299999999999</v>
       </c>
       <c r="AJ90">
-        <v>0.18391399999999999</v>
+        <v>0.29426200000000002</v>
       </c>
       <c r="AK90">
-        <v>0.17727699999999999</v>
+        <v>0.28364299999999998</v>
       </c>
       <c r="AL90">
-        <v>0.17333399999999999</v>
+        <v>0.28212100000000001</v>
       </c>
       <c r="AM90">
-        <v>0.17213000000000001</v>
+        <v>0.27986499999999997</v>
       </c>
       <c r="AN90">
-        <v>0.19267000000000001</v>
+        <v>0.305649</v>
       </c>
       <c r="AO90">
-        <v>0.19825899999999999</v>
+        <v>0.31033100000000002</v>
       </c>
       <c r="AP90">
         <v>52.018991999999997</v>
@@ -23201,58 +23201,58 @@
         <v>30.078702</v>
       </c>
       <c r="X91">
-        <v>9.9093000000000001E-2</v>
+        <v>0.158549</v>
       </c>
       <c r="Y91">
-        <v>0.10406700000000001</v>
+        <v>0.16477900000000001</v>
       </c>
       <c r="Z91">
-        <v>9.3197000000000002E-2</v>
+        <v>0.149115</v>
       </c>
       <c r="AA91">
-        <v>9.7586999999999993E-2</v>
+        <v>0.156139</v>
       </c>
       <c r="AB91">
-        <v>0.102128</v>
+        <v>0.16340499999999999</v>
       </c>
       <c r="AC91">
-        <v>9.8712999999999995E-2</v>
+        <v>0.157944</v>
       </c>
       <c r="AD91">
-        <v>0.112687</v>
+        <v>0.18029999999999999</v>
       </c>
       <c r="AE91">
-        <v>0.114039</v>
+        <v>0.18246299999999999</v>
       </c>
       <c r="AF91">
-        <v>0.105465</v>
+        <v>0.16874400000000001</v>
       </c>
       <c r="AG91">
-        <v>0.11221200000000001</v>
+        <v>0.179539</v>
       </c>
       <c r="AH91">
-        <v>0.11938</v>
+        <v>0.18895500000000001</v>
       </c>
       <c r="AI91">
-        <v>0.11360199999999999</v>
+        <v>0.18104700000000001</v>
       </c>
       <c r="AJ91">
-        <v>0.18284</v>
+        <v>0.29254400000000003</v>
       </c>
       <c r="AK91">
-        <v>0.17580299999999999</v>
+        <v>0.28128500000000001</v>
       </c>
       <c r="AL91">
-        <v>0.17765300000000001</v>
+        <v>0.28660099999999999</v>
       </c>
       <c r="AM91">
-        <v>0.17843000000000001</v>
+        <v>0.286522</v>
       </c>
       <c r="AN91">
-        <v>0.19300899999999999</v>
+        <v>0.30671199999999998</v>
       </c>
       <c r="AO91">
-        <v>0.19505800000000001</v>
+        <v>0.30769400000000002</v>
       </c>
       <c r="AP91">
         <v>51.912509999999997</v>
@@ -23410,58 +23410,58 @@
         <v>29.451902</v>
       </c>
       <c r="X92">
-        <v>9.5558000000000004E-2</v>
+        <v>0.152892</v>
       </c>
       <c r="Y92">
-        <v>0.100187</v>
+        <v>0.15933900000000001</v>
       </c>
       <c r="Z92">
-        <v>9.3356999999999996E-2</v>
+        <v>0.149372</v>
       </c>
       <c r="AA92">
-        <v>9.8600999999999994E-2</v>
+        <v>0.15776200000000001</v>
       </c>
       <c r="AB92">
-        <v>9.8662E-2</v>
+        <v>0.157859</v>
       </c>
       <c r="AC92">
-        <v>9.2494999999999994E-2</v>
+        <v>0.14799200000000001</v>
       </c>
       <c r="AD92">
-        <v>0.109932</v>
+        <v>0.17589099999999999</v>
       </c>
       <c r="AE92">
-        <v>0.11105</v>
+        <v>0.17768</v>
       </c>
       <c r="AF92">
-        <v>0.109171</v>
+        <v>0.17467299999999999</v>
       </c>
       <c r="AG92">
-        <v>0.111042</v>
+        <v>0.17766799999999999</v>
       </c>
       <c r="AH92">
-        <v>0.117067</v>
+        <v>0.18589600000000001</v>
       </c>
       <c r="AI92">
-        <v>0.1084</v>
+        <v>0.173649</v>
       </c>
       <c r="AJ92">
-        <v>0.18353</v>
+        <v>0.29364800000000002</v>
       </c>
       <c r="AK92">
-        <v>0.17208200000000001</v>
+        <v>0.27533099999999999</v>
       </c>
       <c r="AL92">
-        <v>0.179427</v>
+        <v>0.288941</v>
       </c>
       <c r="AM92">
-        <v>0.183032</v>
+        <v>0.292495</v>
       </c>
       <c r="AN92">
-        <v>0.193019</v>
+        <v>0.30777500000000002</v>
       </c>
       <c r="AO92">
-        <v>0.18917200000000001</v>
+        <v>0.30251499999999998</v>
       </c>
       <c r="AP92">
         <v>51.894419999999997</v>
@@ -23619,58 +23619,58 @@
         <v>29.177109000000002</v>
       </c>
       <c r="X93">
-        <v>9.3432000000000001E-2</v>
+        <v>0.14949100000000001</v>
       </c>
       <c r="Y93">
-        <v>9.6285999999999997E-2</v>
+        <v>0.153557</v>
       </c>
       <c r="Z93">
-        <v>9.1155E-2</v>
+        <v>0.14584800000000001</v>
       </c>
       <c r="AA93">
-        <v>9.5449000000000006E-2</v>
+        <v>0.15271899999999999</v>
       </c>
       <c r="AB93">
-        <v>9.5746999999999999E-2</v>
+        <v>0.153195</v>
       </c>
       <c r="AC93">
-        <v>9.0552999999999995E-2</v>
+        <v>0.14488300000000001</v>
       </c>
       <c r="AD93">
-        <v>0.10749</v>
+        <v>0.171985</v>
       </c>
       <c r="AE93">
-        <v>0.10727</v>
+        <v>0.17163200000000001</v>
       </c>
       <c r="AF93">
-        <v>0.106541</v>
+        <v>0.17046600000000001</v>
       </c>
       <c r="AG93">
-        <v>0.106519</v>
+        <v>0.170431</v>
       </c>
       <c r="AH93">
-        <v>0.11522399999999999</v>
+        <v>0.18337000000000001</v>
       </c>
       <c r="AI93">
-        <v>0.105999</v>
+        <v>0.17002</v>
       </c>
       <c r="AJ93">
-        <v>0.186169</v>
+        <v>0.297871</v>
       </c>
       <c r="AK93">
-        <v>0.171039</v>
+        <v>0.27366200000000002</v>
       </c>
       <c r="AL93">
-        <v>0.17530200000000001</v>
+        <v>0.28549999999999998</v>
       </c>
       <c r="AM93">
-        <v>0.18462700000000001</v>
+        <v>0.29547800000000002</v>
       </c>
       <c r="AN93">
-        <v>0.195911</v>
+        <v>0.31115700000000002</v>
       </c>
       <c r="AO93">
-        <v>0.186829</v>
+        <v>0.300016</v>
       </c>
       <c r="AP93">
         <v>51.923054</v>
@@ -23828,58 +23828,58 @@
         <v>29.548131999999999</v>
       </c>
       <c r="X94">
-        <v>9.2365000000000003E-2</v>
+        <v>0.147785</v>
       </c>
       <c r="Y94">
-        <v>9.2031000000000002E-2</v>
+        <v>0.14738899999999999</v>
       </c>
       <c r="Z94">
-        <v>9.7241999999999995E-2</v>
+        <v>0.155587</v>
       </c>
       <c r="AA94">
-        <v>0.10082000000000001</v>
+        <v>0.16131300000000001</v>
       </c>
       <c r="AB94">
-        <v>9.9554000000000004E-2</v>
+        <v>0.15928600000000001</v>
       </c>
       <c r="AC94">
-        <v>9.5564999999999997E-2</v>
+        <v>0.15290500000000001</v>
       </c>
       <c r="AD94">
-        <v>0.10526199999999999</v>
+        <v>0.16841999999999999</v>
       </c>
       <c r="AE94">
-        <v>0.103049</v>
+        <v>0.164878</v>
       </c>
       <c r="AF94">
-        <v>0.111626</v>
+        <v>0.17860100000000001</v>
       </c>
       <c r="AG94">
-        <v>0.11392099999999999</v>
+        <v>0.18227299999999999</v>
       </c>
       <c r="AH94">
-        <v>0.115283</v>
+        <v>0.18331700000000001</v>
       </c>
       <c r="AI94">
-        <v>0.107234</v>
+        <v>0.17136699999999999</v>
       </c>
       <c r="AJ94">
-        <v>0.18344299999999999</v>
+        <v>0.29350900000000002</v>
       </c>
       <c r="AK94">
-        <v>0.16697699999999999</v>
+        <v>0.26716299999999998</v>
       </c>
       <c r="AL94">
-        <v>0.186143</v>
+        <v>0.29752400000000001</v>
       </c>
       <c r="AM94">
-        <v>0.19135199999999999</v>
+        <v>0.30313000000000001</v>
       </c>
       <c r="AN94">
-        <v>0.20094200000000001</v>
+        <v>0.31574400000000002</v>
       </c>
       <c r="AO94">
-        <v>0.18897900000000001</v>
+        <v>0.30108200000000002</v>
       </c>
       <c r="AP94">
         <v>52.121597999999999</v>
@@ -24037,58 +24037,58 @@
         <v>29.610211</v>
       </c>
       <c r="X95">
-        <v>9.035E-2</v>
+        <v>0.14455999999999999</v>
       </c>
       <c r="Y95">
-        <v>8.9051000000000005E-2</v>
+        <v>0.141594</v>
       </c>
       <c r="Z95">
-        <v>9.6270999999999995E-2</v>
+        <v>0.154034</v>
       </c>
       <c r="AA95">
-        <v>9.6791000000000002E-2</v>
+        <v>0.154866</v>
       </c>
       <c r="AB95">
-        <v>9.7134999999999999E-2</v>
+        <v>0.155416</v>
       </c>
       <c r="AC95">
-        <v>9.9350999999999995E-2</v>
+        <v>0.158967</v>
       </c>
       <c r="AD95">
-        <v>0.102378</v>
+        <v>0.16380500000000001</v>
       </c>
       <c r="AE95">
-        <v>9.9337999999999996E-2</v>
+        <v>0.15894</v>
       </c>
       <c r="AF95">
-        <v>0.108305</v>
+        <v>0.173287</v>
       </c>
       <c r="AG95">
-        <v>0.110293</v>
+        <v>0.17646899999999999</v>
       </c>
       <c r="AH95">
-        <v>0.114062</v>
+        <v>0.18146100000000001</v>
       </c>
       <c r="AI95">
-        <v>0.107542</v>
+        <v>0.171461</v>
       </c>
       <c r="AJ95">
-        <v>0.18076200000000001</v>
+        <v>0.289219</v>
       </c>
       <c r="AK95">
-        <v>0.16506699999999999</v>
+        <v>0.26410699999999998</v>
       </c>
       <c r="AL95">
-        <v>0.18643799999999999</v>
+        <v>0.29830600000000002</v>
       </c>
       <c r="AM95">
-        <v>0.19018199999999999</v>
+        <v>0.302589</v>
       </c>
       <c r="AN95">
-        <v>0.20052200000000001</v>
+        <v>0.31510100000000002</v>
       </c>
       <c r="AO95">
-        <v>0.19042400000000001</v>
+        <v>0.30142099999999999</v>
       </c>
       <c r="AP95">
         <v>52.606290999999999</v>
@@ -24246,58 +24246,58 @@
         <v>29.414059000000002</v>
       </c>
       <c r="X96">
-        <v>8.6342000000000002E-2</v>
+        <v>0.13814799999999999</v>
       </c>
       <c r="Y96">
-        <v>8.4287000000000001E-2</v>
+        <v>0.13430800000000001</v>
       </c>
       <c r="Z96">
-        <v>9.2715000000000006E-2</v>
+        <v>0.148344</v>
       </c>
       <c r="AA96">
-        <v>9.7536999999999999E-2</v>
+        <v>0.156059</v>
       </c>
       <c r="AB96">
-        <v>9.4961000000000004E-2</v>
+        <v>0.15193699999999999</v>
       </c>
       <c r="AC96">
-        <v>9.7000000000000003E-2</v>
+        <v>0.15520300000000001</v>
       </c>
       <c r="AD96">
-        <v>0.100144</v>
+        <v>0.16023000000000001</v>
       </c>
       <c r="AE96">
-        <v>9.6461000000000005E-2</v>
+        <v>0.154338</v>
       </c>
       <c r="AF96">
-        <v>0.104904</v>
+        <v>0.167846</v>
       </c>
       <c r="AG96">
-        <v>0.111738</v>
+        <v>0.178781</v>
       </c>
       <c r="AH96">
-        <v>0.112162</v>
+        <v>0.178596</v>
       </c>
       <c r="AI96">
-        <v>0.106085</v>
+        <v>0.169123</v>
       </c>
       <c r="AJ96">
-        <v>0.17722499999999999</v>
+        <v>0.28355999999999998</v>
       </c>
       <c r="AK96">
-        <v>0.16329199999999999</v>
+        <v>0.26126700000000003</v>
       </c>
       <c r="AL96">
-        <v>0.18639700000000001</v>
+        <v>0.29804000000000003</v>
       </c>
       <c r="AM96">
-        <v>0.191549</v>
+        <v>0.30377500000000002</v>
       </c>
       <c r="AN96">
-        <v>0.19689599999999999</v>
+        <v>0.31068000000000001</v>
       </c>
       <c r="AO96">
-        <v>0.188834</v>
+        <v>0.29913499999999998</v>
       </c>
       <c r="AP96">
         <v>53.167481000000002</v>
@@ -24455,58 +24455,58 @@
         <v>28.759276</v>
       </c>
       <c r="X97">
-        <v>8.0866999999999994E-2</v>
+        <v>0.129387</v>
       </c>
       <c r="Y97">
-        <v>7.7688999999999994E-2</v>
+        <v>0.12562699999999999</v>
       </c>
       <c r="Z97">
-        <v>8.8720999999999994E-2</v>
+        <v>0.141953</v>
       </c>
       <c r="AA97">
-        <v>9.7193000000000002E-2</v>
+        <v>0.15550900000000001</v>
       </c>
       <c r="AB97">
-        <v>9.0457999999999997E-2</v>
+        <v>0.144733</v>
       </c>
       <c r="AC97">
-        <v>9.0806999999999999E-2</v>
+        <v>0.145292</v>
       </c>
       <c r="AD97">
-        <v>9.6128000000000005E-2</v>
+        <v>0.153805</v>
       </c>
       <c r="AE97">
-        <v>9.4137999999999999E-2</v>
+        <v>0.150621</v>
       </c>
       <c r="AF97">
-        <v>0.10336099999999999</v>
+        <v>0.165378</v>
       </c>
       <c r="AG97">
-        <v>0.115541</v>
+        <v>0.184865</v>
       </c>
       <c r="AH97">
-        <v>0.108917</v>
+        <v>0.17387</v>
       </c>
       <c r="AI97">
-        <v>0.10301299999999999</v>
+        <v>0.16451399999999999</v>
       </c>
       <c r="AJ97">
-        <v>0.175451</v>
+        <v>0.28072200000000003</v>
       </c>
       <c r="AK97">
-        <v>0.162272</v>
+        <v>0.259635</v>
       </c>
       <c r="AL97">
-        <v>0.18434</v>
+        <v>0.29526400000000003</v>
       </c>
       <c r="AM97">
-        <v>0.19448799999999999</v>
+        <v>0.30612699999999998</v>
       </c>
       <c r="AN97">
-        <v>0.19073799999999999</v>
+        <v>0.30336999999999997</v>
       </c>
       <c r="AO97">
-        <v>0.18482000000000001</v>
+        <v>0.29463800000000001</v>
       </c>
       <c r="AP97">
         <v>53.638866</v>
@@ -24664,58 +24664,58 @@
         <v>28.114383</v>
       </c>
       <c r="X98">
-        <v>7.7355999999999994E-2</v>
+        <v>0.123769</v>
       </c>
       <c r="Y98">
-        <v>7.4991000000000002E-2</v>
+        <v>0.121055</v>
       </c>
       <c r="Z98">
-        <v>8.4547999999999998E-2</v>
+        <v>0.13527700000000001</v>
       </c>
       <c r="AA98">
-        <v>9.2011999999999997E-2</v>
+        <v>0.14721999999999999</v>
       </c>
       <c r="AB98">
-        <v>8.7540000000000007E-2</v>
+        <v>0.14006399999999999</v>
       </c>
       <c r="AC98">
-        <v>8.3004999999999995E-2</v>
+        <v>0.132803</v>
       </c>
       <c r="AD98">
-        <v>9.3510999999999997E-2</v>
+        <v>0.149618</v>
       </c>
       <c r="AE98">
-        <v>9.3264E-2</v>
+        <v>0.14922299999999999</v>
       </c>
       <c r="AF98">
-        <v>0.10158499999999999</v>
+        <v>0.16253600000000001</v>
       </c>
       <c r="AG98">
-        <v>0.11017</v>
+        <v>0.17627300000000001</v>
       </c>
       <c r="AH98">
-        <v>0.105421</v>
+        <v>0.168846</v>
       </c>
       <c r="AI98">
-        <v>9.8000000000000004E-2</v>
+        <v>0.15731899999999999</v>
       </c>
       <c r="AJ98">
-        <v>0.17149</v>
+        <v>0.27438499999999999</v>
       </c>
       <c r="AK98">
-        <v>0.160223</v>
+        <v>0.256357</v>
       </c>
       <c r="AL98">
-        <v>0.18088000000000001</v>
+        <v>0.29126299999999999</v>
       </c>
       <c r="AM98">
-        <v>0.187081</v>
+        <v>0.29788199999999998</v>
       </c>
       <c r="AN98">
-        <v>0.18453600000000001</v>
+        <v>0.295852</v>
       </c>
       <c r="AO98">
-        <v>0.177952</v>
+        <v>0.28791099999999997</v>
       </c>
       <c r="AP98">
         <v>53.818807</v>
@@ -24873,58 +24873,58 @@
         <v>27.809743000000001</v>
       </c>
       <c r="X99">
-        <v>7.6968999999999996E-2</v>
+        <v>0.12314899999999999</v>
       </c>
       <c r="Y99">
-        <v>7.9198000000000005E-2</v>
+        <v>0.123291</v>
       </c>
       <c r="Z99">
-        <v>8.2899E-2</v>
+        <v>0.13263900000000001</v>
       </c>
       <c r="AA99">
-        <v>8.5808999999999996E-2</v>
+        <v>0.137294</v>
       </c>
       <c r="AB99">
-        <v>8.5711999999999997E-2</v>
+        <v>0.13714000000000001</v>
       </c>
       <c r="AC99">
-        <v>7.8940999999999997E-2</v>
+        <v>0.12629799999999999</v>
       </c>
       <c r="AD99">
-        <v>9.3848000000000001E-2</v>
+        <v>0.15015600000000001</v>
       </c>
       <c r="AE99">
-        <v>9.5763000000000001E-2</v>
+        <v>0.15322</v>
       </c>
       <c r="AF99">
-        <v>0.102072</v>
+        <v>0.16331499999999999</v>
       </c>
       <c r="AG99">
-        <v>0.102711</v>
+        <v>0.16433800000000001</v>
       </c>
       <c r="AH99">
-        <v>0.103243</v>
+        <v>0.165688</v>
       </c>
       <c r="AI99">
-        <v>9.5037999999999997E-2</v>
+        <v>0.15300900000000001</v>
       </c>
       <c r="AJ99">
-        <v>0.16941600000000001</v>
+        <v>0.27106599999999997</v>
       </c>
       <c r="AK99">
-        <v>0.16370699999999999</v>
+        <v>0.261932</v>
       </c>
       <c r="AL99">
-        <v>0.18401100000000001</v>
+        <v>0.29442000000000002</v>
       </c>
       <c r="AM99">
-        <v>0.17949399999999999</v>
+        <v>0.28934199999999999</v>
       </c>
       <c r="AN99">
-        <v>0.17983399999999999</v>
+        <v>0.28984599999999999</v>
       </c>
       <c r="AO99">
-        <v>0.17344999999999999</v>
+        <v>0.28337099999999998</v>
       </c>
       <c r="AP99">
         <v>53.853129000000003</v>
@@ -25085,58 +25085,58 @@
         <v>27.734399</v>
       </c>
       <c r="X100">
-        <v>7.7951999999999994E-2</v>
+        <v>0.124723</v>
       </c>
       <c r="Y100">
-        <v>8.0957000000000001E-2</v>
+        <v>0.125083</v>
       </c>
       <c r="Z100">
-        <v>8.4039000000000003E-2</v>
+        <v>0.134461</v>
       </c>
       <c r="AA100">
-        <v>8.6457000000000006E-2</v>
+        <v>0.13833100000000001</v>
       </c>
       <c r="AB100">
-        <v>8.6778999999999995E-2</v>
+        <v>0.138847</v>
       </c>
       <c r="AC100">
-        <v>7.8553999999999999E-2</v>
+        <v>0.12567900000000001</v>
       </c>
       <c r="AD100">
-        <v>9.4279000000000002E-2</v>
+        <v>0.15084700000000001</v>
       </c>
       <c r="AE100">
-        <v>9.6163999999999999E-2</v>
+        <v>0.153862</v>
       </c>
       <c r="AF100">
-        <v>0.10403800000000001</v>
+        <v>0.166461</v>
       </c>
       <c r="AG100">
-        <v>0.10290199999999999</v>
+        <v>0.16464300000000001</v>
       </c>
       <c r="AH100">
-        <v>0.103131</v>
+        <v>0.165464</v>
       </c>
       <c r="AI100">
-        <v>9.4509999999999997E-2</v>
+        <v>0.15219299999999999</v>
       </c>
       <c r="AJ100">
-        <v>0.167993</v>
+        <v>0.26878800000000003</v>
       </c>
       <c r="AK100">
-        <v>0.16405700000000001</v>
+        <v>0.26249099999999997</v>
       </c>
       <c r="AL100">
-        <v>0.186001</v>
+        <v>0.29661300000000002</v>
       </c>
       <c r="AM100">
-        <v>0.179645</v>
+        <v>0.28902099999999997</v>
       </c>
       <c r="AN100">
-        <v>0.179623</v>
+        <v>0.28826600000000002</v>
       </c>
       <c r="AO100">
-        <v>0.17241100000000001</v>
+        <v>0.28215499999999999</v>
       </c>
       <c r="AP100">
         <v>54.486089</v>
@@ -25294,58 +25294,58 @@
         <v>30.160145</v>
       </c>
       <c r="X101">
-        <v>9.6983E-2</v>
+        <v>0.15517300000000001</v>
       </c>
       <c r="Y101">
-        <v>9.4750000000000001E-2</v>
+        <v>0.15407499999999999</v>
       </c>
       <c r="Z101">
-        <v>8.4704000000000002E-2</v>
+        <v>0.13552600000000001</v>
       </c>
       <c r="AA101">
-        <v>8.5239999999999996E-2</v>
+        <v>0.13638400000000001</v>
       </c>
       <c r="AB101">
-        <v>9.7553000000000001E-2</v>
+        <v>0.156084</v>
       </c>
       <c r="AC101">
-        <v>0.112776</v>
+        <v>0.18046000000000001</v>
       </c>
       <c r="AD101">
-        <v>0.108124</v>
+        <v>0.17299900000000001</v>
       </c>
       <c r="AE101">
-        <v>0.104313</v>
+        <v>0.16689999999999999</v>
       </c>
       <c r="AF101">
-        <v>9.3544000000000002E-2</v>
+        <v>0.149671</v>
       </c>
       <c r="AG101">
-        <v>9.4441999999999998E-2</v>
+        <v>0.15110599999999999</v>
       </c>
       <c r="AH101">
-        <v>0.112776</v>
+        <v>0.17929300000000001</v>
       </c>
       <c r="AI101">
-        <v>0.11626599999999999</v>
+        <v>0.184642</v>
       </c>
       <c r="AJ101">
-        <v>0.18428900000000001</v>
+        <v>0.29486299999999999</v>
       </c>
       <c r="AK101">
-        <v>0.16608400000000001</v>
+        <v>0.265735</v>
       </c>
       <c r="AL101">
-        <v>0.16868900000000001</v>
+        <v>0.277003</v>
       </c>
       <c r="AM101">
-        <v>0.166159</v>
+        <v>0.272947</v>
       </c>
       <c r="AN101">
-        <v>0.18698799999999999</v>
+        <v>0.29894199999999999</v>
       </c>
       <c r="AO101">
-        <v>0.197606</v>
+        <v>0.30971199999999999</v>
       </c>
       <c r="AP101">
         <v>51.480516000000001</v>
@@ -25503,58 +25503,58 @@
         <v>30.255928000000001</v>
       </c>
       <c r="X102">
-        <v>9.5433000000000004E-2</v>
+        <v>0.152693</v>
       </c>
       <c r="Y102">
-        <v>9.3940999999999997E-2</v>
+        <v>0.15260099999999999</v>
       </c>
       <c r="Z102">
-        <v>8.4337999999999996E-2</v>
+        <v>0.13494</v>
       </c>
       <c r="AA102">
-        <v>8.6374000000000006E-2</v>
+        <v>0.13819799999999999</v>
       </c>
       <c r="AB102">
-        <v>9.6797999999999995E-2</v>
+        <v>0.15487699999999999</v>
       </c>
       <c r="AC102">
-        <v>0.112632</v>
+        <v>0.180232</v>
       </c>
       <c r="AD102">
-        <v>0.107792</v>
+        <v>0.17246700000000001</v>
       </c>
       <c r="AE102">
-        <v>0.103786</v>
+        <v>0.16605800000000001</v>
       </c>
       <c r="AF102">
-        <v>9.4178999999999999E-2</v>
+        <v>0.15068699999999999</v>
       </c>
       <c r="AG102">
-        <v>9.6508999999999998E-2</v>
+        <v>0.154414</v>
       </c>
       <c r="AH102">
-        <v>0.110888</v>
+        <v>0.176874</v>
       </c>
       <c r="AI102">
-        <v>0.113417</v>
+        <v>0.18063100000000001</v>
       </c>
       <c r="AJ102">
-        <v>0.183197</v>
+        <v>0.29311500000000001</v>
       </c>
       <c r="AK102">
-        <v>0.16522999999999999</v>
+        <v>0.26436799999999999</v>
       </c>
       <c r="AL102">
-        <v>0.16841700000000001</v>
+        <v>0.27655600000000002</v>
       </c>
       <c r="AM102">
-        <v>0.166966</v>
+        <v>0.27361400000000002</v>
       </c>
       <c r="AN102">
-        <v>0.187643</v>
+        <v>0.29994900000000002</v>
       </c>
       <c r="AO102">
-        <v>0.19619200000000001</v>
+        <v>0.30857400000000001</v>
       </c>
       <c r="AP102">
         <v>51.578758999999998</v>
@@ -25715,58 +25715,58 @@
         <v>29.861194000000001</v>
       </c>
       <c r="X103">
-        <v>9.3667E-2</v>
+        <v>0.149867</v>
       </c>
       <c r="Y103">
-        <v>9.4936000000000006E-2</v>
+        <v>0.151893</v>
       </c>
       <c r="Z103">
-        <v>8.3907999999999996E-2</v>
+        <v>0.13425300000000001</v>
       </c>
       <c r="AA103">
-        <v>8.0439999999999998E-2</v>
+        <v>0.12870400000000001</v>
       </c>
       <c r="AB103">
-        <v>8.8901999999999995E-2</v>
+        <v>0.14224300000000001</v>
       </c>
       <c r="AC103">
-        <v>9.1204999999999994E-2</v>
+        <v>0.145927</v>
       </c>
       <c r="AD103">
-        <v>0.107407</v>
+        <v>0.171851</v>
       </c>
       <c r="AE103">
-        <v>0.103826</v>
+        <v>0.16612099999999999</v>
       </c>
       <c r="AF103">
-        <v>9.5440999999999998E-2</v>
+        <v>0.15270500000000001</v>
       </c>
       <c r="AG103">
-        <v>9.1204999999999994E-2</v>
+        <v>0.145928</v>
       </c>
       <c r="AH103">
-        <v>0.106896</v>
+        <v>0.171489</v>
       </c>
       <c r="AI103">
-        <v>0.107144</v>
+        <v>0.17180599999999999</v>
       </c>
       <c r="AJ103">
-        <v>0.18121499999999999</v>
+        <v>0.28994399999999998</v>
       </c>
       <c r="AK103">
-        <v>0.16644400000000001</v>
+        <v>0.26631100000000002</v>
       </c>
       <c r="AL103">
-        <v>0.16941200000000001</v>
+        <v>0.27762500000000001</v>
       </c>
       <c r="AM103">
-        <v>0.16392899999999999</v>
+        <v>0.27122600000000002</v>
       </c>
       <c r="AN103">
-        <v>0.18453700000000001</v>
+        <v>0.29824800000000001</v>
       </c>
       <c r="AO103">
-        <v>0.19142200000000001</v>
+        <v>0.30442799999999998</v>
       </c>
       <c r="AP103">
         <v>51.720711000000001</v>
@@ -25927,58 +25927,58 @@
         <v>29.535069</v>
       </c>
       <c r="X104">
-        <v>9.2105999999999993E-2</v>
+        <v>0.147369</v>
       </c>
       <c r="Y104">
-        <v>9.4839999999999994E-2</v>
+        <v>0.14984700000000001</v>
       </c>
       <c r="Z104">
-        <v>8.2373000000000002E-2</v>
+        <v>0.131796</v>
       </c>
       <c r="AA104">
-        <v>7.4159000000000003E-2</v>
+        <v>0.118655</v>
       </c>
       <c r="AB104">
-        <v>8.3658999999999997E-2</v>
+        <v>0.133854</v>
       </c>
       <c r="AC104">
-        <v>8.5279999999999995E-2</v>
+        <v>0.13644300000000001</v>
       </c>
       <c r="AD104">
-        <v>0.106376</v>
+        <v>0.17020099999999999</v>
       </c>
       <c r="AE104">
-        <v>0.103756</v>
+        <v>0.16600999999999999</v>
       </c>
       <c r="AF104">
-        <v>9.4735E-2</v>
+        <v>0.15157699999999999</v>
       </c>
       <c r="AG104">
-        <v>8.3410999999999999E-2</v>
+        <v>0.13345699999999999</v>
       </c>
       <c r="AH104">
-        <v>0.104784</v>
+        <v>0.168576</v>
       </c>
       <c r="AI104">
-        <v>0.104409</v>
+        <v>0.167772</v>
       </c>
       <c r="AJ104">
-        <v>0.18319199999999999</v>
+        <v>0.29310700000000001</v>
       </c>
       <c r="AK104">
-        <v>0.169989</v>
+        <v>0.271982</v>
       </c>
       <c r="AL104">
-        <v>0.16655300000000001</v>
+        <v>0.27494099999999999</v>
       </c>
       <c r="AM104">
-        <v>0.16433500000000001</v>
+        <v>0.27273700000000001</v>
       </c>
       <c r="AN104">
-        <v>0.18501300000000001</v>
+        <v>0.29950100000000002</v>
       </c>
       <c r="AO104">
-        <v>0.189968</v>
+        <v>0.30279099999999998</v>
       </c>
       <c r="AP104">
         <v>51.827759999999998</v>
@@ -26139,58 +26139,58 @@
         <v>30.046879000000001</v>
       </c>
       <c r="X105">
-        <v>8.9896000000000004E-2</v>
+        <v>0.14383299999999999</v>
       </c>
       <c r="Y105">
-        <v>9.0076000000000003E-2</v>
+        <v>0.14430299999999999</v>
       </c>
       <c r="Z105">
-        <v>8.8043999999999997E-2</v>
+        <v>0.14087</v>
       </c>
       <c r="AA105">
-        <v>9.0255000000000002E-2</v>
+        <v>0.14440900000000001</v>
       </c>
       <c r="AB105">
-        <v>9.0979000000000004E-2</v>
+        <v>0.145566</v>
       </c>
       <c r="AC105">
-        <v>9.5451999999999995E-2</v>
+        <v>0.152726</v>
       </c>
       <c r="AD105">
-        <v>0.10421999999999999</v>
+        <v>0.16675100000000001</v>
       </c>
       <c r="AE105">
-        <v>0.103191</v>
+        <v>0.165105</v>
       </c>
       <c r="AF105">
-        <v>0.10151200000000001</v>
+        <v>0.16242000000000001</v>
       </c>
       <c r="AG105">
-        <v>0.103172</v>
+        <v>0.165076</v>
       </c>
       <c r="AH105">
-        <v>0.107832</v>
+        <v>0.17261699999999999</v>
       </c>
       <c r="AI105">
-        <v>0.106326</v>
+        <v>0.17008200000000001</v>
       </c>
       <c r="AJ105">
-        <v>0.18423600000000001</v>
+        <v>0.29477700000000001</v>
       </c>
       <c r="AK105">
-        <v>0.173316</v>
+        <v>0.277306</v>
       </c>
       <c r="AL105">
-        <v>0.179838</v>
+        <v>0.290103</v>
       </c>
       <c r="AM105">
-        <v>0.186531</v>
+        <v>0.29681099999999999</v>
       </c>
       <c r="AN105">
-        <v>0.19411</v>
+        <v>0.30728299999999997</v>
       </c>
       <c r="AO105">
-        <v>0.19222800000000001</v>
+        <v>0.30400300000000002</v>
       </c>
       <c r="AP105">
         <v>51.872568999999999</v>
@@ -26351,58 +26351,58 @@
         <v>30.557012</v>
       </c>
       <c r="X106">
-        <v>8.9122000000000007E-2</v>
+        <v>0.142596</v>
       </c>
       <c r="Y106">
-        <v>8.9498999999999995E-2</v>
+        <v>0.14110300000000001</v>
       </c>
       <c r="Z106">
-        <v>9.6303E-2</v>
+        <v>0.154085</v>
       </c>
       <c r="AA106">
-        <v>0.102865</v>
+        <v>0.16458400000000001</v>
       </c>
       <c r="AB106">
-        <v>9.6946000000000004E-2</v>
+        <v>0.155114</v>
       </c>
       <c r="AC106">
-        <v>0.11675099999999999</v>
+        <v>0.18682599999999999</v>
       </c>
       <c r="AD106">
-        <v>0.102163</v>
+        <v>0.16345999999999999</v>
       </c>
       <c r="AE106">
-        <v>0.102052</v>
+        <v>0.16328400000000001</v>
       </c>
       <c r="AF106">
-        <v>0.109572</v>
+        <v>0.175315</v>
       </c>
       <c r="AG106">
-        <v>0.11609899999999999</v>
+        <v>0.18575800000000001</v>
       </c>
       <c r="AH106">
-        <v>0.11002099999999999</v>
+        <v>0.17544299999999999</v>
       </c>
       <c r="AI106">
-        <v>0.10878599999999999</v>
+        <v>0.17311699999999999</v>
       </c>
       <c r="AJ106">
-        <v>0.186996</v>
+        <v>0.29919400000000002</v>
       </c>
       <c r="AK106">
-        <v>0.17400499999999999</v>
+        <v>0.27840799999999999</v>
       </c>
       <c r="AL106">
-        <v>0.19722100000000001</v>
+        <v>0.30905500000000002</v>
       </c>
       <c r="AM106">
-        <v>0.198384</v>
+        <v>0.31008999999999998</v>
       </c>
       <c r="AN106">
-        <v>0.19992599999999999</v>
+        <v>0.31176399999999999</v>
       </c>
       <c r="AO106">
-        <v>0.19473799999999999</v>
+        <v>0.30521999999999999</v>
       </c>
       <c r="AP106">
         <v>51.975096000000001</v>
@@ -26563,58 +26563,58 @@
         <v>30.142569000000002</v>
       </c>
       <c r="X107">
-        <v>8.5763000000000006E-2</v>
+        <v>0.13722000000000001</v>
       </c>
       <c r="Y107">
-        <v>8.4241999999999997E-2</v>
+        <v>0.13492399999999999</v>
       </c>
       <c r="Z107">
-        <v>9.3201000000000006E-2</v>
+        <v>0.149122</v>
       </c>
       <c r="AA107">
-        <v>9.8225999999999994E-2</v>
+        <v>0.157161</v>
       </c>
       <c r="AB107">
-        <v>9.4240000000000004E-2</v>
+        <v>0.150784</v>
       </c>
       <c r="AC107">
-        <v>9.8488999999999993E-2</v>
+        <v>0.15758800000000001</v>
       </c>
       <c r="AD107">
-        <v>0.10186199999999999</v>
+        <v>0.16297900000000001</v>
       </c>
       <c r="AE107">
-        <v>9.9782999999999997E-2</v>
+        <v>0.15965299999999999</v>
       </c>
       <c r="AF107">
-        <v>0.10974</v>
+        <v>0.17558399999999999</v>
       </c>
       <c r="AG107">
-        <v>0.11358699999999999</v>
+        <v>0.18173900000000001</v>
       </c>
       <c r="AH107">
-        <v>0.108149</v>
+        <v>0.17269200000000001</v>
       </c>
       <c r="AI107">
-        <v>0.106671</v>
+        <v>0.16988700000000001</v>
       </c>
       <c r="AJ107">
-        <v>0.18216299999999999</v>
+        <v>0.29146</v>
       </c>
       <c r="AK107">
-        <v>0.167465</v>
+        <v>0.26794299999999999</v>
       </c>
       <c r="AL107">
-        <v>0.19020799999999999</v>
+        <v>0.30218499999999998</v>
       </c>
       <c r="AM107">
-        <v>0.19352900000000001</v>
+        <v>0.30540400000000001</v>
       </c>
       <c r="AN107">
-        <v>0.19420999999999999</v>
+        <v>0.30586000000000002</v>
       </c>
       <c r="AO107">
-        <v>0.191244</v>
+        <v>0.30126999999999998</v>
       </c>
       <c r="AP107">
         <v>52.230367999999999</v>
@@ -26775,58 +26775,58 @@
         <v>29.664793</v>
       </c>
       <c r="X108">
-        <v>8.2604999999999998E-2</v>
+        <v>0.13216800000000001</v>
       </c>
       <c r="Y108">
-        <v>8.1005999999999995E-2</v>
+        <v>0.13028899999999999</v>
       </c>
       <c r="Z108">
-        <v>9.1026999999999997E-2</v>
+        <v>0.14564299999999999</v>
       </c>
       <c r="AA108">
-        <v>9.4436000000000006E-2</v>
+        <v>0.15109700000000001</v>
       </c>
       <c r="AB108">
-        <v>9.0258000000000005E-2</v>
+        <v>0.14441200000000001</v>
       </c>
       <c r="AC108">
-        <v>9.2446E-2</v>
+        <v>0.14791799999999999</v>
       </c>
       <c r="AD108">
-        <v>0.10321</v>
+        <v>0.16513600000000001</v>
       </c>
       <c r="AE108">
-        <v>9.8813999999999999E-2</v>
+        <v>0.15810199999999999</v>
       </c>
       <c r="AF108">
-        <v>0.109502</v>
+        <v>0.175204</v>
       </c>
       <c r="AG108">
-        <v>0.11495</v>
+        <v>0.18392</v>
       </c>
       <c r="AH108">
-        <v>0.104391</v>
+        <v>0.167356</v>
       </c>
       <c r="AI108">
-        <v>0.10410800000000001</v>
+        <v>0.16595799999999999</v>
       </c>
       <c r="AJ108">
-        <v>0.18082300000000001</v>
+        <v>0.28931800000000002</v>
       </c>
       <c r="AK108">
-        <v>0.16297500000000001</v>
+        <v>0.26075999999999999</v>
       </c>
       <c r="AL108">
-        <v>0.18768799999999999</v>
+        <v>0.29948200000000003</v>
       </c>
       <c r="AM108">
-        <v>0.19547900000000001</v>
+        <v>0.30683199999999999</v>
       </c>
       <c r="AN108">
-        <v>0.18643000000000001</v>
+        <v>0.29744300000000001</v>
       </c>
       <c r="AO108">
-        <v>0.18754799999999999</v>
+        <v>0.29693799999999998</v>
       </c>
       <c r="AP108">
         <v>52.709859999999999</v>
@@ -26987,58 +26987,58 @@
         <v>28.715208000000001</v>
       </c>
       <c r="X109">
-        <v>7.9406000000000004E-2</v>
+        <v>0.127049</v>
       </c>
       <c r="Y109">
-        <v>7.9016000000000003E-2</v>
+        <v>0.12753999999999999</v>
       </c>
       <c r="Z109">
-        <v>9.0653999999999998E-2</v>
+        <v>0.14504700000000001</v>
       </c>
       <c r="AA109">
-        <v>8.7940000000000004E-2</v>
+        <v>0.140704</v>
       </c>
       <c r="AB109">
-        <v>8.5818000000000005E-2</v>
+        <v>0.13730899999999999</v>
       </c>
       <c r="AC109">
-        <v>8.1474000000000005E-2</v>
+        <v>0.130353</v>
       </c>
       <c r="AD109">
-        <v>0.101949</v>
+        <v>0.16311899999999999</v>
       </c>
       <c r="AE109">
-        <v>9.8077999999999999E-2</v>
+        <v>0.15692500000000001</v>
       </c>
       <c r="AF109">
-        <v>0.10859099999999999</v>
+        <v>0.17374500000000001</v>
       </c>
       <c r="AG109">
-        <v>0.10653799999999999</v>
+        <v>0.170461</v>
       </c>
       <c r="AH109">
-        <v>0.100581</v>
+        <v>0.161997</v>
       </c>
       <c r="AI109">
-        <v>9.8411999999999999E-2</v>
+        <v>0.15779299999999999</v>
       </c>
       <c r="AJ109">
-        <v>0.17612700000000001</v>
+        <v>0.281804</v>
       </c>
       <c r="AK109">
-        <v>0.16200500000000001</v>
+        <v>0.25920799999999999</v>
       </c>
       <c r="AL109">
-        <v>0.18404200000000001</v>
+        <v>0.29518499999999998</v>
       </c>
       <c r="AM109">
-        <v>0.18337500000000001</v>
+        <v>0.29365999999999998</v>
       </c>
       <c r="AN109">
-        <v>0.178231</v>
+        <v>0.28842200000000001</v>
       </c>
       <c r="AO109">
-        <v>0.17937500000000001</v>
+        <v>0.28898400000000002</v>
       </c>
       <c r="AP109">
         <v>53.342879000000003</v>
@@ -27199,58 +27199,58 @@
         <v>27.854061000000002</v>
       </c>
       <c r="X110">
-        <v>7.9325999999999994E-2</v>
+        <v>0.12692000000000001</v>
       </c>
       <c r="Y110">
-        <v>7.7023999999999995E-2</v>
+        <v>0.12604799999999999</v>
       </c>
       <c r="Z110">
-        <v>8.3350999999999995E-2</v>
+        <v>0.13336100000000001</v>
       </c>
       <c r="AA110">
-        <v>7.3636999999999994E-2</v>
+        <v>0.11781899999999999</v>
       </c>
       <c r="AB110">
-        <v>7.7179999999999999E-2</v>
+        <v>0.123488</v>
       </c>
       <c r="AC110">
-        <v>6.8695999999999993E-2</v>
+        <v>0.10989500000000001</v>
       </c>
       <c r="AD110">
-        <v>0.105111</v>
+        <v>0.16817799999999999</v>
       </c>
       <c r="AE110">
-        <v>9.8551E-2</v>
+        <v>0.15768199999999999</v>
       </c>
       <c r="AF110">
-        <v>0.10011200000000001</v>
+        <v>0.16017899999999999</v>
       </c>
       <c r="AG110">
-        <v>8.8276999999999994E-2</v>
+        <v>0.14124400000000001</v>
       </c>
       <c r="AH110">
-        <v>9.7263000000000002E-2</v>
+        <v>0.157364</v>
       </c>
       <c r="AI110">
-        <v>9.2936000000000005E-2</v>
+        <v>0.15001100000000001</v>
       </c>
       <c r="AJ110">
-        <v>0.17494599999999999</v>
+        <v>0.27991300000000002</v>
       </c>
       <c r="AK110">
-        <v>0.16208800000000001</v>
+        <v>0.25934099999999999</v>
       </c>
       <c r="AL110">
-        <v>0.16614599999999999</v>
+        <v>0.27595700000000001</v>
       </c>
       <c r="AM110">
-        <v>0.16006100000000001</v>
+        <v>0.26890900000000001</v>
       </c>
       <c r="AN110">
-        <v>0.17053599999999999</v>
+        <v>0.28009200000000001</v>
       </c>
       <c r="AO110">
-        <v>0.171375</v>
+        <v>0.28137200000000001</v>
       </c>
       <c r="AP110">
         <v>54.117507000000003</v>
@@ -27411,58 +27411,58 @@
         <v>27.733117</v>
       </c>
       <c r="X111">
-        <v>8.0407000000000006E-2</v>
+        <v>0.12865099999999999</v>
       </c>
       <c r="Y111">
-        <v>7.8242999999999993E-2</v>
+        <v>0.12723599999999999</v>
       </c>
       <c r="Z111">
-        <v>8.3069000000000004E-2</v>
+        <v>0.13291</v>
       </c>
       <c r="AA111">
-        <v>7.8036999999999995E-2</v>
+        <v>0.124859</v>
       </c>
       <c r="AB111">
-        <v>7.8643000000000005E-2</v>
+        <v>0.125828</v>
       </c>
       <c r="AC111">
-        <v>7.1743000000000001E-2</v>
+        <v>0.114775</v>
       </c>
       <c r="AD111">
-        <v>0.106989</v>
+        <v>0.171183</v>
       </c>
       <c r="AE111">
-        <v>9.9088999999999997E-2</v>
+        <v>0.15854299999999999</v>
       </c>
       <c r="AF111">
-        <v>9.9407999999999996E-2</v>
+        <v>0.159053</v>
       </c>
       <c r="AG111">
-        <v>9.1109999999999997E-2</v>
+        <v>0.14577699999999999</v>
       </c>
       <c r="AH111">
-        <v>9.7721000000000002E-2</v>
+        <v>0.15798100000000001</v>
       </c>
       <c r="AI111">
-        <v>9.2138999999999999E-2</v>
+        <v>0.148786</v>
       </c>
       <c r="AJ111">
-        <v>0.17438000000000001</v>
+        <v>0.27900799999999998</v>
       </c>
       <c r="AK111">
-        <v>0.162966</v>
+        <v>0.260745</v>
       </c>
       <c r="AL111">
-        <v>0.16659499999999999</v>
+        <v>0.27609099999999998</v>
       </c>
       <c r="AM111">
-        <v>0.160244</v>
+        <v>0.26830999999999999</v>
       </c>
       <c r="AN111">
-        <v>0.17120099999999999</v>
+        <v>0.279393</v>
       </c>
       <c r="AO111">
-        <v>0.169215</v>
+        <v>0.27912500000000001</v>
       </c>
       <c r="AP111">
         <v>54.612023999999998</v>
@@ -27620,58 +27620,58 @@
         <v>28.542134000000001</v>
       </c>
       <c r="X112">
-        <v>9.4156000000000004E-2</v>
+        <v>0.15064900000000001</v>
       </c>
       <c r="Y112">
-        <v>9.5714999999999995E-2</v>
+        <v>0.155531</v>
       </c>
       <c r="Z112">
-        <v>9.6018999999999993E-2</v>
+        <v>0.15363099999999999</v>
       </c>
       <c r="AA112">
-        <v>9.5005000000000006E-2</v>
+        <v>0.152008</v>
       </c>
       <c r="AB112">
-        <v>9.6166000000000001E-2</v>
+        <v>0.153865</v>
       </c>
       <c r="AC112">
-        <v>9.2111999999999999E-2</v>
+        <v>0.14737900000000001</v>
       </c>
       <c r="AD112">
-        <v>0.107713</v>
+        <v>0.17233999999999999</v>
       </c>
       <c r="AE112">
-        <v>0.112069</v>
+        <v>0.179311</v>
       </c>
       <c r="AF112">
-        <v>0.10883</v>
+        <v>0.174128</v>
       </c>
       <c r="AG112">
-        <v>0.109472</v>
+        <v>0.17515600000000001</v>
       </c>
       <c r="AH112">
-        <v>0.10884099999999999</v>
+        <v>0.173071</v>
       </c>
       <c r="AI112">
-        <v>0.10935499999999999</v>
+        <v>0.17432900000000001</v>
       </c>
       <c r="AJ112">
-        <v>0.17391699999999999</v>
+        <v>0.27826699999999999</v>
       </c>
       <c r="AK112">
-        <v>0.16617899999999999</v>
+        <v>0.26588600000000001</v>
       </c>
       <c r="AL112">
-        <v>0.17180200000000001</v>
+        <v>0.28125899999999998</v>
       </c>
       <c r="AM112">
-        <v>0.17679300000000001</v>
+        <v>0.286526</v>
       </c>
       <c r="AN112">
-        <v>0.185748</v>
+        <v>0.294462</v>
       </c>
       <c r="AO112">
-        <v>0.18998999999999999</v>
+        <v>0.30080299999999999</v>
       </c>
       <c r="AP112">
         <v>54.500177999999998</v>
@@ -27829,58 +27829,58 @@
         <v>28.739933000000001</v>
       </c>
       <c r="X113">
-        <v>9.4792000000000001E-2</v>
+        <v>0.151667</v>
       </c>
       <c r="Y113">
-        <v>9.6514000000000003E-2</v>
+        <v>0.156134</v>
       </c>
       <c r="Z113">
-        <v>9.5984E-2</v>
+        <v>0.15357399999999999</v>
       </c>
       <c r="AA113">
-        <v>9.4025999999999998E-2</v>
+        <v>0.15044099999999999</v>
       </c>
       <c r="AB113">
-        <v>9.5624000000000001E-2</v>
+        <v>0.152998</v>
       </c>
       <c r="AC113">
-        <v>9.4503000000000004E-2</v>
+        <v>0.15120700000000001</v>
       </c>
       <c r="AD113">
-        <v>0.108725</v>
+        <v>0.17396</v>
       </c>
       <c r="AE113">
-        <v>0.11358</v>
+        <v>0.181727</v>
       </c>
       <c r="AF113">
-        <v>0.10820100000000001</v>
+        <v>0.173122</v>
       </c>
       <c r="AG113">
-        <v>0.107748</v>
+        <v>0.17239599999999999</v>
       </c>
       <c r="AH113">
-        <v>0.10703600000000001</v>
+        <v>0.17066899999999999</v>
       </c>
       <c r="AI113">
-        <v>0.10942499999999999</v>
+        <v>0.17435700000000001</v>
       </c>
       <c r="AJ113">
-        <v>0.174845</v>
+        <v>0.27975100000000003</v>
       </c>
       <c r="AK113">
-        <v>0.168294</v>
+        <v>0.26927000000000001</v>
       </c>
       <c r="AL113">
-        <v>0.174905</v>
+        <v>0.28456399999999998</v>
       </c>
       <c r="AM113">
-        <v>0.17763999999999999</v>
+        <v>0.28734500000000002</v>
       </c>
       <c r="AN113">
-        <v>0.18390400000000001</v>
+        <v>0.29255199999999998</v>
       </c>
       <c r="AO113">
-        <v>0.18967999999999999</v>
+        <v>0.30054399999999998</v>
       </c>
       <c r="AP113">
         <v>54.533352999999998</v>
@@ -28038,58 +28038,58 @@
         <v>28.648782000000001</v>
       </c>
       <c r="X114">
-        <v>9.5731999999999998E-2</v>
+        <v>0.153171</v>
       </c>
       <c r="Y114">
-        <v>9.9541000000000004E-2</v>
+        <v>0.15815799999999999</v>
       </c>
       <c r="Z114">
-        <v>9.4112000000000001E-2</v>
+        <v>0.15057999999999999</v>
       </c>
       <c r="AA114">
-        <v>9.1603000000000004E-2</v>
+        <v>0.146565</v>
       </c>
       <c r="AB114">
-        <v>9.4810000000000005E-2</v>
+        <v>0.151696</v>
       </c>
       <c r="AC114">
-        <v>9.5873E-2</v>
+        <v>0.15340000000000001</v>
       </c>
       <c r="AD114">
-        <v>0.109322</v>
+        <v>0.17491499999999999</v>
       </c>
       <c r="AE114">
-        <v>0.114242</v>
+        <v>0.182786</v>
       </c>
       <c r="AF114">
-        <v>0.104208</v>
+        <v>0.16673299999999999</v>
       </c>
       <c r="AG114">
-        <v>0.10363</v>
+        <v>0.16580800000000001</v>
       </c>
       <c r="AH114">
-        <v>0.10387399999999999</v>
+        <v>0.166351</v>
       </c>
       <c r="AI114">
-        <v>0.108337</v>
+        <v>0.17272399999999999</v>
       </c>
       <c r="AJ114">
-        <v>0.17654300000000001</v>
+        <v>0.28246900000000003</v>
       </c>
       <c r="AK114">
-        <v>0.172925</v>
+        <v>0.27667999999999998</v>
       </c>
       <c r="AL114">
-        <v>0.17911099999999999</v>
+        <v>0.289136</v>
       </c>
       <c r="AM114">
-        <v>0.17982200000000001</v>
+        <v>0.289352</v>
       </c>
       <c r="AN114">
-        <v>0.17991399999999999</v>
+        <v>0.288412</v>
       </c>
       <c r="AO114">
-        <v>0.18853</v>
+        <v>0.29944900000000002</v>
       </c>
       <c r="AP114">
         <v>54.562655999999997</v>
@@ -28247,58 +28247,58 @@
         <v>28.778867999999999</v>
       </c>
       <c r="X115">
-        <v>9.4905000000000003E-2</v>
+        <v>0.15184800000000001</v>
       </c>
       <c r="Y115">
-        <v>9.8408999999999996E-2</v>
+        <v>0.15689600000000001</v>
       </c>
       <c r="Z115">
-        <v>8.6532999999999999E-2</v>
+        <v>0.13845199999999999</v>
       </c>
       <c r="AA115">
-        <v>8.2553000000000001E-2</v>
+        <v>0.13208400000000001</v>
       </c>
       <c r="AB115">
-        <v>8.8457999999999995E-2</v>
+        <v>0.14153299999999999</v>
       </c>
       <c r="AC115">
-        <v>9.2330999999999996E-2</v>
+        <v>0.147727</v>
       </c>
       <c r="AD115">
-        <v>0.10921699999999999</v>
+        <v>0.17474700000000001</v>
       </c>
       <c r="AE115">
-        <v>0.113162</v>
+        <v>0.18106</v>
       </c>
       <c r="AF115">
-        <v>9.5478999999999994E-2</v>
+        <v>0.15276600000000001</v>
       </c>
       <c r="AG115">
-        <v>9.2909000000000005E-2</v>
+        <v>0.14865400000000001</v>
       </c>
       <c r="AH115">
-        <v>0.100286</v>
+        <v>0.161409</v>
       </c>
       <c r="AI115">
-        <v>0.106657</v>
+        <v>0.170205</v>
       </c>
       <c r="AJ115">
-        <v>0.181341</v>
+        <v>0.29014499999999999</v>
       </c>
       <c r="AK115">
-        <v>0.17549600000000001</v>
+        <v>0.28079300000000001</v>
       </c>
       <c r="AL115">
-        <v>0.17208599999999999</v>
+        <v>0.28175299999999998</v>
       </c>
       <c r="AM115">
-        <v>0.17236899999999999</v>
+        <v>0.28179199999999999</v>
       </c>
       <c r="AN115">
-        <v>0.17396400000000001</v>
+        <v>0.28259600000000001</v>
       </c>
       <c r="AO115">
-        <v>0.187808</v>
+        <v>0.29855199999999998</v>
       </c>
       <c r="AP115">
         <v>54.139389999999999</v>
@@ -28459,58 +28459,58 @@
         <v>29.085505000000001</v>
       </c>
       <c r="X116">
-        <v>9.3299999999999994E-2</v>
+        <v>0.149281</v>
       </c>
       <c r="Y116">
-        <v>9.7237000000000004E-2</v>
+        <v>0.15470200000000001</v>
       </c>
       <c r="Z116">
-        <v>8.9783000000000002E-2</v>
+        <v>0.143653</v>
       </c>
       <c r="AA116">
-        <v>9.6596000000000001E-2</v>
+        <v>0.154554</v>
       </c>
       <c r="AB116">
-        <v>9.4759999999999997E-2</v>
+        <v>0.151615</v>
       </c>
       <c r="AC116">
-        <v>0.101428</v>
+        <v>0.16229199999999999</v>
       </c>
       <c r="AD116">
-        <v>0.106354</v>
+        <v>0.17016700000000001</v>
       </c>
       <c r="AE116">
-        <v>0.11197500000000001</v>
+        <v>0.17916099999999999</v>
       </c>
       <c r="AF116">
-        <v>9.7308000000000006E-2</v>
+        <v>0.155693</v>
       </c>
       <c r="AG116">
-        <v>0.104653</v>
+        <v>0.16744500000000001</v>
       </c>
       <c r="AH116">
-        <v>9.9809999999999996E-2</v>
+        <v>0.160666</v>
       </c>
       <c r="AI116">
-        <v>0.10538699999999999</v>
+        <v>0.16814599999999999</v>
       </c>
       <c r="AJ116">
-        <v>0.18223</v>
+        <v>0.29156700000000002</v>
       </c>
       <c r="AK116">
-        <v>0.17664099999999999</v>
+        <v>0.28262599999999999</v>
       </c>
       <c r="AL116">
-        <v>0.17594299999999999</v>
+        <v>0.28570899999999999</v>
       </c>
       <c r="AM116">
-        <v>0.17785100000000001</v>
+        <v>0.28669099999999997</v>
       </c>
       <c r="AN116">
-        <v>0.17677000000000001</v>
+        <v>0.28357199999999999</v>
       </c>
       <c r="AO116">
-        <v>0.188001</v>
+        <v>0.29824000000000001</v>
       </c>
       <c r="AP116">
         <v>53.621659000000001</v>
@@ -28668,58 +28668,58 @@
         <v>29.203835000000002</v>
       </c>
       <c r="X117">
-        <v>9.2759999999999995E-2</v>
+        <v>0.14841599999999999</v>
       </c>
       <c r="Y117">
-        <v>9.5519000000000007E-2</v>
+        <v>0.15192800000000001</v>
       </c>
       <c r="Z117">
-        <v>9.7094E-2</v>
+        <v>0.15535099999999999</v>
       </c>
       <c r="AA117">
-        <v>9.9971000000000004E-2</v>
+        <v>0.15995300000000001</v>
       </c>
       <c r="AB117">
-        <v>9.7968E-2</v>
+        <v>0.156749</v>
       </c>
       <c r="AC117">
-        <v>0.118689</v>
+        <v>0.18993099999999999</v>
       </c>
       <c r="AD117">
-        <v>0.10523</v>
+        <v>0.16836799999999999</v>
       </c>
       <c r="AE117">
-        <v>0.11157599999999999</v>
+        <v>0.17852100000000001</v>
       </c>
       <c r="AF117">
-        <v>0.103924</v>
+        <v>0.16627800000000001</v>
       </c>
       <c r="AG117">
-        <v>0.11146200000000001</v>
+        <v>0.178339</v>
       </c>
       <c r="AH117">
-        <v>9.8971000000000003E-2</v>
+        <v>0.159409</v>
       </c>
       <c r="AI117">
-        <v>0.104001</v>
+        <v>0.16588</v>
       </c>
       <c r="AJ117">
-        <v>0.184057</v>
+        <v>0.29449199999999998</v>
       </c>
       <c r="AK117">
-        <v>0.17755299999999999</v>
+        <v>0.284084</v>
       </c>
       <c r="AL117">
-        <v>0.18420600000000001</v>
+        <v>0.29389799999999999</v>
       </c>
       <c r="AM117">
-        <v>0.180338</v>
+        <v>0.288242</v>
       </c>
       <c r="AN117">
-        <v>0.17807000000000001</v>
+        <v>0.28328199999999998</v>
       </c>
       <c r="AO117">
-        <v>0.187415</v>
+        <v>0.29718800000000001</v>
       </c>
       <c r="AP117">
         <v>53.021225000000001</v>
@@ -28877,58 +28877,58 @@
         <v>28.375482000000002</v>
       </c>
       <c r="X118">
-        <v>9.2405000000000001E-2</v>
+        <v>0.14784800000000001</v>
       </c>
       <c r="Y118">
-        <v>9.1542999999999999E-2</v>
+        <v>0.147951</v>
       </c>
       <c r="Z118">
-        <v>9.7004999999999994E-2</v>
+        <v>0.15520900000000001</v>
       </c>
       <c r="AA118">
-        <v>8.6069999999999994E-2</v>
+        <v>0.137712</v>
       </c>
       <c r="AB118">
-        <v>8.7831000000000006E-2</v>
+        <v>0.14052999999999999</v>
       </c>
       <c r="AC118">
-        <v>9.0911000000000006E-2</v>
+        <v>0.145456</v>
       </c>
       <c r="AD118">
-        <v>0.103725</v>
+        <v>0.16596</v>
       </c>
       <c r="AE118">
-        <v>0.107865</v>
+        <v>0.17258399999999999</v>
       </c>
       <c r="AF118">
-        <v>9.9806000000000006E-2</v>
+        <v>0.15969</v>
       </c>
       <c r="AG118">
-        <v>9.8532999999999996E-2</v>
+        <v>0.15765299999999999</v>
       </c>
       <c r="AH118">
-        <v>9.4612000000000002E-2</v>
+        <v>0.15343999999999999</v>
       </c>
       <c r="AI118">
-        <v>9.7792000000000004E-2</v>
+        <v>0.15711800000000001</v>
       </c>
       <c r="AJ118">
-        <v>0.179511</v>
+        <v>0.287217</v>
       </c>
       <c r="AK118">
-        <v>0.17126</v>
+        <v>0.27401599999999998</v>
       </c>
       <c r="AL118">
-        <v>0.17649200000000001</v>
+        <v>0.286605</v>
       </c>
       <c r="AM118">
-        <v>0.16774600000000001</v>
+        <v>0.27584799999999998</v>
       </c>
       <c r="AN118">
-        <v>0.17086899999999999</v>
+        <v>0.27634599999999998</v>
       </c>
       <c r="AO118">
-        <v>0.181839</v>
+        <v>0.29204599999999997</v>
       </c>
       <c r="AP118">
         <v>52.859578999999997</v>
@@ -29089,58 +29089,58 @@
         <v>27.659210000000002</v>
       </c>
       <c r="X119">
-        <v>9.1555999999999998E-2</v>
+        <v>0.14649000000000001</v>
       </c>
       <c r="Y119">
-        <v>9.1572000000000001E-2</v>
+        <v>0.14708299999999999</v>
       </c>
       <c r="Z119">
-        <v>9.4076000000000007E-2</v>
+        <v>0.15052199999999999</v>
       </c>
       <c r="AA119">
-        <v>8.4502999999999995E-2</v>
+        <v>0.13520499999999999</v>
       </c>
       <c r="AB119">
-        <v>8.5891999999999996E-2</v>
+        <v>0.13742699999999999</v>
       </c>
       <c r="AC119">
-        <v>8.0376000000000003E-2</v>
+        <v>0.12859300000000001</v>
       </c>
       <c r="AD119">
-        <v>0.103562</v>
+        <v>0.16569900000000001</v>
       </c>
       <c r="AE119">
-        <v>0.10702200000000001</v>
+        <v>0.171235</v>
       </c>
       <c r="AF119">
-        <v>0.103778</v>
+        <v>0.166045</v>
       </c>
       <c r="AG119">
-        <v>0.105312</v>
+        <v>0.16849900000000001</v>
       </c>
       <c r="AH119">
-        <v>9.3349000000000001E-2</v>
+        <v>0.151669</v>
       </c>
       <c r="AI119">
-        <v>9.4657000000000005E-2</v>
+        <v>0.15257299999999999</v>
       </c>
       <c r="AJ119">
-        <v>0.18027799999999999</v>
+        <v>0.28844500000000001</v>
       </c>
       <c r="AK119">
-        <v>0.17043900000000001</v>
+        <v>0.272702</v>
       </c>
       <c r="AL119">
-        <v>0.18604100000000001</v>
+        <v>0.29701100000000002</v>
       </c>
       <c r="AM119">
-        <v>0.17319599999999999</v>
+        <v>0.28098899999999999</v>
       </c>
       <c r="AN119">
-        <v>0.17006199999999999</v>
+        <v>0.27448600000000001</v>
       </c>
       <c r="AO119">
-        <v>0.179645</v>
+        <v>0.28968300000000002</v>
       </c>
       <c r="AP119">
         <v>53.285626000000001</v>
@@ -29301,58 +29301,58 @@
         <v>27.470027000000002</v>
       </c>
       <c r="X120">
-        <v>9.1383000000000006E-2</v>
+        <v>0.14621200000000001</v>
       </c>
       <c r="Y120">
-        <v>9.2480999999999994E-2</v>
+        <v>0.14621799999999999</v>
       </c>
       <c r="Z120">
-        <v>9.2391000000000001E-2</v>
+        <v>0.14782500000000001</v>
       </c>
       <c r="AA120">
-        <v>9.0956999999999996E-2</v>
+        <v>0.14553099999999999</v>
       </c>
       <c r="AB120">
-        <v>9.0110999999999997E-2</v>
+        <v>0.144178</v>
       </c>
       <c r="AC120">
-        <v>8.3250000000000005E-2</v>
+        <v>0.13319500000000001</v>
       </c>
       <c r="AD120">
-        <v>0.102733</v>
+        <v>0.16437299999999999</v>
       </c>
       <c r="AE120">
-        <v>0.103842</v>
+        <v>0.16614799999999999</v>
       </c>
       <c r="AF120">
-        <v>0.106557</v>
+        <v>0.170492</v>
       </c>
       <c r="AG120">
-        <v>0.104598</v>
+        <v>0.16735700000000001</v>
       </c>
       <c r="AH120">
-        <v>9.3694E-2</v>
+        <v>0.15221199999999999</v>
       </c>
       <c r="AI120">
-        <v>9.5028000000000001E-2</v>
+        <v>0.15291399999999999</v>
       </c>
       <c r="AJ120">
-        <v>0.17693900000000001</v>
+        <v>0.28310299999999999</v>
       </c>
       <c r="AK120">
-        <v>0.16551099999999999</v>
+        <v>0.264818</v>
       </c>
       <c r="AL120">
-        <v>0.18938099999999999</v>
+        <v>0.30102800000000002</v>
       </c>
       <c r="AM120">
-        <v>0.176487</v>
+        <v>0.284418</v>
       </c>
       <c r="AN120">
-        <v>0.169823</v>
+        <v>0.27329399999999998</v>
       </c>
       <c r="AO120">
-        <v>0.18004300000000001</v>
+        <v>0.28953699999999999</v>
       </c>
       <c r="AP120">
         <v>54.077877999999998</v>
@@ -29513,58 +29513,58 @@
         <v>27.794926</v>
       </c>
       <c r="X121">
-        <v>8.9326000000000003E-2</v>
+        <v>0.14292199999999999</v>
       </c>
       <c r="Y121">
-        <v>8.5708999999999994E-2</v>
+        <v>0.14002600000000001</v>
       </c>
       <c r="Z121">
-        <v>8.8160000000000002E-2</v>
+        <v>0.14105599999999999</v>
       </c>
       <c r="AA121">
-        <v>8.8607000000000005E-2</v>
+        <v>0.14177100000000001</v>
       </c>
       <c r="AB121">
-        <v>8.7707999999999994E-2</v>
+        <v>0.14033300000000001</v>
       </c>
       <c r="AC121">
-        <v>8.5813E-2</v>
+        <v>0.137298</v>
       </c>
       <c r="AD121">
-        <v>0.103091</v>
+        <v>0.16494600000000001</v>
       </c>
       <c r="AE121">
-        <v>9.8872000000000002E-2</v>
+        <v>0.158196</v>
       </c>
       <c r="AF121">
-        <v>0.103911</v>
+        <v>0.16625699999999999</v>
       </c>
       <c r="AG121">
-        <v>9.7878000000000007E-2</v>
+        <v>0.15660499999999999</v>
       </c>
       <c r="AH121">
-        <v>9.2557E-2</v>
+        <v>0.15081600000000001</v>
       </c>
       <c r="AI121">
-        <v>9.6909999999999996E-2</v>
+        <v>0.15542400000000001</v>
       </c>
       <c r="AJ121">
-        <v>0.17335900000000001</v>
+        <v>0.27737400000000001</v>
       </c>
       <c r="AK121">
-        <v>0.15879499999999999</v>
+        <v>0.25407099999999999</v>
       </c>
       <c r="AL121">
-        <v>0.185367</v>
+        <v>0.29710799999999998</v>
       </c>
       <c r="AM121">
-        <v>0.16900299999999999</v>
+        <v>0.27649000000000001</v>
       </c>
       <c r="AN121">
-        <v>0.16567899999999999</v>
+        <v>0.26925900000000003</v>
       </c>
       <c r="AO121">
-        <v>0.18087800000000001</v>
+        <v>0.28988999999999998</v>
       </c>
       <c r="AP121">
         <v>54.860895999999997</v>
@@ -29725,58 +29725,58 @@
         <v>27.767958</v>
       </c>
       <c r="X122">
-        <v>8.8095999999999994E-2</v>
+        <v>0.140954</v>
       </c>
       <c r="Y122">
-        <v>8.2705000000000001E-2</v>
+        <v>0.13714000000000001</v>
       </c>
       <c r="Z122">
-        <v>8.7013999999999994E-2</v>
+        <v>0.13922200000000001</v>
       </c>
       <c r="AA122">
-        <v>8.5894999999999999E-2</v>
+        <v>0.137433</v>
       </c>
       <c r="AB122">
-        <v>8.5144999999999998E-2</v>
+        <v>0.13623199999999999</v>
       </c>
       <c r="AC122">
-        <v>8.6445999999999995E-2</v>
+        <v>0.13831099999999999</v>
       </c>
       <c r="AD122">
-        <v>0.10319</v>
+        <v>0.165103</v>
       </c>
       <c r="AE122">
-        <v>9.7113000000000005E-2</v>
+        <v>0.15538099999999999</v>
       </c>
       <c r="AF122">
-        <v>0.103104</v>
+        <v>0.164967</v>
       </c>
       <c r="AG122">
-        <v>9.4833000000000001E-2</v>
+        <v>0.15173300000000001</v>
       </c>
       <c r="AH122">
-        <v>9.1843999999999995E-2</v>
+        <v>0.150062</v>
       </c>
       <c r="AI122">
-        <v>9.7576999999999997E-2</v>
+        <v>0.156359</v>
       </c>
       <c r="AJ122">
-        <v>0.17176900000000001</v>
+        <v>0.27483000000000002</v>
       </c>
       <c r="AK122">
-        <v>0.15770999999999999</v>
+        <v>0.252336</v>
       </c>
       <c r="AL122">
-        <v>0.18504100000000001</v>
+        <v>0.29675200000000002</v>
       </c>
       <c r="AM122">
-        <v>0.164466</v>
+        <v>0.27190399999999998</v>
       </c>
       <c r="AN122">
-        <v>0.16312599999999999</v>
+        <v>0.266955</v>
       </c>
       <c r="AO122">
-        <v>0.180142</v>
+        <v>0.28914099999999998</v>
       </c>
       <c r="AP122">
         <v>55.457617999999997</v>
@@ -30162,58 +30162,58 @@
         <v>23.563457</v>
       </c>
       <c r="X2">
-        <v>0.10602399999999999</v>
+        <v>0.16963900000000001</v>
       </c>
       <c r="Y2">
-        <v>0.111788</v>
+        <v>0.177814</v>
       </c>
       <c r="Z2">
-        <v>0.108792</v>
+        <v>0.174067</v>
       </c>
       <c r="AA2">
-        <v>9.5514000000000002E-2</v>
+        <v>0.15282299999999999</v>
       </c>
       <c r="AB2">
-        <v>9.2817999999999998E-2</v>
+        <v>0.148509</v>
       </c>
       <c r="AC2">
-        <v>8.3654999999999993E-2</v>
+        <v>0.13384099999999999</v>
       </c>
       <c r="AD2">
-        <v>0.111915</v>
+        <v>0.179064</v>
       </c>
       <c r="AE2">
-        <v>0.11482000000000001</v>
+        <v>0.18371199999999999</v>
       </c>
       <c r="AF2">
-        <v>0.11322599999999999</v>
+        <v>0.18116199999999999</v>
       </c>
       <c r="AG2">
-        <v>0.104754</v>
+        <v>0.167606</v>
       </c>
       <c r="AH2">
-        <v>9.7356999999999999E-2</v>
+        <v>0.15721399999999999</v>
       </c>
       <c r="AI2">
-        <v>9.5029000000000002E-2</v>
+        <v>0.15296399999999999</v>
       </c>
       <c r="AJ2">
-        <v>0.18155499999999999</v>
+        <v>0.29048800000000002</v>
       </c>
       <c r="AK2">
-        <v>0.18304100000000001</v>
+        <v>0.29286600000000002</v>
       </c>
       <c r="AL2">
-        <v>0.18577099999999999</v>
+        <v>0.29779899999999998</v>
       </c>
       <c r="AM2">
-        <v>0.174457</v>
+        <v>0.28410400000000002</v>
       </c>
       <c r="AN2">
-        <v>0.163547</v>
+        <v>0.26447500000000002</v>
       </c>
       <c r="AO2">
-        <v>0.17175399999999999</v>
+        <v>0.27785900000000002</v>
       </c>
       <c r="AP2">
         <v>58.137847999999998</v>
@@ -30374,58 +30374,58 @@
         <v>23.257286000000001</v>
       </c>
       <c r="X3">
-        <v>0.10348499999999999</v>
+        <v>0.165577</v>
       </c>
       <c r="Y3">
-        <v>0.111846</v>
+        <v>0.17644299999999999</v>
       </c>
       <c r="Z3">
-        <v>0.114396</v>
+        <v>0.183034</v>
       </c>
       <c r="AA3">
-        <v>0.106252</v>
+        <v>0.17000299999999999</v>
       </c>
       <c r="AB3">
-        <v>9.3878000000000003E-2</v>
+        <v>0.150204</v>
       </c>
       <c r="AC3">
-        <v>8.9113999999999999E-2</v>
+        <v>0.14258100000000001</v>
       </c>
       <c r="AD3">
-        <v>0.110447</v>
+        <v>0.17671500000000001</v>
       </c>
       <c r="AE3">
-        <v>0.117129</v>
+        <v>0.18740699999999999</v>
       </c>
       <c r="AF3">
-        <v>0.12217</v>
+        <v>0.19547200000000001</v>
       </c>
       <c r="AG3">
-        <v>0.11412799999999999</v>
+        <v>0.18260399999999999</v>
       </c>
       <c r="AH3">
-        <v>9.8920999999999995E-2</v>
+        <v>0.15918499999999999</v>
       </c>
       <c r="AI3">
-        <v>9.8183999999999994E-2</v>
+        <v>0.15733800000000001</v>
       </c>
       <c r="AJ3">
-        <v>0.17916699999999999</v>
+        <v>0.28666700000000001</v>
       </c>
       <c r="AK3">
-        <v>0.184557</v>
+        <v>0.295292</v>
       </c>
       <c r="AL3">
-        <v>0.194268</v>
+        <v>0.307531</v>
       </c>
       <c r="AM3">
-        <v>0.18637100000000001</v>
+        <v>0.29693999999999998</v>
       </c>
       <c r="AN3">
-        <v>0.16472899999999999</v>
+        <v>0.26608399999999999</v>
       </c>
       <c r="AO3">
-        <v>0.170927</v>
+        <v>0.27681899999999998</v>
       </c>
       <c r="AP3">
         <v>57.278246000000003</v>
@@ -30586,58 +30586,58 @@
         <v>23.345859000000001</v>
       </c>
       <c r="X4">
-        <v>9.9289000000000002E-2</v>
+        <v>0.158861</v>
       </c>
       <c r="Y4">
-        <v>0.10116</v>
+        <v>0.16344500000000001</v>
       </c>
       <c r="Z4">
-        <v>0.111044</v>
+        <v>0.177671</v>
       </c>
       <c r="AA4">
-        <v>0.104347</v>
+        <v>0.16695599999999999</v>
       </c>
       <c r="AB4">
-        <v>9.3779000000000001E-2</v>
+        <v>0.15004600000000001</v>
       </c>
       <c r="AC4">
-        <v>8.8595999999999994E-2</v>
+        <v>0.14175199999999999</v>
       </c>
       <c r="AD4">
-        <v>0.109995</v>
+        <v>0.17599200000000001</v>
       </c>
       <c r="AE4">
-        <v>0.11354400000000001</v>
+        <v>0.18167</v>
       </c>
       <c r="AF4">
-        <v>0.12562499999999999</v>
+        <v>0.20100100000000001</v>
       </c>
       <c r="AG4">
-        <v>0.116757</v>
+        <v>0.18681</v>
       </c>
       <c r="AH4">
-        <v>0.102793</v>
+        <v>0.16467699999999999</v>
       </c>
       <c r="AI4">
-        <v>0.10029200000000001</v>
+        <v>0.160606</v>
       </c>
       <c r="AJ4">
-        <v>0.174876</v>
+        <v>0.279802</v>
       </c>
       <c r="AK4">
-        <v>0.174868</v>
+        <v>0.27978999999999998</v>
       </c>
       <c r="AL4">
-        <v>0.19386</v>
+        <v>0.30743300000000001</v>
       </c>
       <c r="AM4">
-        <v>0.187219</v>
+        <v>0.29830400000000001</v>
       </c>
       <c r="AN4">
-        <v>0.17044500000000001</v>
+        <v>0.27347399999999999</v>
       </c>
       <c r="AO4">
-        <v>0.17169699999999999</v>
+        <v>0.27825499999999997</v>
       </c>
       <c r="AP4">
         <v>56.232588999999997</v>
@@ -30798,58 +30798,58 @@
         <v>24.748999999999999</v>
       </c>
       <c r="X5">
-        <v>9.9944000000000005E-2</v>
+        <v>0.15991</v>
       </c>
       <c r="Y5">
-        <v>9.9507999999999999E-2</v>
+        <v>0.16014600000000001</v>
       </c>
       <c r="Z5">
-        <v>0.11511200000000001</v>
+        <v>0.18417900000000001</v>
       </c>
       <c r="AA5">
-        <v>0.10510899999999999</v>
+        <v>0.16817499999999999</v>
       </c>
       <c r="AB5">
-        <v>9.5315999999999998E-2</v>
+        <v>0.152506</v>
       </c>
       <c r="AC5">
-        <v>9.6723000000000003E-2</v>
+        <v>0.15475900000000001</v>
       </c>
       <c r="AD5">
-        <v>0.110981</v>
+        <v>0.177569</v>
       </c>
       <c r="AE5">
-        <v>0.113443</v>
+        <v>0.181508</v>
       </c>
       <c r="AF5">
-        <v>0.12650800000000001</v>
+        <v>0.20241300000000001</v>
       </c>
       <c r="AG5">
-        <v>0.1173</v>
+        <v>0.18767900000000001</v>
       </c>
       <c r="AH5">
-        <v>0.10666100000000001</v>
+        <v>0.17043</v>
       </c>
       <c r="AI5">
-        <v>0.103023</v>
+        <v>0.16469700000000001</v>
       </c>
       <c r="AJ5">
-        <v>0.1782</v>
+        <v>0.28511999999999998</v>
       </c>
       <c r="AK5">
-        <v>0.17216699999999999</v>
+        <v>0.27546700000000002</v>
       </c>
       <c r="AL5">
-        <v>0.19592100000000001</v>
+        <v>0.30977900000000003</v>
       </c>
       <c r="AM5">
-        <v>0.190994</v>
+        <v>0.302867</v>
       </c>
       <c r="AN5">
-        <v>0.17677100000000001</v>
+        <v>0.28281600000000001</v>
       </c>
       <c r="AO5">
-        <v>0.17827699999999999</v>
+        <v>0.28553499999999998</v>
       </c>
       <c r="AP5">
         <v>54.721451000000002</v>
@@ -31010,58 +31010,58 @@
         <v>26.034576999999999</v>
       </c>
       <c r="X6">
-        <v>9.8500000000000004E-2</v>
+        <v>0.15759999999999999</v>
       </c>
       <c r="Y6">
-        <v>0.102534</v>
+        <v>0.163301</v>
       </c>
       <c r="Z6">
-        <v>0.11377900000000001</v>
+        <v>0.18204600000000001</v>
       </c>
       <c r="AA6">
-        <v>0.101573</v>
+        <v>0.16251699999999999</v>
       </c>
       <c r="AB6">
-        <v>9.4403000000000001E-2</v>
+        <v>0.15104500000000001</v>
       </c>
       <c r="AC6">
-        <v>9.1787999999999995E-2</v>
+        <v>0.14685999999999999</v>
       </c>
       <c r="AD6">
-        <v>0.107928</v>
+        <v>0.17268500000000001</v>
       </c>
       <c r="AE6">
-        <v>0.114422</v>
+        <v>0.18307499999999999</v>
       </c>
       <c r="AF6">
-        <v>0.12596499999999999</v>
+        <v>0.201544</v>
       </c>
       <c r="AG6">
-        <v>0.11314299999999999</v>
+        <v>0.18102799999999999</v>
       </c>
       <c r="AH6">
-        <v>0.108515</v>
+        <v>0.173401</v>
       </c>
       <c r="AI6">
-        <v>0.10333199999999999</v>
+        <v>0.165322</v>
       </c>
       <c r="AJ6">
-        <v>0.175094</v>
+        <v>0.28015000000000001</v>
       </c>
       <c r="AK6">
-        <v>0.17500399999999999</v>
+        <v>0.28000599999999998</v>
       </c>
       <c r="AL6">
-        <v>0.19194700000000001</v>
+        <v>0.30525999999999998</v>
       </c>
       <c r="AM6">
-        <v>0.19042799999999999</v>
+        <v>0.30233500000000002</v>
       </c>
       <c r="AN6">
-        <v>0.18232300000000001</v>
+        <v>0.29143200000000002</v>
       </c>
       <c r="AO6">
-        <v>0.182392</v>
+        <v>0.29094199999999998</v>
       </c>
       <c r="AP6">
         <v>53.812973</v>
@@ -31222,58 +31222,58 @@
         <v>26.827175</v>
       </c>
       <c r="X7">
-        <v>9.8072999999999994E-2</v>
+        <v>0.156918</v>
       </c>
       <c r="Y7">
-        <v>0.100317</v>
+        <v>0.15901899999999999</v>
       </c>
       <c r="Z7">
-        <v>0.109113</v>
+        <v>0.17458199999999999</v>
       </c>
       <c r="AA7">
-        <v>0.100385</v>
+        <v>0.16061600000000001</v>
       </c>
       <c r="AB7">
-        <v>0.10188999999999999</v>
+        <v>0.163024</v>
       </c>
       <c r="AC7">
-        <v>9.2531000000000002E-2</v>
+        <v>0.14805099999999999</v>
       </c>
       <c r="AD7">
-        <v>0.104711</v>
+        <v>0.16753799999999999</v>
       </c>
       <c r="AE7">
-        <v>0.10810599999999999</v>
+        <v>0.17297000000000001</v>
       </c>
       <c r="AF7">
-        <v>0.120841</v>
+        <v>0.19334599999999999</v>
       </c>
       <c r="AG7">
-        <v>0.11522300000000001</v>
+        <v>0.18435699999999999</v>
       </c>
       <c r="AH7">
-        <v>0.11201899999999999</v>
+        <v>0.17852699999999999</v>
       </c>
       <c r="AI7">
-        <v>0.103452</v>
+        <v>0.165548</v>
       </c>
       <c r="AJ7">
-        <v>0.173343</v>
+        <v>0.27734799999999998</v>
       </c>
       <c r="AK7">
-        <v>0.17366699999999999</v>
+        <v>0.277868</v>
       </c>
       <c r="AL7">
-        <v>0.19158500000000001</v>
+        <v>0.30413099999999998</v>
       </c>
       <c r="AM7">
-        <v>0.19000800000000001</v>
+        <v>0.30146400000000001</v>
       </c>
       <c r="AN7">
-        <v>0.189358</v>
+        <v>0.30049100000000001</v>
       </c>
       <c r="AO7">
-        <v>0.18429899999999999</v>
+        <v>0.29401500000000003</v>
       </c>
       <c r="AP7">
         <v>53.480555000000003</v>
@@ -31434,58 +31434,58 @@
         <v>27.080991999999998</v>
       </c>
       <c r="X8">
-        <v>9.3978000000000006E-2</v>
+        <v>0.150365</v>
       </c>
       <c r="Y8">
-        <v>8.8432999999999998E-2</v>
+        <v>0.144459</v>
       </c>
       <c r="Z8">
-        <v>9.4974000000000003E-2</v>
+        <v>0.15195700000000001</v>
       </c>
       <c r="AA8">
-        <v>9.2952000000000007E-2</v>
+        <v>0.148724</v>
       </c>
       <c r="AB8">
-        <v>9.4171000000000005E-2</v>
+        <v>0.150673</v>
       </c>
       <c r="AC8">
-        <v>8.8553999999999994E-2</v>
+        <v>0.141683</v>
       </c>
       <c r="AD8">
-        <v>0.103505</v>
+        <v>0.16560800000000001</v>
       </c>
       <c r="AE8">
-        <v>9.9346000000000004E-2</v>
+        <v>0.15895400000000001</v>
       </c>
       <c r="AF8">
-        <v>0.105156</v>
+        <v>0.16824900000000001</v>
       </c>
       <c r="AG8">
-        <v>0.10532900000000001</v>
+        <v>0.16852600000000001</v>
       </c>
       <c r="AH8">
-        <v>0.110615</v>
+        <v>0.17678099999999999</v>
       </c>
       <c r="AI8">
-        <v>0.102961</v>
+        <v>0.164967</v>
       </c>
       <c r="AJ8">
-        <v>0.17561299999999999</v>
+        <v>0.28098099999999998</v>
       </c>
       <c r="AK8">
-        <v>0.16165099999999999</v>
+        <v>0.25864100000000001</v>
       </c>
       <c r="AL8">
-        <v>0.17594299999999999</v>
+        <v>0.28576000000000001</v>
       </c>
       <c r="AM8">
-        <v>0.18113899999999999</v>
+        <v>0.29153600000000002</v>
       </c>
       <c r="AN8">
-        <v>0.187386</v>
+        <v>0.300734</v>
       </c>
       <c r="AO8">
-        <v>0.184367</v>
+        <v>0.29499500000000001</v>
       </c>
       <c r="AP8">
         <v>53.385734999999997</v>
@@ -31646,58 +31646,58 @@
         <v>28.485783999999999</v>
       </c>
       <c r="X9">
-        <v>8.9847999999999997E-2</v>
+        <v>0.143757</v>
       </c>
       <c r="Y9">
-        <v>8.7998000000000007E-2</v>
+        <v>0.141323</v>
       </c>
       <c r="Z9">
-        <v>9.4650999999999999E-2</v>
+        <v>0.15144099999999999</v>
       </c>
       <c r="AA9">
-        <v>0.10310800000000001</v>
+        <v>0.16497300000000001</v>
       </c>
       <c r="AB9">
-        <v>0.100673</v>
+        <v>0.161076</v>
       </c>
       <c r="AC9">
-        <v>9.6443000000000001E-2</v>
+        <v>0.154312</v>
       </c>
       <c r="AD9">
-        <v>0.103105</v>
+        <v>0.164967</v>
       </c>
       <c r="AE9">
-        <v>9.9196999999999994E-2</v>
+        <v>0.158716</v>
       </c>
       <c r="AF9">
-        <v>0.105448</v>
+        <v>0.168716</v>
       </c>
       <c r="AG9">
-        <v>0.117245</v>
+        <v>0.18759200000000001</v>
       </c>
       <c r="AH9">
-        <v>0.114202</v>
+        <v>0.18168200000000001</v>
       </c>
       <c r="AI9">
-        <v>0.105457</v>
+        <v>0.168517</v>
       </c>
       <c r="AJ9">
-        <v>0.177563</v>
+        <v>0.28410099999999999</v>
       </c>
       <c r="AK9">
-        <v>0.161519</v>
+        <v>0.25842999999999999</v>
       </c>
       <c r="AL9">
-        <v>0.18185599999999999</v>
+        <v>0.29222500000000001</v>
       </c>
       <c r="AM9">
-        <v>0.192134</v>
+        <v>0.30364200000000002</v>
       </c>
       <c r="AN9">
-        <v>0.19327900000000001</v>
+        <v>0.30668499999999999</v>
       </c>
       <c r="AO9">
-        <v>0.186112</v>
+        <v>0.297068</v>
       </c>
       <c r="AP9">
         <v>53.496406999999998</v>
@@ -31858,58 +31858,58 @@
         <v>29.178816999999999</v>
       </c>
       <c r="X10">
-        <v>8.8099999999999998E-2</v>
+        <v>0.14096</v>
       </c>
       <c r="Y10">
-        <v>8.8665999999999995E-2</v>
+        <v>0.14142099999999999</v>
       </c>
       <c r="Z10">
-        <v>8.9976E-2</v>
+        <v>0.14396200000000001</v>
       </c>
       <c r="AA10">
-        <v>9.3530000000000002E-2</v>
+        <v>0.149648</v>
       </c>
       <c r="AB10">
-        <v>9.3729999999999994E-2</v>
+        <v>0.14996799999999999</v>
       </c>
       <c r="AC10">
-        <v>9.0878E-2</v>
+        <v>0.14540400000000001</v>
       </c>
       <c r="AD10">
-        <v>0.10288799999999999</v>
+        <v>0.16462099999999999</v>
       </c>
       <c r="AE10">
-        <v>0.102051</v>
+        <v>0.16328200000000001</v>
       </c>
       <c r="AF10">
-        <v>0.10527</v>
+        <v>0.168432</v>
       </c>
       <c r="AG10">
-        <v>0.108543</v>
+        <v>0.17366899999999999</v>
       </c>
       <c r="AH10">
-        <v>0.111334</v>
+        <v>0.17747499999999999</v>
       </c>
       <c r="AI10">
-        <v>0.104961</v>
+        <v>0.167904</v>
       </c>
       <c r="AJ10">
-        <v>0.17840900000000001</v>
+        <v>0.28545399999999999</v>
       </c>
       <c r="AK10">
-        <v>0.16686699999999999</v>
+        <v>0.26698699999999997</v>
       </c>
       <c r="AL10">
-        <v>0.18157000000000001</v>
+        <v>0.29194999999999999</v>
       </c>
       <c r="AM10">
-        <v>0.18401200000000001</v>
+        <v>0.29436299999999999</v>
       </c>
       <c r="AN10">
-        <v>0.191248</v>
+        <v>0.30426599999999998</v>
       </c>
       <c r="AO10">
-        <v>0.18624399999999999</v>
+        <v>0.29756500000000002</v>
       </c>
       <c r="AP10">
         <v>52.755482999999998</v>
@@ -32070,58 +32070,58 @@
         <v>29.598277</v>
       </c>
       <c r="X11">
-        <v>8.7345000000000006E-2</v>
+        <v>0.13975199999999999</v>
       </c>
       <c r="Y11">
-        <v>8.6901000000000006E-2</v>
+        <v>0.13985300000000001</v>
       </c>
       <c r="Z11">
-        <v>8.8381000000000001E-2</v>
+        <v>0.14140900000000001</v>
       </c>
       <c r="AA11">
-        <v>8.7720000000000006E-2</v>
+        <v>0.140352</v>
       </c>
       <c r="AB11">
-        <v>8.9471999999999996E-2</v>
+        <v>0.14315600000000001</v>
       </c>
       <c r="AC11">
-        <v>9.1339000000000004E-2</v>
+        <v>0.146143</v>
       </c>
       <c r="AD11">
-        <v>0.10463</v>
+        <v>0.167409</v>
       </c>
       <c r="AE11">
-        <v>0.10130400000000001</v>
+        <v>0.16208700000000001</v>
       </c>
       <c r="AF11">
-        <v>0.10238700000000001</v>
+        <v>0.16381999999999999</v>
       </c>
       <c r="AG11">
-        <v>0.10138900000000001</v>
+        <v>0.16222300000000001</v>
       </c>
       <c r="AH11">
-        <v>0.10509499999999999</v>
+        <v>0.16856499999999999</v>
       </c>
       <c r="AI11">
-        <v>0.10433199999999999</v>
+        <v>0.16692899999999999</v>
       </c>
       <c r="AJ11">
-        <v>0.18068600000000001</v>
+        <v>0.28909800000000002</v>
       </c>
       <c r="AK11">
-        <v>0.16702500000000001</v>
+        <v>0.26723999999999998</v>
       </c>
       <c r="AL11">
-        <v>0.17824400000000001</v>
+        <v>0.28834900000000002</v>
       </c>
       <c r="AM11">
-        <v>0.17822299999999999</v>
+        <v>0.28762500000000002</v>
       </c>
       <c r="AN11">
-        <v>0.18532000000000001</v>
+        <v>0.29679299999999997</v>
       </c>
       <c r="AO11">
-        <v>0.18742</v>
+        <v>0.29847299999999999</v>
       </c>
       <c r="AP11">
         <v>52.447211000000003</v>
@@ -32282,58 +32282,58 @@
         <v>28.260161</v>
       </c>
       <c r="X12">
-        <v>9.2862E-2</v>
+        <v>0.14857899999999999</v>
       </c>
       <c r="Y12">
-        <v>9.4047000000000006E-2</v>
+        <v>0.15077399999999999</v>
       </c>
       <c r="Z12">
-        <v>9.2913999999999997E-2</v>
+        <v>0.14866199999999999</v>
       </c>
       <c r="AA12">
-        <v>9.0728000000000003E-2</v>
+        <v>0.14516599999999999</v>
       </c>
       <c r="AB12">
-        <v>9.1449000000000003E-2</v>
+        <v>0.146319</v>
       </c>
       <c r="AC12">
-        <v>9.2638999999999999E-2</v>
+        <v>0.14822399999999999</v>
       </c>
       <c r="AD12">
-        <v>0.10549600000000001</v>
+        <v>0.168793</v>
       </c>
       <c r="AE12">
-        <v>0.108518</v>
+        <v>0.173628</v>
       </c>
       <c r="AF12">
-        <v>0.10270600000000001</v>
+        <v>0.164329</v>
       </c>
       <c r="AG12">
-        <v>0.102369</v>
+        <v>0.16378999999999999</v>
       </c>
       <c r="AH12">
-        <v>9.8409999999999997E-2</v>
+        <v>0.158771</v>
       </c>
       <c r="AI12">
-        <v>0.101956</v>
+        <v>0.16317999999999999</v>
       </c>
       <c r="AJ12">
-        <v>0.177703</v>
+        <v>0.28432499999999999</v>
       </c>
       <c r="AK12">
-        <v>0.16957800000000001</v>
+        <v>0.27132499999999998</v>
       </c>
       <c r="AL12">
-        <v>0.17965600000000001</v>
+        <v>0.29001100000000002</v>
       </c>
       <c r="AM12">
-        <v>0.174119</v>
+        <v>0.28262599999999999</v>
       </c>
       <c r="AN12">
-        <v>0.17427699999999999</v>
+        <v>0.28032899999999999</v>
       </c>
       <c r="AO12">
-        <v>0.184644</v>
+        <v>0.29478700000000002</v>
       </c>
       <c r="AP12">
         <v>54.206525999999997</v>
@@ -32432,9 +32432,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -32588,26 +32591,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9EAE9DF-01E1-49E5-8603-E69C76183A40}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FABF7966-B5A2-43B3-86A8-0DA6CE927C7F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="728ae82c-3d1b-45f0-8d67-959bce25b5b0"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -32631,9 +32623,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FABF7966-B5A2-43B3-86A8-0DA6CE927C7F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9EAE9DF-01E1-49E5-8603-E69C76183A40}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="728ae82c-3d1b-45f0-8d67-959bce25b5b0"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Data/2014_F013B4_CO_ISOS/2014_F013B4_CO_ISOS_SoilAnalysis.xlsx
+++ b/Data/2014_F013B4_CO_ISOS/2014_F013B4_CO_ISOS_SoilAnalysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\mnt\Data1\USDA-ALARC\GIS\PDI project\cottondata\Data\2014_F013B4_CO_ISOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9758605B-4105-44E7-9C86-7E0C88ACA3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114E6D29-9DAB-4340-81CC-2EF9A12F3493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1425" yWindow="-24390" windowWidth="17775" windowHeight="24285" xr2:uid="{8C00C1F2-89F9-4A44-A266-AB1BCF5C18BB}"/>
+    <workbookView xWindow="-1815" yWindow="-28410" windowWidth="16335" windowHeight="23370" xr2:uid="{8C00C1F2-89F9-4A44-A266-AB1BCF5C18BB}"/>
   </bookViews>
   <sheets>
     <sheet name="SoilDJH" sheetId="4" r:id="rId1"/>
@@ -446,12 +446,6 @@
     <t>Plot</t>
   </si>
   <si>
-    <t>2015d118EM38</t>
-  </si>
-  <si>
-    <t>2015d119EM38</t>
-  </si>
-  <si>
     <t>SLSND015</t>
   </si>
   <si>
@@ -1314,6 +1308,12 @@
   </si>
   <si>
     <t>2013d260EM38V</t>
+  </si>
+  <si>
+    <t>2015d118EM38V</t>
+  </si>
+  <si>
+    <t>2015d119EM38V</t>
   </si>
 </sst>
 </file>
@@ -1696,13 +1696,13 @@
         <v>122</v>
       </c>
       <c r="B1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E1" t="s">
         <v>134</v>
@@ -1713,7 +1713,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C2">
         <v>409014.13040000002</v>
@@ -1730,7 +1730,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C3">
         <v>409013.595399999</v>
@@ -1747,7 +1747,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C4">
         <v>409013.23430000001</v>
@@ -1764,7 +1764,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C5">
         <v>409012.73710000003</v>
@@ -1781,7 +1781,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C6">
         <v>409012.32490000001</v>
@@ -1798,7 +1798,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C7">
         <v>409011.88799999899</v>
@@ -1815,7 +1815,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C8">
         <v>408983.429999999</v>
@@ -1832,7 +1832,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C9">
         <v>408983.89409999899</v>
@@ -1849,7 +1849,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C10">
         <v>408984.30259999901</v>
@@ -1866,7 +1866,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C11">
         <v>408984.79070000001</v>
@@ -1883,7 +1883,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C12">
         <v>408985.21360000002</v>
@@ -1900,7 +1900,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C13">
         <v>408985.649299999</v>
@@ -1917,7 +1917,7 @@
         <v>131</v>
       </c>
       <c r="B14" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C14">
         <v>408992.87400000001</v>
@@ -1934,7 +1934,7 @@
         <v>132</v>
       </c>
       <c r="B15" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C15">
         <v>408992.37520000001</v>
@@ -1951,7 +1951,7 @@
         <v>133</v>
       </c>
       <c r="B16" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C16">
         <v>408991.93300000002</v>
@@ -1968,7 +1968,7 @@
         <v>134</v>
       </c>
       <c r="B17" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C17">
         <v>408991.4412</v>
@@ -1985,7 +1985,7 @@
         <v>135</v>
       </c>
       <c r="B18" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C18">
         <v>408990.94170000002</v>
@@ -2002,7 +2002,7 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C19">
         <v>408957.18540000002</v>
@@ -2019,7 +2019,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C20">
         <v>408956.76750000002</v>
@@ -2036,7 +2036,7 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C21">
         <v>408956.30570000003</v>
@@ -2053,7 +2053,7 @@
         <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C22">
         <v>408955.91499999899</v>
@@ -2070,7 +2070,7 @@
         <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C23">
         <v>408955.44280000002</v>
@@ -2087,7 +2087,7 @@
         <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C24">
         <v>408955.01179999899</v>
@@ -2104,7 +2104,7 @@
         <v>136</v>
       </c>
       <c r="B25" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C25">
         <v>408962.41840000002</v>
@@ -2121,7 +2121,7 @@
         <v>137</v>
       </c>
       <c r="B26" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C26">
         <v>408961.93680000002</v>
@@ -2138,7 +2138,7 @@
         <v>138</v>
       </c>
       <c r="B27" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C27">
         <v>408961.4645</v>
@@ -2155,7 +2155,7 @@
         <v>139</v>
       </c>
       <c r="B28" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C28">
         <v>408960.96830000001</v>
@@ -2172,7 +2172,7 @@
         <v>140</v>
       </c>
       <c r="B29" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C29">
         <v>408960.493599999</v>
@@ -2189,7 +2189,7 @@
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C30">
         <v>408926.557299999</v>
@@ -2206,7 +2206,7 @@
         <v>20</v>
       </c>
       <c r="B31" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C31">
         <v>408926.97979999898</v>
@@ -2223,7 +2223,7 @@
         <v>21</v>
       </c>
       <c r="B32" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C32">
         <v>408927.42930000002</v>
@@ -2240,7 +2240,7 @@
         <v>22</v>
       </c>
       <c r="B33" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C33">
         <v>408927.88109999901</v>
@@ -2257,7 +2257,7 @@
         <v>23</v>
       </c>
       <c r="B34" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C34">
         <v>408928.31640000001</v>
@@ -2274,7 +2274,7 @@
         <v>24</v>
       </c>
       <c r="B35" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C35">
         <v>408928.783999999</v>
@@ -2291,7 +2291,7 @@
         <v>141</v>
       </c>
       <c r="B36" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C36">
         <v>408936.025599999</v>
@@ -2308,7 +2308,7 @@
         <v>142</v>
       </c>
       <c r="B37" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C37">
         <v>408935.529199999</v>
@@ -2325,7 +2325,7 @@
         <v>143</v>
       </c>
       <c r="B38" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C38">
         <v>408935.03840000002</v>
@@ -2342,7 +2342,7 @@
         <v>144</v>
       </c>
       <c r="B39" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C39">
         <v>408934.55099999899</v>
@@ -2359,7 +2359,7 @@
         <v>145</v>
       </c>
       <c r="B40" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C40">
         <v>408934.06530000002</v>
@@ -2376,7 +2376,7 @@
         <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C41">
         <v>408901.33329999901</v>
@@ -2393,7 +2393,7 @@
         <v>26</v>
       </c>
       <c r="B42" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C42">
         <v>408900.9032</v>
@@ -2410,7 +2410,7 @@
         <v>27</v>
       </c>
       <c r="B43" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C43">
         <v>408900.44150000002</v>
@@ -2427,7 +2427,7 @@
         <v>28</v>
       </c>
       <c r="B44" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C44">
         <v>408899.99949999899</v>
@@ -2444,7 +2444,7 @@
         <v>29</v>
       </c>
       <c r="B45" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C45">
         <v>408899.580599999</v>
@@ -2461,7 +2461,7 @@
         <v>30</v>
       </c>
       <c r="B46" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C46">
         <v>408899.109999999</v>
@@ -2478,7 +2478,7 @@
         <v>146</v>
       </c>
       <c r="B47" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C47">
         <v>408906.29479999898</v>
@@ -2495,7 +2495,7 @@
         <v>147</v>
       </c>
       <c r="B48" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C48">
         <v>408905.79359999899</v>
@@ -2512,7 +2512,7 @@
         <v>148</v>
       </c>
       <c r="B49" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C49">
         <v>408905.32140000002</v>
@@ -2529,7 +2529,7 @@
         <v>149</v>
       </c>
       <c r="B50" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C50">
         <v>408904.8211</v>
@@ -2546,7 +2546,7 @@
         <v>150</v>
       </c>
       <c r="B51" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C51">
         <v>408904.35749999899</v>
@@ -2563,7 +2563,7 @@
         <v>31</v>
       </c>
       <c r="B52" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C52">
         <v>408870.67979999899</v>
@@ -2580,7 +2580,7 @@
         <v>32</v>
       </c>
       <c r="B53" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C53">
         <v>408871.13660000003</v>
@@ -2597,7 +2597,7 @@
         <v>33</v>
       </c>
       <c r="B54" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C54">
         <v>408871.57900000003</v>
@@ -2614,7 +2614,7 @@
         <v>34</v>
       </c>
       <c r="B55" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C55">
         <v>408872.00809999899</v>
@@ -2631,7 +2631,7 @@
         <v>35</v>
       </c>
       <c r="B56" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C56">
         <v>408872.451899999</v>
@@ -2648,7 +2648,7 @@
         <v>36</v>
       </c>
       <c r="B57" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C57">
         <v>408872.89059999899</v>
@@ -2665,7 +2665,7 @@
         <v>151</v>
       </c>
       <c r="B58" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C58">
         <v>408879.86940000003</v>
@@ -2682,7 +2682,7 @@
         <v>152</v>
       </c>
       <c r="B59" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C59">
         <v>408879.400499999</v>
@@ -2699,7 +2699,7 @@
         <v>153</v>
       </c>
       <c r="B60" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C60">
         <v>408878.89939999901</v>
@@ -2716,7 +2716,7 @@
         <v>154</v>
       </c>
       <c r="B61" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C61">
         <v>408878.41070000001</v>
@@ -2733,7 +2733,7 @@
         <v>155</v>
       </c>
       <c r="B62" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C62">
         <v>408877.92340000003</v>
@@ -2750,7 +2750,7 @@
         <v>37</v>
       </c>
       <c r="B63" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C63">
         <v>408845.46089999902</v>
@@ -2767,7 +2767,7 @@
         <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C64">
         <v>408845.02049999899</v>
@@ -2784,7 +2784,7 @@
         <v>39</v>
       </c>
       <c r="B65" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C65">
         <v>408844.56319999899</v>
@@ -2801,7 +2801,7 @@
         <v>40</v>
       </c>
       <c r="B66" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C66">
         <v>408844.13500000001</v>
@@ -2818,7 +2818,7 @@
         <v>41</v>
       </c>
       <c r="B67" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C67">
         <v>408843.68329999998</v>
@@ -2835,7 +2835,7 @@
         <v>42</v>
       </c>
       <c r="B68" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C68">
         <v>408843.26179999899</v>
@@ -2852,7 +2852,7 @@
         <v>156</v>
       </c>
       <c r="B69" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C69">
         <v>408850.18070000003</v>
@@ -2869,7 +2869,7 @@
         <v>157</v>
       </c>
       <c r="B70" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C70">
         <v>408849.70020000002</v>
@@ -2886,7 +2886,7 @@
         <v>158</v>
       </c>
       <c r="B71" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C71">
         <v>408849.219199999</v>
@@ -2903,7 +2903,7 @@
         <v>159</v>
       </c>
       <c r="B72" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C72">
         <v>408848.73200000002</v>
@@ -2920,7 +2920,7 @@
         <v>160</v>
       </c>
       <c r="B73" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C73">
         <v>408848.231299999</v>
@@ -2937,7 +2937,7 @@
         <v>43</v>
       </c>
       <c r="B74" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C74">
         <v>408814.80080000003</v>
@@ -2954,7 +2954,7 @@
         <v>44</v>
       </c>
       <c r="B75" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C75">
         <v>408815.248499999</v>
@@ -2971,7 +2971,7 @@
         <v>45</v>
       </c>
       <c r="B76" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C76">
         <v>408815.666399999</v>
@@ -2988,7 +2988,7 @@
         <v>46</v>
       </c>
       <c r="B77" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C77">
         <v>408816.12689999898</v>
@@ -3005,7 +3005,7 @@
         <v>47</v>
       </c>
       <c r="B78" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C78">
         <v>408816.55469999899</v>
@@ -3022,7 +3022,7 @@
         <v>48</v>
       </c>
       <c r="B79" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C79">
         <v>408817.00829999999</v>
@@ -3039,7 +3039,7 @@
         <v>161</v>
       </c>
       <c r="B80" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C80">
         <v>408823.76260000002</v>
@@ -3056,7 +3056,7 @@
         <v>162</v>
       </c>
       <c r="B81" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C81">
         <v>408823.264399999</v>
@@ -3073,7 +3073,7 @@
         <v>163</v>
       </c>
       <c r="B82" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C82">
         <v>408822.77899999899</v>
@@ -3090,7 +3090,7 @@
         <v>164</v>
       </c>
       <c r="B83" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C83">
         <v>408822.312299999</v>
@@ -3107,7 +3107,7 @@
         <v>165</v>
       </c>
       <c r="B84" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C84">
         <v>408821.829399999</v>
@@ -3124,7 +3124,7 @@
         <v>49</v>
       </c>
       <c r="B85" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C85">
         <v>408788.581799999</v>
@@ -3141,7 +3141,7 @@
         <v>50</v>
       </c>
       <c r="B86" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C86">
         <v>408788.11670000001</v>
@@ -3158,7 +3158,7 @@
         <v>51</v>
       </c>
       <c r="B87" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C87">
         <v>408787.67560000002</v>
@@ -3175,7 +3175,7 @@
         <v>52</v>
       </c>
       <c r="B88" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C88">
         <v>408787.222799999</v>
@@ -3192,7 +3192,7 @@
         <v>53</v>
       </c>
       <c r="B89" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C89">
         <v>408786.80749999901</v>
@@ -3209,7 +3209,7 @@
         <v>54</v>
       </c>
       <c r="B90" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C90">
         <v>408786.36930000002</v>
@@ -3226,7 +3226,7 @@
         <v>166</v>
       </c>
       <c r="B91" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C91">
         <v>408793.35800000001</v>
@@ -3243,7 +3243,7 @@
         <v>167</v>
       </c>
       <c r="B92" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C92">
         <v>408792.866099999</v>
@@ -3260,7 +3260,7 @@
         <v>168</v>
       </c>
       <c r="B93" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C93">
         <v>408792.38530000002</v>
@@ -3277,7 +3277,7 @@
         <v>169</v>
       </c>
       <c r="B94" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C94">
         <v>408791.8947</v>
@@ -3294,7 +3294,7 @@
         <v>170</v>
       </c>
       <c r="B95" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C95">
         <v>408791.43050000002</v>
@@ -3311,7 +3311,7 @@
         <v>55</v>
       </c>
       <c r="B96" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C96">
         <v>408757.90980000002</v>
@@ -3328,7 +3328,7 @@
         <v>56</v>
       </c>
       <c r="B97" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C97">
         <v>408758.367499999</v>
@@ -3345,7 +3345,7 @@
         <v>57</v>
       </c>
       <c r="B98" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C98">
         <v>408758.807399999</v>
@@ -3362,7 +3362,7 @@
         <v>58</v>
       </c>
       <c r="B99" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C99">
         <v>408759.24219999899</v>
@@ -3379,7 +3379,7 @@
         <v>59</v>
       </c>
       <c r="B100" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C100">
         <v>408759.692099999</v>
@@ -3396,7 +3396,7 @@
         <v>60</v>
       </c>
       <c r="B101" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C101">
         <v>408760.11839999899</v>
@@ -3413,7 +3413,7 @@
         <v>171</v>
       </c>
       <c r="B102" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C102">
         <v>408766.92910000001</v>
@@ -3430,7 +3430,7 @@
         <v>172</v>
       </c>
       <c r="B103" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C103">
         <v>408766.46409999899</v>
@@ -3447,7 +3447,7 @@
         <v>173</v>
       </c>
       <c r="B104" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C104">
         <v>408765.99229999899</v>
@@ -3464,7 +3464,7 @@
         <v>174</v>
       </c>
       <c r="B105" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C105">
         <v>408765.47999999899</v>
@@ -3481,7 +3481,7 @@
         <v>175</v>
       </c>
       <c r="B106" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C106">
         <v>408765.01639999897</v>
@@ -3498,7 +3498,7 @@
         <v>61</v>
       </c>
       <c r="B107" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C107">
         <v>408674.80969999899</v>
@@ -3515,7 +3515,7 @@
         <v>62</v>
       </c>
       <c r="B108" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C108">
         <v>408674.3175</v>
@@ -3532,7 +3532,7 @@
         <v>63</v>
       </c>
       <c r="B109" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C109">
         <v>408673.885899999</v>
@@ -3549,7 +3549,7 @@
         <v>64</v>
       </c>
       <c r="B110" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C110">
         <v>408673.42570000002</v>
@@ -3566,7 +3566,7 @@
         <v>65</v>
       </c>
       <c r="B111" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C111">
         <v>408673.00859999901</v>
@@ -3583,7 +3583,7 @@
         <v>66</v>
       </c>
       <c r="B112" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C112">
         <v>408672.59139999899</v>
@@ -3600,7 +3600,7 @@
         <v>176</v>
       </c>
       <c r="B113" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C113">
         <v>408680.68900000001</v>
@@ -3617,7 +3617,7 @@
         <v>177</v>
       </c>
       <c r="B114" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C114">
         <v>408680.20289999899</v>
@@ -3634,7 +3634,7 @@
         <v>178</v>
       </c>
       <c r="B115" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C115">
         <v>408679.7047</v>
@@ -3651,7 +3651,7 @@
         <v>179</v>
       </c>
       <c r="B116" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C116">
         <v>408679.21340000001</v>
@@ -3668,7 +3668,7 @@
         <v>180</v>
       </c>
       <c r="B117" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C117">
         <v>408678.73639999999</v>
@@ -3698,13 +3698,13 @@
         <v>122</v>
       </c>
       <c r="B1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D1" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E1" t="s">
         <v>134</v>
@@ -3715,7 +3715,7 @@
         <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C2">
         <v>409014.52750000003</v>
@@ -3732,7 +3732,7 @@
         <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C3">
         <v>409016.286599999</v>
@@ -3749,7 +3749,7 @@
         <v>151</v>
       </c>
       <c r="B4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C4">
         <v>409015.53</v>
@@ -3766,7 +3766,7 @@
         <v>152</v>
       </c>
       <c r="B5" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C5">
         <v>409014.96</v>
@@ -3783,7 +3783,7 @@
         <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C6">
         <v>409000.4903</v>
@@ -3800,7 +3800,7 @@
         <v>71</v>
       </c>
       <c r="B7" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C7">
         <v>408997.63040000002</v>
@@ -3817,7 +3817,7 @@
         <v>72</v>
       </c>
       <c r="B8" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C8">
         <v>408987.19380000001</v>
@@ -3834,7 +3834,7 @@
         <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C9">
         <v>408982.38959999901</v>
@@ -3851,7 +3851,7 @@
         <v>146</v>
       </c>
       <c r="B10" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C10">
         <v>408985.71999999898</v>
@@ -3868,7 +3868,7 @@
         <v>147</v>
       </c>
       <c r="B11" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C11">
         <v>408984.80999999901</v>
@@ -3885,7 +3885,7 @@
         <v>148</v>
       </c>
       <c r="B12" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C12">
         <v>408983.89</v>
@@ -3902,7 +3902,7 @@
         <v>149</v>
       </c>
       <c r="B13" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C13">
         <v>409002.11999999901</v>
@@ -3919,7 +3919,7 @@
         <v>150</v>
       </c>
       <c r="B14" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C14">
         <v>409003.26</v>
@@ -3936,7 +3936,7 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C15">
         <v>408957.29330000002</v>
@@ -3953,7 +3953,7 @@
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C16">
         <v>408956.69130000001</v>
@@ -3970,7 +3970,7 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C17">
         <v>408956.084399999</v>
@@ -3987,7 +3987,7 @@
         <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C18">
         <v>408955.49589999899</v>
@@ -4004,7 +4004,7 @@
         <v>74</v>
       </c>
       <c r="B19" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C19">
         <v>408973.7121</v>
@@ -4021,7 +4021,7 @@
         <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C20">
         <v>408968.074599999</v>
@@ -4038,7 +4038,7 @@
         <v>84</v>
       </c>
       <c r="B21" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C21">
         <v>408961.65999999898</v>
@@ -4055,7 +4055,7 @@
         <v>144</v>
       </c>
       <c r="B22" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C22">
         <v>408961.76</v>
@@ -4072,7 +4072,7 @@
         <v>145</v>
       </c>
       <c r="B23" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C23">
         <v>408963.02</v>
@@ -4089,7 +4089,7 @@
         <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C24">
         <v>408943.05879999901</v>
@@ -4106,7 +4106,7 @@
         <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C25">
         <v>408942.48519999901</v>
@@ -4123,7 +4123,7 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C26">
         <v>408941.846599999</v>
@@ -4140,7 +4140,7 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C27">
         <v>408941.274299999</v>
@@ -4157,7 +4157,7 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C28">
         <v>408928.85560000001</v>
@@ -4174,7 +4174,7 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C29">
         <v>408928.25300000003</v>
@@ -4191,7 +4191,7 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C30">
         <v>408927.64370000002</v>
@@ -4208,7 +4208,7 @@
         <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C31">
         <v>408927.035299999</v>
@@ -4225,7 +4225,7 @@
         <v>85</v>
       </c>
       <c r="B32" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C32">
         <v>408933.28</v>
@@ -4242,7 +4242,7 @@
         <v>140</v>
       </c>
       <c r="B33" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C33">
         <v>408933.33</v>
@@ -4259,7 +4259,7 @@
         <v>141</v>
       </c>
       <c r="B34" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C34">
         <v>408934.59</v>
@@ -4276,7 +4276,7 @@
         <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C35">
         <v>408914.35340000002</v>
@@ -4293,7 +4293,7 @@
         <v>14</v>
       </c>
       <c r="B36" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C36">
         <v>408913.7599</v>
@@ -4310,7 +4310,7 @@
         <v>15</v>
       </c>
       <c r="B37" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C37">
         <v>408913.14380000002</v>
@@ -4327,7 +4327,7 @@
         <v>16</v>
       </c>
       <c r="B38" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C38">
         <v>408912.52870000002</v>
@@ -4344,7 +4344,7 @@
         <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C39">
         <v>408904.549999999</v>
@@ -4361,7 +4361,7 @@
         <v>138</v>
       </c>
       <c r="B40" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C40">
         <v>408906.5</v>
@@ -4378,7 +4378,7 @@
         <v>139</v>
       </c>
       <c r="B41" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C41">
         <v>408905.239999999</v>
@@ -4395,7 +4395,7 @@
         <v>153</v>
       </c>
       <c r="B42" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C42">
         <v>408900.20380000002</v>
@@ -4412,7 +4412,7 @@
         <v>154</v>
       </c>
       <c r="B43" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C43">
         <v>408899.61949999898</v>
@@ -4429,7 +4429,7 @@
         <v>155</v>
       </c>
       <c r="B44" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C44">
         <v>408899.00260000001</v>
@@ -4446,7 +4446,7 @@
         <v>156</v>
       </c>
       <c r="B45" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C45">
         <v>408898.37829999899</v>
@@ -4463,7 +4463,7 @@
         <v>87</v>
       </c>
       <c r="B46" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C46">
         <v>408877.08</v>
@@ -4480,7 +4480,7 @@
         <v>134</v>
       </c>
       <c r="B47" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C47">
         <v>408879.09999999899</v>
@@ -4497,7 +4497,7 @@
         <v>135</v>
       </c>
       <c r="B48" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C48">
         <v>408877.859999999</v>
@@ -4514,7 +4514,7 @@
         <v>157</v>
       </c>
       <c r="B49" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C49">
         <v>408885.99040000001</v>
@@ -4531,7 +4531,7 @@
         <v>158</v>
       </c>
       <c r="B50" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C50">
         <v>408885.37439999898</v>
@@ -4548,7 +4548,7 @@
         <v>159</v>
       </c>
       <c r="B51" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C51">
         <v>408884.80279999902</v>
@@ -4565,7 +4565,7 @@
         <v>160</v>
       </c>
       <c r="B52" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C52">
         <v>408884.17149999901</v>
@@ -4582,7 +4582,7 @@
         <v>17</v>
       </c>
       <c r="B53" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C53">
         <v>408859.25290000002</v>
@@ -4599,7 +4599,7 @@
         <v>18</v>
       </c>
       <c r="B54" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C54">
         <v>408858.64659999899</v>
@@ -4616,7 +4616,7 @@
         <v>19</v>
       </c>
       <c r="B55" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C55">
         <v>408858.0344</v>
@@ -4633,7 +4633,7 @@
         <v>20</v>
       </c>
       <c r="B56" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C56">
         <v>408857.44079999899</v>
@@ -4650,7 +4650,7 @@
         <v>21</v>
       </c>
       <c r="B57" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C57">
         <v>408845.03460000001</v>
@@ -4667,7 +4667,7 @@
         <v>22</v>
       </c>
       <c r="B58" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C58">
         <v>408844.4375</v>
@@ -4684,7 +4684,7 @@
         <v>23</v>
       </c>
       <c r="B59" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C59">
         <v>408843.829399999</v>
@@ -4701,7 +4701,7 @@
         <v>24</v>
       </c>
       <c r="B60" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C60">
         <v>408843.20490000001</v>
@@ -4718,7 +4718,7 @@
         <v>88</v>
       </c>
       <c r="B61" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C61">
         <v>408849.53</v>
@@ -4735,7 +4735,7 @@
         <v>132</v>
       </c>
       <c r="B62" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C62">
         <v>408849.489999999</v>
@@ -4752,7 +4752,7 @@
         <v>133</v>
       </c>
       <c r="B63" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C63">
         <v>408850.72999999899</v>
@@ -4769,7 +4769,7 @@
         <v>25</v>
       </c>
       <c r="B64" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C64">
         <v>408830.81489999901</v>
@@ -4786,7 +4786,7 @@
         <v>26</v>
       </c>
       <c r="B65" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C65">
         <v>408830.206899999</v>
@@ -4803,7 +4803,7 @@
         <v>27</v>
       </c>
       <c r="B66" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C66">
         <v>408829.59519999899</v>
@@ -4820,7 +4820,7 @@
         <v>28</v>
       </c>
       <c r="B67" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C67">
         <v>408828.99920000002</v>
@@ -4837,7 +4837,7 @@
         <v>29</v>
       </c>
       <c r="B68" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C68">
         <v>408816.59179999901</v>
@@ -4854,7 +4854,7 @@
         <v>30</v>
       </c>
       <c r="B69" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C69">
         <v>408815.986199999</v>
@@ -4871,7 +4871,7 @@
         <v>31</v>
       </c>
       <c r="B70" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C70">
         <v>408815.39</v>
@@ -4888,7 +4888,7 @@
         <v>32</v>
       </c>
       <c r="B71" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C71">
         <v>408814.777</v>
@@ -4905,7 +4905,7 @@
         <v>89</v>
       </c>
       <c r="B72" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C72">
         <v>408821.01</v>
@@ -4922,7 +4922,7 @@
         <v>128</v>
       </c>
       <c r="B73" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C73">
         <v>408821.109999999</v>
@@ -4939,7 +4939,7 @@
         <v>129</v>
       </c>
       <c r="B74" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C74">
         <v>408822.35</v>
@@ -4956,7 +4956,7 @@
         <v>33</v>
       </c>
       <c r="B75" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C75">
         <v>408802.449499999</v>
@@ -4973,7 +4973,7 @@
         <v>34</v>
       </c>
       <c r="B76" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C76">
         <v>408801.83819999901</v>
@@ -4990,7 +4990,7 @@
         <v>35</v>
       </c>
       <c r="B77" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C77">
         <v>408801.21379999898</v>
@@ -5007,7 +5007,7 @@
         <v>36</v>
       </c>
       <c r="B78" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C78">
         <v>408800.62819999899</v>
@@ -5024,7 +5024,7 @@
         <v>37</v>
       </c>
       <c r="B79" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C79">
         <v>408788.22350000002</v>
@@ -5041,7 +5041,7 @@
         <v>38</v>
       </c>
       <c r="B80" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C80">
         <v>408787.60700000002</v>
@@ -5058,7 +5058,7 @@
         <v>39</v>
       </c>
       <c r="B81" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C81">
         <v>408787.00040000002</v>
@@ -5075,7 +5075,7 @@
         <v>40</v>
       </c>
       <c r="B82" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C82">
         <v>408786.40159999899</v>
@@ -5092,7 +5092,7 @@
         <v>90</v>
       </c>
       <c r="B83" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C83">
         <v>408792.64</v>
@@ -5109,7 +5109,7 @@
         <v>126</v>
       </c>
       <c r="B84" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C84">
         <v>408794.59</v>
@@ -5126,7 +5126,7 @@
         <v>127</v>
       </c>
       <c r="B85" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C85">
         <v>408793.34999999899</v>
@@ -5143,7 +5143,7 @@
         <v>41</v>
       </c>
       <c r="B86" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C86">
         <v>408773.99790000002</v>
@@ -5160,7 +5160,7 @@
         <v>42</v>
       </c>
       <c r="B87" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C87">
         <v>408773.39649999898</v>
@@ -5177,7 +5177,7 @@
         <v>43</v>
       </c>
       <c r="B88" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C88">
         <v>408772.784099999</v>
@@ -5194,7 +5194,7 @@
         <v>44</v>
       </c>
       <c r="B89" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C89">
         <v>408772.17050000001</v>
@@ -5211,7 +5211,7 @@
         <v>45</v>
       </c>
       <c r="B90" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C90">
         <v>408759.7758</v>
@@ -5228,7 +5228,7 @@
         <v>46</v>
       </c>
       <c r="B91" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C91">
         <v>408759.1692</v>
@@ -5245,7 +5245,7 @@
         <v>47</v>
       </c>
       <c r="B92" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C92">
         <v>408758.57179999899</v>
@@ -5262,7 +5262,7 @@
         <v>48</v>
       </c>
       <c r="B93" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C93">
         <v>408757.959299999</v>
@@ -5279,7 +5279,7 @@
         <v>91</v>
       </c>
       <c r="B94" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C94">
         <v>408764.2</v>
@@ -5296,7 +5296,7 @@
         <v>122</v>
       </c>
       <c r="B95" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C95">
         <v>408766.09</v>
@@ -5313,7 +5313,7 @@
         <v>123</v>
       </c>
       <c r="B96" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C96">
         <v>408764.84999999899</v>
@@ -5330,7 +5330,7 @@
         <v>67</v>
       </c>
       <c r="B97" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C97">
         <v>408685.49530000001</v>
@@ -5347,7 +5347,7 @@
         <v>68</v>
       </c>
       <c r="B98" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C98">
         <v>408676.1875</v>
@@ -5364,7 +5364,7 @@
         <v>70</v>
       </c>
       <c r="B99" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C99">
         <v>408673.02689999901</v>
@@ -5381,7 +5381,7 @@
         <v>94</v>
       </c>
       <c r="B100" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C100">
         <v>408678.94</v>
@@ -5398,7 +5398,7 @@
         <v>113</v>
       </c>
       <c r="B101" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C101">
         <v>408680.549999999</v>
@@ -5415,7 +5415,7 @@
         <v>114</v>
       </c>
       <c r="B102" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C102">
         <v>408679.679999999</v>
@@ -5432,7 +5432,7 @@
         <v>115</v>
       </c>
       <c r="B103" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C103">
         <v>408678.72999999899</v>
@@ -5462,211 +5462,211 @@
         <v>121</v>
       </c>
       <c r="C1" t="s">
+        <v>422</v>
+      </c>
+      <c r="D1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E1" t="s">
         <v>424</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>135</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>136</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>137</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>138</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>139</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>140</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>141</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>142</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>143</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>144</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>145</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>146</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>147</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>148</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>149</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>150</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>151</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>152</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>153</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>154</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>155</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>156</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>157</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>158</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>159</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>160</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>161</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>162</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>163</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>164</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>165</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>166</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>167</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>168</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AN1" t="s">
         <v>169</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AO1" t="s">
         <v>170</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>171</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>172</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>173</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>174</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AT1" t="s">
         <v>175</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>176</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>177</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>178</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>179</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>180</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>181</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>182</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" t="s">
         <v>183</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>184</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BD1" t="s">
         <v>185</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>186</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>187</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>188</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
         <v>189</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BI1" t="s">
         <v>190</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BJ1" t="s">
         <v>191</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BK1" t="s">
         <v>192</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BL1" t="s">
         <v>193</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>194</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>195</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>196</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>197</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>198</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>199</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>200</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>201</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">
@@ -29887,211 +29887,211 @@
         <v>134</v>
       </c>
       <c r="C1" t="s">
+        <v>422</v>
+      </c>
+      <c r="D1" t="s">
+        <v>423</v>
+      </c>
+      <c r="E1" t="s">
         <v>424</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>135</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>136</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>137</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>138</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>139</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>140</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>141</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>142</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>143</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>144</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>145</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>146</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>147</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>148</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>149</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>150</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>151</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>152</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>153</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>154</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>155</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>156</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>157</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>158</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>159</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>160</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>161</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>162</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>163</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>164</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>165</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>166</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>167</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>168</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AN1" t="s">
         <v>169</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AO1" t="s">
         <v>170</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>171</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>172</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>173</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>174</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AT1" t="s">
         <v>175</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>176</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>177</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>178</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>179</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AY1" t="s">
         <v>180</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AZ1" t="s">
         <v>181</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BA1" t="s">
         <v>182</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BB1" t="s">
         <v>183</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BC1" t="s">
         <v>184</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BD1" t="s">
         <v>185</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BE1" t="s">
         <v>186</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BF1" t="s">
         <v>187</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BG1" t="s">
         <v>188</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
         <v>189</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BI1" t="s">
         <v>190</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BJ1" t="s">
         <v>191</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BK1" t="s">
         <v>192</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BL1" t="s">
         <v>193</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BM1" t="s">
         <v>194</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BN1" t="s">
         <v>195</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BO1" t="s">
         <v>196</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>197</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BQ1" t="s">
         <v>198</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BR1" t="s">
         <v>199</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BS1" t="s">
         <v>200</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>201</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:71" x14ac:dyDescent="0.25">
